--- a/exercices/pib_suisse_seco_revenu.xlsx
+++ b/exercices/pib_suisse_seco_revenu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA94C60-B277-41E8-BE05-1BE190E6B25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6278A2FB-3B41-4C61-9E9E-5EBE8DE39713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="swiss_qna" sheetId="22080" r:id="rId1"/>
@@ -20,19 +20,6 @@
     <sheet name="beschriftung" sheetId="22045" state="veryHidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -565,6 +552,7 @@
       <sz val="8"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -819,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
@@ -874,28 +862,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -963,8 +930,28 @@
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1268,7 +1255,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>1079500</xdr:colOff>
+          <xdr:colOff>1081088</xdr:colOff>
           <xdr:row>25</xdr:row>
           <xdr:rowOff>57150</xdr:rowOff>
         </xdr:to>
@@ -1280,7 +1267,7 @@
                   <a14:compatExt spid="_x0000_s4097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{332CF6D2-BE22-6647-D8C6-21BC46AE78C2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1670,121 +1657,121 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="150.77734375" customWidth="1"/>
+    <col min="1" max="1" width="150.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2"/>
     </row>
-    <row r="2" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
     </row>
   </sheetData>
@@ -1808,7 +1795,7 @@
                   </from>
                   <to>
                     <xdr:col>0</xdr:col>
-                    <xdr:colOff>1079500</xdr:colOff>
+                    <xdr:colOff>1081088</xdr:colOff>
                     <xdr:row>25</xdr:row>
                     <xdr:rowOff>57150</xdr:rowOff>
                   </to>
@@ -1827,14 +1814,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Table03"/>
   <dimension ref="A1:AH195"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="34" width="9.77734375" customWidth="1"/>
+    <col min="3" max="34" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A1)-1,COLUMN(beschriftung!A$1)))</f>
         <v>ESA 2010, Quarterly aggregates of Gross Domestic Product, income approach, raw data</v>
@@ -1870,7 +1857,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="10"/>
     </row>
-    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A2)-1,COLUMN(beschriftung!A$1)))</f>
         <v>In Mio. Swiss Francs, at current prices, percentage change to previous year</v>
@@ -1906,7 +1893,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="9"/>
@@ -1938,354 +1925,354 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="C4" s="20" t="str">
+      <c r="C4" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!C$1)))</f>
         <v xml:space="preserve">Gross domestic product </v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="20" t="str">
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!O$1)))</f>
         <v>Gross national income</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="20" t="str">
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!AA$1)))</f>
         <v>Disposable income, gross</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="21"/>
-      <c r="AF4" s="22"/>
-    </row>
-    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="39"/>
+    </row>
+    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="20" t="str">
+      <c r="C5" s="31"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!E$1)))</f>
         <v>Compensation of employees</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="20" t="str">
+      <c r="F5" s="39"/>
+      <c r="G5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!G$1)))</f>
         <v>Net operating surplus and net mixed income</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="20" t="str">
+      <c r="H5" s="39"/>
+      <c r="I5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!I$1)))</f>
         <v xml:space="preserve">Consumption of fixed capital </v>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="20" t="str">
+      <c r="J5" s="39"/>
+      <c r="K5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!K$1)))</f>
         <v>Taxes on production and imports</v>
       </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="20" t="str">
+      <c r="L5" s="39"/>
+      <c r="M5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!M$1)))</f>
         <v>Subsidies</v>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="20" t="str">
+      <c r="N5" s="39"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Q$1)))</f>
         <v>Compensation of employees received from the rest of the world</v>
       </c>
-      <c r="R5" s="22"/>
-      <c r="S5" s="20" t="str">
+      <c r="R5" s="39"/>
+      <c r="S5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!S$1)))</f>
         <v>Compensation of employees paid to the rest of the world</v>
       </c>
-      <c r="T5" s="22"/>
-      <c r="U5" s="20" t="str">
+      <c r="T5" s="39"/>
+      <c r="U5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!U$1)))</f>
         <v>Taxes on production and imports received from the rest of the world</v>
       </c>
-      <c r="V5" s="22"/>
-      <c r="W5" s="20" t="str">
+      <c r="V5" s="39"/>
+      <c r="W5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!W$1)))</f>
         <v>Property income received from the rest of the world</v>
       </c>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="20" t="str">
+      <c r="X5" s="39"/>
+      <c r="Y5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Y$1)))</f>
         <v>Property income paid to the rest of the world</v>
       </c>
-      <c r="Z5" s="22"/>
+      <c r="Z5" s="39"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="11" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1))))</f>
         <v/>
       </c>
-      <c r="AC5" s="20" t="str">
+      <c r="AC5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AC$1)))</f>
         <v>Current transfers receivable from the rest of the world</v>
       </c>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="20" t="str">
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AE$1)))</f>
         <v>Current transfers payable to the rest of the world</v>
       </c>
-      <c r="AF5" s="22"/>
-    </row>
-    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF5" s="39"/>
+    </row>
+    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="24"/>
-    </row>
-    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="32"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="41"/>
+    </row>
+    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="24"/>
-    </row>
-    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="32"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="41"/>
+    </row>
+    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="24"/>
-    </row>
-    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="32"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="41"/>
+    </row>
+    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="24"/>
-    </row>
-    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="32"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="41"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="41"/>
+    </row>
+    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="26"/>
-    </row>
-    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="33"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="42"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="42"/>
+      <c r="AF10" s="43"/>
+    </row>
+    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42" t="s">
+      <c r="D11" s="35"/>
+      <c r="E11" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="42" t="s">
+      <c r="F11" s="37"/>
+      <c r="G11" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42" t="s">
+      <c r="H11" s="37"/>
+      <c r="I11" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="42" t="s">
+      <c r="J11" s="37"/>
+      <c r="K11" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="42" t="s">
+      <c r="L11" s="37"/>
+      <c r="M11" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="43"/>
-      <c r="O11" s="27" t="s">
+      <c r="N11" s="37"/>
+      <c r="O11" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="27" t="s">
+      <c r="P11" s="22"/>
+      <c r="Q11" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="28"/>
-      <c r="S11" s="27" t="s">
+      <c r="R11" s="22"/>
+      <c r="S11" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27" t="s">
+      <c r="T11" s="22"/>
+      <c r="U11" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="V11" s="28"/>
-      <c r="W11" s="27" t="s">
+      <c r="V11" s="22"/>
+      <c r="W11" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="27" t="s">
+      <c r="X11" s="22"/>
+      <c r="Y11" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="27" t="s">
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="27" t="s">
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="27" t="s">
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="AF11" s="28"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AF11" s="22"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <v>1980</v>
       </c>
@@ -2327,7 +2314,7 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="19"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>1980</v>
       </c>
@@ -2369,7 +2356,7 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="19"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>1980</v>
       </c>
@@ -2411,7 +2398,7 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="19"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>1980</v>
       </c>
@@ -2453,7 +2440,7 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="19"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>1981</v>
       </c>
@@ -2497,7 +2484,7 @@
       <c r="AG16" s="18"/>
       <c r="AH16" s="19"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>1981</v>
       </c>
@@ -2541,7 +2528,7 @@
       <c r="AG17" s="18"/>
       <c r="AH17" s="19"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>1981</v>
       </c>
@@ -2585,7 +2572,7 @@
       <c r="AG18" s="18"/>
       <c r="AH18" s="19"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
         <v>1981</v>
       </c>
@@ -2629,7 +2616,7 @@
       <c r="AG19" s="18"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
         <v>1982</v>
       </c>
@@ -2673,7 +2660,7 @@
       <c r="AG20" s="18"/>
       <c r="AH20" s="19"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <v>1982</v>
       </c>
@@ -2717,7 +2704,7 @@
       <c r="AG21" s="18"/>
       <c r="AH21" s="19"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>1982</v>
       </c>
@@ -2761,7 +2748,7 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="19"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <v>1982</v>
       </c>
@@ -2805,7 +2792,7 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="19"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <v>1983</v>
       </c>
@@ -2849,7 +2836,7 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="19"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>1983</v>
       </c>
@@ -2893,7 +2880,7 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="19"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>1983</v>
       </c>
@@ -2937,7 +2924,7 @@
       <c r="AG26" s="18"/>
       <c r="AH26" s="19"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>1983</v>
       </c>
@@ -2981,7 +2968,7 @@
       <c r="AG27" s="18"/>
       <c r="AH27" s="19"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <v>1984</v>
       </c>
@@ -3025,7 +3012,7 @@
       <c r="AG28" s="18"/>
       <c r="AH28" s="19"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A29" s="17">
         <v>1984</v>
       </c>
@@ -3069,7 +3056,7 @@
       <c r="AG29" s="18"/>
       <c r="AH29" s="19"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A30" s="17">
         <v>1984</v>
       </c>
@@ -3113,7 +3100,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="19"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A31" s="17">
         <v>1984</v>
       </c>
@@ -3157,7 +3144,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="19"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A32" s="17">
         <v>1985</v>
       </c>
@@ -3201,7 +3188,7 @@
       <c r="AG32" s="18"/>
       <c r="AH32" s="19"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33" s="17">
         <v>1985</v>
       </c>
@@ -3245,7 +3232,7 @@
       <c r="AG33" s="18"/>
       <c r="AH33" s="19"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A34" s="17">
         <v>1985</v>
       </c>
@@ -3289,7 +3276,7 @@
       <c r="AG34" s="18"/>
       <c r="AH34" s="19"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A35" s="17">
         <v>1985</v>
       </c>
@@ -3333,7 +3320,7 @@
       <c r="AG35" s="18"/>
       <c r="AH35" s="19"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A36" s="17">
         <v>1986</v>
       </c>
@@ -3377,7 +3364,7 @@
       <c r="AG36" s="18"/>
       <c r="AH36" s="19"/>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A37" s="17">
         <v>1986</v>
       </c>
@@ -3421,7 +3408,7 @@
       <c r="AG37" s="18"/>
       <c r="AH37" s="19"/>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>1986</v>
       </c>
@@ -3465,7 +3452,7 @@
       <c r="AG38" s="18"/>
       <c r="AH38" s="19"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <v>1986</v>
       </c>
@@ -3509,7 +3496,7 @@
       <c r="AG39" s="18"/>
       <c r="AH39" s="19"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A40" s="17">
         <v>1987</v>
       </c>
@@ -3553,7 +3540,7 @@
       <c r="AG40" s="18"/>
       <c r="AH40" s="19"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A41" s="17">
         <v>1987</v>
       </c>
@@ -3597,7 +3584,7 @@
       <c r="AG41" s="18"/>
       <c r="AH41" s="19"/>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A42" s="17">
         <v>1987</v>
       </c>
@@ -3641,7 +3628,7 @@
       <c r="AG42" s="18"/>
       <c r="AH42" s="19"/>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A43" s="17">
         <v>1987</v>
       </c>
@@ -3685,7 +3672,7 @@
       <c r="AG43" s="18"/>
       <c r="AH43" s="19"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A44" s="17">
         <v>1988</v>
       </c>
@@ -3729,7 +3716,7 @@
       <c r="AG44" s="18"/>
       <c r="AH44" s="19"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A45" s="17">
         <v>1988</v>
       </c>
@@ -3773,7 +3760,7 @@
       <c r="AG45" s="18"/>
       <c r="AH45" s="19"/>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A46" s="17">
         <v>1988</v>
       </c>
@@ -3817,7 +3804,7 @@
       <c r="AG46" s="18"/>
       <c r="AH46" s="19"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A47" s="17">
         <v>1988</v>
       </c>
@@ -3861,7 +3848,7 @@
       <c r="AG47" s="18"/>
       <c r="AH47" s="19"/>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A48" s="17">
         <v>1989</v>
       </c>
@@ -3905,7 +3892,7 @@
       <c r="AG48" s="18"/>
       <c r="AH48" s="19"/>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A49" s="17">
         <v>1989</v>
       </c>
@@ -3949,7 +3936,7 @@
       <c r="AG49" s="18"/>
       <c r="AH49" s="19"/>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A50" s="17">
         <v>1989</v>
       </c>
@@ -3993,7 +3980,7 @@
       <c r="AG50" s="18"/>
       <c r="AH50" s="19"/>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A51" s="17">
         <v>1989</v>
       </c>
@@ -4037,7 +4024,7 @@
       <c r="AG51" s="18"/>
       <c r="AH51" s="19"/>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A52" s="17">
         <v>1990</v>
       </c>
@@ -4109,7 +4096,7 @@
       <c r="AG52" s="18"/>
       <c r="AH52" s="19"/>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A53" s="17">
         <v>1990</v>
       </c>
@@ -4181,7 +4168,7 @@
       <c r="AG53" s="18"/>
       <c r="AH53" s="19"/>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A54" s="17">
         <v>1990</v>
       </c>
@@ -4253,7 +4240,7 @@
       <c r="AG54" s="18"/>
       <c r="AH54" s="19"/>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A55" s="17">
         <v>1990</v>
       </c>
@@ -4325,7 +4312,7 @@
       <c r="AG55" s="18"/>
       <c r="AH55" s="19"/>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A56" s="17">
         <v>1991</v>
       </c>
@@ -4425,7 +4412,7 @@
       <c r="AG56" s="18"/>
       <c r="AH56" s="19"/>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A57" s="17">
         <v>1991</v>
       </c>
@@ -4525,7 +4512,7 @@
       <c r="AG57" s="18"/>
       <c r="AH57" s="19"/>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A58" s="17">
         <v>1991</v>
       </c>
@@ -4625,7 +4612,7 @@
       <c r="AG58" s="18"/>
       <c r="AH58" s="19"/>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A59" s="17">
         <v>1991</v>
       </c>
@@ -4725,7 +4712,7 @@
       <c r="AG59" s="18"/>
       <c r="AH59" s="19"/>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A60" s="17">
         <v>1992</v>
       </c>
@@ -4825,7 +4812,7 @@
       <c r="AG60" s="18"/>
       <c r="AH60" s="19"/>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A61" s="17">
         <v>1992</v>
       </c>
@@ -4925,7 +4912,7 @@
       <c r="AG61" s="18"/>
       <c r="AH61" s="19"/>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A62" s="17">
         <v>1992</v>
       </c>
@@ -5025,7 +5012,7 @@
       <c r="AG62" s="18"/>
       <c r="AH62" s="19"/>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A63" s="17">
         <v>1992</v>
       </c>
@@ -5125,7 +5112,7 @@
       <c r="AG63" s="18"/>
       <c r="AH63" s="19"/>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A64" s="17">
         <v>1993</v>
       </c>
@@ -5225,7 +5212,7 @@
       <c r="AG64" s="18"/>
       <c r="AH64" s="19"/>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A65" s="17">
         <v>1993</v>
       </c>
@@ -5325,7 +5312,7 @@
       <c r="AG65" s="18"/>
       <c r="AH65" s="19"/>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A66" s="17">
         <v>1993</v>
       </c>
@@ -5425,7 +5412,7 @@
       <c r="AG66" s="18"/>
       <c r="AH66" s="19"/>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A67" s="17">
         <v>1993</v>
       </c>
@@ -5525,7 +5512,7 @@
       <c r="AG67" s="18"/>
       <c r="AH67" s="19"/>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A68" s="17">
         <v>1994</v>
       </c>
@@ -5625,7 +5612,7 @@
       <c r="AG68" s="18"/>
       <c r="AH68" s="19"/>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A69" s="17">
         <v>1994</v>
       </c>
@@ -5725,7 +5712,7 @@
       <c r="AG69" s="18"/>
       <c r="AH69" s="19"/>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A70" s="17">
         <v>1994</v>
       </c>
@@ -5825,7 +5812,7 @@
       <c r="AG70" s="18"/>
       <c r="AH70" s="19"/>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A71" s="17">
         <v>1994</v>
       </c>
@@ -5925,7 +5912,7 @@
       <c r="AG71" s="18"/>
       <c r="AH71" s="19"/>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A72" s="17">
         <v>1995</v>
       </c>
@@ -6025,7 +6012,7 @@
       <c r="AG72" s="18"/>
       <c r="AH72" s="19"/>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A73" s="17">
         <v>1995</v>
       </c>
@@ -6125,7 +6112,7 @@
       <c r="AG73" s="18"/>
       <c r="AH73" s="19"/>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A74" s="17">
         <v>1995</v>
       </c>
@@ -6225,7 +6212,7 @@
       <c r="AG74" s="18"/>
       <c r="AH74" s="19"/>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A75" s="17">
         <v>1995</v>
       </c>
@@ -6325,7 +6312,7 @@
       <c r="AG75" s="18"/>
       <c r="AH75" s="19"/>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A76" s="17">
         <v>1996</v>
       </c>
@@ -6425,7 +6412,7 @@
       <c r="AG76" s="18"/>
       <c r="AH76" s="19"/>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A77" s="17">
         <v>1996</v>
       </c>
@@ -6525,7 +6512,7 @@
       <c r="AG77" s="18"/>
       <c r="AH77" s="19"/>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A78" s="17">
         <v>1996</v>
       </c>
@@ -6625,7 +6612,7 @@
       <c r="AG78" s="18"/>
       <c r="AH78" s="19"/>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A79" s="17">
         <v>1996</v>
       </c>
@@ -6725,7 +6712,7 @@
       <c r="AG79" s="18"/>
       <c r="AH79" s="19"/>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A80" s="17">
         <v>1997</v>
       </c>
@@ -6825,7 +6812,7 @@
       <c r="AG80" s="18"/>
       <c r="AH80" s="19"/>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A81" s="17">
         <v>1997</v>
       </c>
@@ -6925,7 +6912,7 @@
       <c r="AG81" s="18"/>
       <c r="AH81" s="19"/>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A82" s="17">
         <v>1997</v>
       </c>
@@ -7025,7 +7012,7 @@
       <c r="AG82" s="18"/>
       <c r="AH82" s="19"/>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A83" s="17">
         <v>1997</v>
       </c>
@@ -7125,7 +7112,7 @@
       <c r="AG83" s="18"/>
       <c r="AH83" s="19"/>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A84" s="17">
         <v>1998</v>
       </c>
@@ -7225,7 +7212,7 @@
       <c r="AG84" s="18"/>
       <c r="AH84" s="19"/>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A85" s="17">
         <v>1998</v>
       </c>
@@ -7325,7 +7312,7 @@
       <c r="AG85" s="18"/>
       <c r="AH85" s="19"/>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A86" s="17">
         <v>1998</v>
       </c>
@@ -7425,7 +7412,7 @@
       <c r="AG86" s="18"/>
       <c r="AH86" s="19"/>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A87" s="17">
         <v>1998</v>
       </c>
@@ -7525,7 +7512,7 @@
       <c r="AG87" s="18"/>
       <c r="AH87" s="19"/>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A88" s="17">
         <v>1999</v>
       </c>
@@ -7625,7 +7612,7 @@
       <c r="AG88" s="18"/>
       <c r="AH88" s="19"/>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A89" s="17">
         <v>1999</v>
       </c>
@@ -7725,7 +7712,7 @@
       <c r="AG89" s="18"/>
       <c r="AH89" s="19"/>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A90" s="17">
         <v>1999</v>
       </c>
@@ -7825,7 +7812,7 @@
       <c r="AG90" s="18"/>
       <c r="AH90" s="19"/>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A91" s="17">
         <v>1999</v>
       </c>
@@ -7925,7 +7912,7 @@
       <c r="AG91" s="18"/>
       <c r="AH91" s="19"/>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A92" s="17">
         <v>2000</v>
       </c>
@@ -8025,7 +8012,7 @@
       <c r="AG92" s="18"/>
       <c r="AH92" s="19"/>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A93" s="17">
         <v>2000</v>
       </c>
@@ -8125,7 +8112,7 @@
       <c r="AG93" s="18"/>
       <c r="AH93" s="19"/>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A94" s="17">
         <v>2000</v>
       </c>
@@ -8225,7 +8212,7 @@
       <c r="AG94" s="18"/>
       <c r="AH94" s="19"/>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A95" s="17">
         <v>2000</v>
       </c>
@@ -8325,7 +8312,7 @@
       <c r="AG95" s="18"/>
       <c r="AH95" s="19"/>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A96" s="17">
         <v>2001</v>
       </c>
@@ -8425,7 +8412,7 @@
       <c r="AG96" s="18"/>
       <c r="AH96" s="19"/>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A97" s="17">
         <v>2001</v>
       </c>
@@ -8525,7 +8512,7 @@
       <c r="AG97" s="18"/>
       <c r="AH97" s="19"/>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A98" s="17">
         <v>2001</v>
       </c>
@@ -8625,7 +8612,7 @@
       <c r="AG98" s="18"/>
       <c r="AH98" s="19"/>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A99" s="17">
         <v>2001</v>
       </c>
@@ -8725,7 +8712,7 @@
       <c r="AG99" s="18"/>
       <c r="AH99" s="19"/>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A100" s="17">
         <v>2002</v>
       </c>
@@ -8825,7 +8812,7 @@
       <c r="AG100" s="18"/>
       <c r="AH100" s="19"/>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A101" s="17">
         <v>2002</v>
       </c>
@@ -8925,7 +8912,7 @@
       <c r="AG101" s="18"/>
       <c r="AH101" s="19"/>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A102" s="17">
         <v>2002</v>
       </c>
@@ -9025,7 +9012,7 @@
       <c r="AG102" s="18"/>
       <c r="AH102" s="19"/>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A103" s="17">
         <v>2002</v>
       </c>
@@ -9125,7 +9112,7 @@
       <c r="AG103" s="18"/>
       <c r="AH103" s="19"/>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A104" s="17">
         <v>2003</v>
       </c>
@@ -9225,7 +9212,7 @@
       <c r="AG104" s="18"/>
       <c r="AH104" s="19"/>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A105" s="17">
         <v>2003</v>
       </c>
@@ -9325,7 +9312,7 @@
       <c r="AG105" s="18"/>
       <c r="AH105" s="19"/>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A106" s="17">
         <v>2003</v>
       </c>
@@ -9425,7 +9412,7 @@
       <c r="AG106" s="18"/>
       <c r="AH106" s="19"/>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A107" s="17">
         <v>2003</v>
       </c>
@@ -9525,7 +9512,7 @@
       <c r="AG107" s="18"/>
       <c r="AH107" s="19"/>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A108" s="17">
         <v>2004</v>
       </c>
@@ -9625,7 +9612,7 @@
       <c r="AG108" s="18"/>
       <c r="AH108" s="19"/>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A109" s="17">
         <v>2004</v>
       </c>
@@ -9725,7 +9712,7 @@
       <c r="AG109" s="18"/>
       <c r="AH109" s="19"/>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A110" s="17">
         <v>2004</v>
       </c>
@@ -9825,7 +9812,7 @@
       <c r="AG110" s="18"/>
       <c r="AH110" s="19"/>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A111" s="17">
         <v>2004</v>
       </c>
@@ -9925,7 +9912,7 @@
       <c r="AG111" s="18"/>
       <c r="AH111" s="19"/>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A112" s="17">
         <v>2005</v>
       </c>
@@ -10025,7 +10012,7 @@
       <c r="AG112" s="18"/>
       <c r="AH112" s="19"/>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A113" s="17">
         <v>2005</v>
       </c>
@@ -10125,7 +10112,7 @@
       <c r="AG113" s="18"/>
       <c r="AH113" s="19"/>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A114" s="17">
         <v>2005</v>
       </c>
@@ -10225,7 +10212,7 @@
       <c r="AG114" s="18"/>
       <c r="AH114" s="19"/>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A115" s="17">
         <v>2005</v>
       </c>
@@ -10325,7 +10312,7 @@
       <c r="AG115" s="18"/>
       <c r="AH115" s="19"/>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A116" s="17">
         <v>2006</v>
       </c>
@@ -10425,7 +10412,7 @@
       <c r="AG116" s="18"/>
       <c r="AH116" s="19"/>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A117" s="17">
         <v>2006</v>
       </c>
@@ -10525,7 +10512,7 @@
       <c r="AG117" s="18"/>
       <c r="AH117" s="19"/>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A118" s="17">
         <v>2006</v>
       </c>
@@ -10625,7 +10612,7 @@
       <c r="AG118" s="18"/>
       <c r="AH118" s="19"/>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A119" s="17">
         <v>2006</v>
       </c>
@@ -10725,7 +10712,7 @@
       <c r="AG119" s="18"/>
       <c r="AH119" s="19"/>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A120" s="17">
         <v>2007</v>
       </c>
@@ -10825,7 +10812,7 @@
       <c r="AG120" s="18"/>
       <c r="AH120" s="19"/>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A121" s="17">
         <v>2007</v>
       </c>
@@ -10925,7 +10912,7 @@
       <c r="AG121" s="18"/>
       <c r="AH121" s="19"/>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A122" s="17">
         <v>2007</v>
       </c>
@@ -11025,7 +11012,7 @@
       <c r="AG122" s="18"/>
       <c r="AH122" s="19"/>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A123" s="17">
         <v>2007</v>
       </c>
@@ -11125,7 +11112,7 @@
       <c r="AG123" s="18"/>
       <c r="AH123" s="19"/>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A124" s="17">
         <v>2008</v>
       </c>
@@ -11225,7 +11212,7 @@
       <c r="AG124" s="18"/>
       <c r="AH124" s="19"/>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A125" s="17">
         <v>2008</v>
       </c>
@@ -11325,7 +11312,7 @@
       <c r="AG125" s="18"/>
       <c r="AH125" s="19"/>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A126" s="17">
         <v>2008</v>
       </c>
@@ -11425,7 +11412,7 @@
       <c r="AG126" s="18"/>
       <c r="AH126" s="19"/>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A127" s="17">
         <v>2008</v>
       </c>
@@ -11525,7 +11512,7 @@
       <c r="AG127" s="18"/>
       <c r="AH127" s="19"/>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A128" s="17">
         <v>2009</v>
       </c>
@@ -11625,7 +11612,7 @@
       <c r="AG128" s="18"/>
       <c r="AH128" s="19"/>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" s="17">
         <v>2009</v>
       </c>
@@ -11725,7 +11712,7 @@
       <c r="AG129" s="18"/>
       <c r="AH129" s="19"/>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" s="17">
         <v>2009</v>
       </c>
@@ -11825,7 +11812,7 @@
       <c r="AG130" s="18"/>
       <c r="AH130" s="19"/>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" s="17">
         <v>2009</v>
       </c>
@@ -11925,7 +11912,7 @@
       <c r="AG131" s="18"/>
       <c r="AH131" s="19"/>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" s="17">
         <v>2010</v>
       </c>
@@ -12025,7 +12012,7 @@
       <c r="AG132" s="18"/>
       <c r="AH132" s="19"/>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" s="17">
         <v>2010</v>
       </c>
@@ -12125,7 +12112,7 @@
       <c r="AG133" s="18"/>
       <c r="AH133" s="19"/>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A134" s="17">
         <v>2010</v>
       </c>
@@ -12225,7 +12212,7 @@
       <c r="AG134" s="18"/>
       <c r="AH134" s="19"/>
     </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" s="17">
         <v>2010</v>
       </c>
@@ -12325,7 +12312,7 @@
       <c r="AG135" s="18"/>
       <c r="AH135" s="19"/>
     </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" s="17">
         <v>2011</v>
       </c>
@@ -12425,7 +12412,7 @@
       <c r="AG136" s="18"/>
       <c r="AH136" s="19"/>
     </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" s="17">
         <v>2011</v>
       </c>
@@ -12525,7 +12512,7 @@
       <c r="AG137" s="18"/>
       <c r="AH137" s="19"/>
     </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" s="17">
         <v>2011</v>
       </c>
@@ -12625,7 +12612,7 @@
       <c r="AG138" s="18"/>
       <c r="AH138" s="19"/>
     </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" s="17">
         <v>2011</v>
       </c>
@@ -12725,7 +12712,7 @@
       <c r="AG139" s="18"/>
       <c r="AH139" s="19"/>
     </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" s="17">
         <v>2012</v>
       </c>
@@ -12825,7 +12812,7 @@
       <c r="AG140" s="18"/>
       <c r="AH140" s="19"/>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" s="17">
         <v>2012</v>
       </c>
@@ -12925,7 +12912,7 @@
       <c r="AG141" s="18"/>
       <c r="AH141" s="19"/>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" s="17">
         <v>2012</v>
       </c>
@@ -13025,7 +13012,7 @@
       <c r="AG142" s="18"/>
       <c r="AH142" s="19"/>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" s="17">
         <v>2012</v>
       </c>
@@ -13125,7 +13112,7 @@
       <c r="AG143" s="18"/>
       <c r="AH143" s="19"/>
     </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" s="17">
         <v>2013</v>
       </c>
@@ -13225,7 +13212,7 @@
       <c r="AG144" s="18"/>
       <c r="AH144" s="19"/>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A145" s="17">
         <v>2013</v>
       </c>
@@ -13325,7 +13312,7 @@
       <c r="AG145" s="18"/>
       <c r="AH145" s="19"/>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A146" s="17">
         <v>2013</v>
       </c>
@@ -13425,7 +13412,7 @@
       <c r="AG146" s="18"/>
       <c r="AH146" s="19"/>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A147" s="17">
         <v>2013</v>
       </c>
@@ -13525,7 +13512,7 @@
       <c r="AG147" s="18"/>
       <c r="AH147" s="19"/>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A148" s="17">
         <v>2014</v>
       </c>
@@ -13625,7 +13612,7 @@
       <c r="AG148" s="18"/>
       <c r="AH148" s="19"/>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A149" s="17">
         <v>2014</v>
       </c>
@@ -13725,7 +13712,7 @@
       <c r="AG149" s="18"/>
       <c r="AH149" s="19"/>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A150" s="17">
         <v>2014</v>
       </c>
@@ -13825,7 +13812,7 @@
       <c r="AG150" s="18"/>
       <c r="AH150" s="19"/>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A151" s="17">
         <v>2014</v>
       </c>
@@ -13925,7 +13912,7 @@
       <c r="AG151" s="18"/>
       <c r="AH151" s="19"/>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A152" s="17">
         <v>2015</v>
       </c>
@@ -14025,7 +14012,7 @@
       <c r="AG152" s="18"/>
       <c r="AH152" s="19"/>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A153" s="17">
         <v>2015</v>
       </c>
@@ -14125,7 +14112,7 @@
       <c r="AG153" s="18"/>
       <c r="AH153" s="19"/>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A154" s="17">
         <v>2015</v>
       </c>
@@ -14225,7 +14212,7 @@
       <c r="AG154" s="18"/>
       <c r="AH154" s="19"/>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A155" s="17">
         <v>2015</v>
       </c>
@@ -14325,7 +14312,7 @@
       <c r="AG155" s="18"/>
       <c r="AH155" s="19"/>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A156" s="17">
         <v>2016</v>
       </c>
@@ -14425,7 +14412,7 @@
       <c r="AG156" s="18"/>
       <c r="AH156" s="19"/>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A157" s="17">
         <v>2016</v>
       </c>
@@ -14525,7 +14512,7 @@
       <c r="AG157" s="18"/>
       <c r="AH157" s="19"/>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A158" s="17">
         <v>2016</v>
       </c>
@@ -14625,7 +14612,7 @@
       <c r="AG158" s="18"/>
       <c r="AH158" s="19"/>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A159" s="17">
         <v>2016</v>
       </c>
@@ -14725,7 +14712,7 @@
       <c r="AG159" s="18"/>
       <c r="AH159" s="19"/>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A160" s="17">
         <v>2017</v>
       </c>
@@ -14825,7 +14812,7 @@
       <c r="AG160" s="18"/>
       <c r="AH160" s="19"/>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A161" s="17">
         <v>2017</v>
       </c>
@@ -14925,7 +14912,7 @@
       <c r="AG161" s="18"/>
       <c r="AH161" s="19"/>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A162" s="17">
         <v>2017</v>
       </c>
@@ -15025,7 +15012,7 @@
       <c r="AG162" s="18"/>
       <c r="AH162" s="19"/>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A163" s="17">
         <v>2017</v>
       </c>
@@ -15125,7 +15112,7 @@
       <c r="AG163" s="18"/>
       <c r="AH163" s="19"/>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A164" s="17">
         <v>2018</v>
       </c>
@@ -15225,7 +15212,7 @@
       <c r="AG164" s="18"/>
       <c r="AH164" s="19"/>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A165" s="17">
         <v>2018</v>
       </c>
@@ -15325,7 +15312,7 @@
       <c r="AG165" s="18"/>
       <c r="AH165" s="19"/>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A166" s="17">
         <v>2018</v>
       </c>
@@ -15425,7 +15412,7 @@
       <c r="AG166" s="18"/>
       <c r="AH166" s="19"/>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A167" s="17">
         <v>2018</v>
       </c>
@@ -15525,7 +15512,7 @@
       <c r="AG167" s="18"/>
       <c r="AH167" s="19"/>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A168" s="17">
         <v>2019</v>
       </c>
@@ -15625,7 +15612,7 @@
       <c r="AG168" s="18"/>
       <c r="AH168" s="19"/>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A169" s="17">
         <v>2019</v>
       </c>
@@ -15725,7 +15712,7 @@
       <c r="AG169" s="18"/>
       <c r="AH169" s="19"/>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A170" s="17">
         <v>2019</v>
       </c>
@@ -15825,7 +15812,7 @@
       <c r="AG170" s="18"/>
       <c r="AH170" s="19"/>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A171" s="17">
         <v>2019</v>
       </c>
@@ -15925,7 +15912,7 @@
       <c r="AG171" s="18"/>
       <c r="AH171" s="19"/>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A172" s="17">
         <v>2020</v>
       </c>
@@ -16025,7 +16012,7 @@
       <c r="AG172" s="18"/>
       <c r="AH172" s="19"/>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A173" s="17">
         <v>2020</v>
       </c>
@@ -16125,7 +16112,7 @@
       <c r="AG173" s="18"/>
       <c r="AH173" s="19"/>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A174" s="17">
         <v>2020</v>
       </c>
@@ -16225,7 +16212,7 @@
       <c r="AG174" s="18"/>
       <c r="AH174" s="19"/>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A175" s="17">
         <v>2020</v>
       </c>
@@ -16325,7 +16312,7 @@
       <c r="AG175" s="18"/>
       <c r="AH175" s="19"/>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A176" s="17">
         <v>2021</v>
       </c>
@@ -16425,7 +16412,7 @@
       <c r="AG176" s="18"/>
       <c r="AH176" s="19"/>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A177" s="17">
         <v>2021</v>
       </c>
@@ -16525,7 +16512,7 @@
       <c r="AG177" s="18"/>
       <c r="AH177" s="19"/>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A178" s="17">
         <v>2021</v>
       </c>
@@ -16625,7 +16612,7 @@
       <c r="AG178" s="18"/>
       <c r="AH178" s="19"/>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A179" s="17">
         <v>2021</v>
       </c>
@@ -16725,7 +16712,7 @@
       <c r="AG179" s="18"/>
       <c r="AH179" s="19"/>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A180" s="17">
         <v>2022</v>
       </c>
@@ -16825,7 +16812,7 @@
       <c r="AG180" s="18"/>
       <c r="AH180" s="19"/>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A181" s="17">
         <v>2022</v>
       </c>
@@ -16925,7 +16912,7 @@
       <c r="AG181" s="18"/>
       <c r="AH181" s="19"/>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A182" s="17">
         <v>2022</v>
       </c>
@@ -17025,7 +17012,7 @@
       <c r="AG182" s="18"/>
       <c r="AH182" s="19"/>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A183" s="17">
         <v>2022</v>
       </c>
@@ -17125,7 +17112,7 @@
       <c r="AG183" s="18"/>
       <c r="AH183" s="19"/>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A184" s="17">
         <v>2023</v>
       </c>
@@ -17225,7 +17212,7 @@
       <c r="AG184" s="18"/>
       <c r="AH184" s="19"/>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A185" s="17">
         <v>2023</v>
       </c>
@@ -17325,7 +17312,7 @@
       <c r="AG185" s="18"/>
       <c r="AH185" s="19"/>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A186" s="17">
         <v>2023</v>
       </c>
@@ -17425,7 +17412,7 @@
       <c r="AG186" s="18"/>
       <c r="AH186" s="19"/>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A187" s="17">
         <v>2023</v>
       </c>
@@ -17525,7 +17512,7 @@
       <c r="AG187" s="18"/>
       <c r="AH187" s="19"/>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A188" s="17">
         <v>2024</v>
       </c>
@@ -17625,7 +17612,7 @@
       <c r="AG188" s="18"/>
       <c r="AH188" s="19"/>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A189" s="17">
         <v>2024</v>
       </c>
@@ -17725,7 +17712,7 @@
       <c r="AG189" s="18"/>
       <c r="AH189" s="19"/>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A190" s="17">
         <v>2024</v>
       </c>
@@ -17825,7 +17812,7 @@
       <c r="AG190" s="18"/>
       <c r="AH190" s="19"/>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A191" s="17">
         <v>2024</v>
       </c>
@@ -17925,7 +17912,7 @@
       <c r="AG191" s="18"/>
       <c r="AH191" s="19"/>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A192" s="17">
         <v>2025</v>
       </c>
@@ -18025,7 +18012,7 @@
       <c r="AG192" s="18"/>
       <c r="AH192" s="19"/>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A193" s="17">
         <v>2025</v>
       </c>
@@ -18125,7 +18112,7 @@
       <c r="AG193" s="18"/>
       <c r="AH193" s="19"/>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A194" s="17">
         <v>2025</v>
       </c>
@@ -18225,7 +18212,7 @@
       <c r="AG194" s="18"/>
       <c r="AH194" s="19"/>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A195" s="17"/>
       <c r="B195" s="17"/>
       <c r="C195" s="18"/>
@@ -18264,25 +18251,6 @@
   </sheetData>
   <sheetProtection password="DD0B" sheet="1"/>
   <mergeCells count="33">
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="AA6:AB10"/>
-    <mergeCell ref="O5:P10"/>
-    <mergeCell ref="C5:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="U5:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
     <mergeCell ref="AA4:AF4"/>
     <mergeCell ref="AC5:AD10"/>
     <mergeCell ref="AE5:AF10"/>
@@ -18297,6 +18265,25 @@
     <mergeCell ref="W5:X10"/>
     <mergeCell ref="Y5:Z10"/>
     <mergeCell ref="O4:Z4"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="AA6:AB10"/>
+    <mergeCell ref="O5:P10"/>
+    <mergeCell ref="C5:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="U5:V10"/>
+    <mergeCell ref="U11:V11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18307,14 +18294,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Table04"/>
   <dimension ref="A1:AH57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="34" width="9.77734375" customWidth="1"/>
+    <col min="3" max="34" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A1)-1,COLUMN(beschriftung!A$1)))</f>
         <v>ESA 2010, Quarterly aggregates of Gross Domestic Product, income approach, raw data</v>
@@ -18350,7 +18337,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="10"/>
     </row>
-    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A2)-1,COLUMN(beschriftung!B$1)))</f>
         <v>In Mio. Swiss Francs, at current prices, percentage change to previous year</v>
@@ -18386,7 +18373,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="9"/>
@@ -18418,427 +18405,427 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="C4" s="20" t="str">
+      <c r="C4" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!C$1)))</f>
         <v xml:space="preserve">Gross domestic product </v>
       </c>
-      <c r="D4" s="21" t="e">
+      <c r="D4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="E4" s="21" t="e">
+      <c r="E4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="F4" s="21" t="e">
+      <c r="F4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="G4" s="21" t="e">
+      <c r="G4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="H4" s="21" t="e">
+      <c r="H4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="I4" s="21" t="e">
+      <c r="I4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="J4" s="21" t="e">
+      <c r="J4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="K4" s="21" t="e">
+      <c r="K4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="L4" s="21" t="e">
+      <c r="L4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="M4" s="21" t="e">
+      <c r="M4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="N4" s="22" t="e">
+      <c r="N4" s="39" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="O4" s="20" t="str">
+      <c r="O4" s="38" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A5)-1,COLUMN(O$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A5)-1,COLUMN(O$1))))</f>
         <v>Gross national income</v>
       </c>
-      <c r="P4" s="21" t="e">
+      <c r="P4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q4" s="21" t="e">
+      <c r="Q4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="R4" s="21" t="e">
+      <c r="R4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="S4" s="21" t="e">
+      <c r="S4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="T4" s="21" t="e">
+      <c r="T4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21" t="e">
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="X4" s="21" t="e">
+      <c r="X4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Y4" s="21" t="e">
+      <c r="Y4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Z4" s="22" t="e">
+      <c r="Z4" s="39" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="AA4" s="20" t="str">
+      <c r="AA4" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!AA$1)))</f>
         <v>Disposable income, gross</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="21"/>
-      <c r="AF4" s="22"/>
-    </row>
-    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="39"/>
+    </row>
+    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="20" t="str">
+      <c r="C5" s="31"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!E$1)))</f>
         <v>Compensation of employees</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="20" t="str">
+      <c r="F5" s="39"/>
+      <c r="G5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!G$1)))</f>
         <v>Net operating surplus and net mixed income</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="20" t="str">
+      <c r="H5" s="39"/>
+      <c r="I5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!I$1)))</f>
         <v xml:space="preserve">Consumption of fixed capital </v>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="20" t="str">
+      <c r="J5" s="39"/>
+      <c r="K5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!K$1)))</f>
         <v>Taxes on production and imports</v>
       </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="20" t="str">
+      <c r="L5" s="39"/>
+      <c r="M5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!M$1)))</f>
         <v>Subsidies</v>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="31" t="str">
+      <c r="N5" s="39"/>
+      <c r="O5" s="25" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(O$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(O$1))))</f>
         <v/>
       </c>
-      <c r="P5" s="32" t="e">
+      <c r="P5" s="26" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A6)-1,COLUMN(P$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A6)-1,COLUMN(P$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q5" s="20" t="str">
+      <c r="Q5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Q$1)))</f>
         <v>Compensation of employees received from the rest of the world</v>
       </c>
-      <c r="R5" s="22"/>
-      <c r="S5" s="20" t="str">
+      <c r="R5" s="39"/>
+      <c r="S5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!S$1)))</f>
         <v>Compensation of employees paid to the rest of the world</v>
       </c>
-      <c r="T5" s="22"/>
-      <c r="U5" s="20" t="str">
+      <c r="T5" s="39"/>
+      <c r="U5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!U$1)))</f>
         <v>Taxes on production and imports received from the rest of the world</v>
       </c>
-      <c r="V5" s="22"/>
-      <c r="W5" s="20" t="str">
+      <c r="V5" s="39"/>
+      <c r="W5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!W$1)))</f>
         <v>Property income received from the rest of the world</v>
       </c>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="20" t="str">
+      <c r="X5" s="39"/>
+      <c r="Y5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Y$1)))</f>
         <v>Property income paid to the rest of the world</v>
       </c>
-      <c r="Z5" s="22"/>
+      <c r="Z5" s="39"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="11" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1))))</f>
         <v/>
       </c>
-      <c r="AC5" s="20" t="str">
+      <c r="AC5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AC$1)))</f>
         <v>Current transfers receivable from the rest of the world</v>
       </c>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="20" t="str">
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="38" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AE$1)))</f>
         <v>Current transfers payable to the rest of the world</v>
       </c>
-      <c r="AF5" s="22"/>
+      <c r="AF5" s="39"/>
       <c r="AG5" s="4" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AG$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AG$1))))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="33" t="e">
+      <c r="C6" s="32"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="27" t="e">
         <f ca="1">INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW(#REF!)-1,COLUMN(#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="24"/>
-    </row>
-    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P6" s="28"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="41"/>
+    </row>
+    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="24"/>
-    </row>
-    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="32"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="41"/>
+    </row>
+    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="24"/>
-    </row>
-    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="32"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="41"/>
+    </row>
+    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="24"/>
-    </row>
-    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="32"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="41"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="41"/>
+    </row>
+    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="26"/>
-    </row>
-    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="33"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="42"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="42"/>
+      <c r="AF10" s="43"/>
+    </row>
+    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42" t="s">
+      <c r="D11" s="35"/>
+      <c r="E11" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="42" t="s">
+      <c r="F11" s="37"/>
+      <c r="G11" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42" t="s">
+      <c r="H11" s="37"/>
+      <c r="I11" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="42" t="s">
+      <c r="J11" s="37"/>
+      <c r="K11" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="42" t="s">
+      <c r="L11" s="37"/>
+      <c r="M11" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="43"/>
-      <c r="O11" s="27" t="s">
+      <c r="N11" s="37"/>
+      <c r="O11" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="27" t="s">
+      <c r="P11" s="22"/>
+      <c r="Q11" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="28"/>
-      <c r="S11" s="27" t="s">
+      <c r="R11" s="22"/>
+      <c r="S11" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27" t="s">
+      <c r="T11" s="22"/>
+      <c r="U11" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="V11" s="28"/>
-      <c r="W11" s="27" t="s">
+      <c r="V11" s="22"/>
+      <c r="W11" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="27" t="s">
+      <c r="X11" s="22"/>
+      <c r="Y11" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="27" t="s">
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="27" t="s">
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="27" t="s">
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="AF11" s="28"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AF11" s="22"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <v>1980</v>
       </c>
@@ -18878,7 +18865,7 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="19"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>1981</v>
       </c>
@@ -18920,7 +18907,7 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="19"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>1982</v>
       </c>
@@ -18962,7 +18949,7 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="19"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>1983</v>
       </c>
@@ -19004,7 +18991,7 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="19"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>1984</v>
       </c>
@@ -19046,7 +19033,7 @@
       <c r="AG16" s="18"/>
       <c r="AH16" s="19"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>1985</v>
       </c>
@@ -19088,7 +19075,7 @@
       <c r="AG17" s="18"/>
       <c r="AH17" s="19"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>1986</v>
       </c>
@@ -19130,7 +19117,7 @@
       <c r="AG18" s="18"/>
       <c r="AH18" s="19"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
         <v>1987</v>
       </c>
@@ -19172,7 +19159,7 @@
       <c r="AG19" s="18"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
         <v>1988</v>
       </c>
@@ -19214,7 +19201,7 @@
       <c r="AG20" s="18"/>
       <c r="AH20" s="19"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <v>1989</v>
       </c>
@@ -19256,7 +19243,7 @@
       <c r="AG21" s="18"/>
       <c r="AH21" s="19"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>1990</v>
       </c>
@@ -19326,7 +19313,7 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="19"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <v>1991</v>
       </c>
@@ -19424,7 +19411,7 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="19"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <v>1992</v>
       </c>
@@ -19522,7 +19509,7 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="19"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>1993</v>
       </c>
@@ -19620,7 +19607,7 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="19"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>1994</v>
       </c>
@@ -19718,7 +19705,7 @@
       <c r="AG26" s="18"/>
       <c r="AH26" s="19"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>1995</v>
       </c>
@@ -19816,7 +19803,7 @@
       <c r="AG27" s="18"/>
       <c r="AH27" s="19"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <v>1996</v>
       </c>
@@ -19914,7 +19901,7 @@
       <c r="AG28" s="18"/>
       <c r="AH28" s="19"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A29" s="17">
         <v>1997</v>
       </c>
@@ -20012,7 +19999,7 @@
       <c r="AG29" s="18"/>
       <c r="AH29" s="19"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A30" s="17">
         <v>1998</v>
       </c>
@@ -20110,7 +20097,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="19"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A31" s="17">
         <v>1999</v>
       </c>
@@ -20208,7 +20195,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="19"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A32" s="17">
         <v>2000</v>
       </c>
@@ -20306,7 +20293,7 @@
       <c r="AG32" s="18"/>
       <c r="AH32" s="19"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33" s="17">
         <v>2001</v>
       </c>
@@ -20404,7 +20391,7 @@
       <c r="AG33" s="18"/>
       <c r="AH33" s="19"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A34" s="17">
         <v>2002</v>
       </c>
@@ -20502,7 +20489,7 @@
       <c r="AG34" s="18"/>
       <c r="AH34" s="19"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A35" s="17">
         <v>2003</v>
       </c>
@@ -20600,7 +20587,7 @@
       <c r="AG35" s="18"/>
       <c r="AH35" s="19"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A36" s="17">
         <v>2004</v>
       </c>
@@ -20698,7 +20685,7 @@
       <c r="AG36" s="18"/>
       <c r="AH36" s="19"/>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A37" s="17">
         <v>2005</v>
       </c>
@@ -20796,7 +20783,7 @@
       <c r="AG37" s="18"/>
       <c r="AH37" s="19"/>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>2006</v>
       </c>
@@ -20894,7 +20881,7 @@
       <c r="AG38" s="18"/>
       <c r="AH38" s="19"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <v>2007</v>
       </c>
@@ -20992,7 +20979,7 @@
       <c r="AG39" s="18"/>
       <c r="AH39" s="19"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A40" s="17">
         <v>2008</v>
       </c>
@@ -21090,7 +21077,7 @@
       <c r="AG40" s="18"/>
       <c r="AH40" s="19"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A41" s="17">
         <v>2009</v>
       </c>
@@ -21188,7 +21175,7 @@
       <c r="AG41" s="18"/>
       <c r="AH41" s="19"/>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A42" s="17">
         <v>2010</v>
       </c>
@@ -21286,7 +21273,7 @@
       <c r="AG42" s="18"/>
       <c r="AH42" s="19"/>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A43" s="17">
         <v>2011</v>
       </c>
@@ -21384,7 +21371,7 @@
       <c r="AG43" s="18"/>
       <c r="AH43" s="19"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A44" s="17">
         <v>2012</v>
       </c>
@@ -21482,7 +21469,7 @@
       <c r="AG44" s="18"/>
       <c r="AH44" s="19"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A45" s="17">
         <v>2013</v>
       </c>
@@ -21580,7 +21567,7 @@
       <c r="AG45" s="18"/>
       <c r="AH45" s="19"/>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A46" s="17">
         <v>2014</v>
       </c>
@@ -21678,7 +21665,7 @@
       <c r="AG46" s="18"/>
       <c r="AH46" s="19"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A47" s="17">
         <v>2015</v>
       </c>
@@ -21776,7 +21763,7 @@
       <c r="AG47" s="18"/>
       <c r="AH47" s="19"/>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A48" s="17">
         <v>2016</v>
       </c>
@@ -21874,7 +21861,7 @@
       <c r="AG48" s="18"/>
       <c r="AH48" s="19"/>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A49" s="17">
         <v>2017</v>
       </c>
@@ -21972,7 +21959,7 @@
       <c r="AG49" s="18"/>
       <c r="AH49" s="19"/>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A50" s="17">
         <v>2018</v>
       </c>
@@ -22070,7 +22057,7 @@
       <c r="AG50" s="18"/>
       <c r="AH50" s="19"/>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A51" s="17">
         <v>2019</v>
       </c>
@@ -22168,7 +22155,7 @@
       <c r="AG51" s="18"/>
       <c r="AH51" s="19"/>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A52" s="17">
         <v>2020</v>
       </c>
@@ -22266,7 +22253,7 @@
       <c r="AG52" s="18"/>
       <c r="AH52" s="19"/>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A53" s="17">
         <v>2021</v>
       </c>
@@ -22364,7 +22351,7 @@
       <c r="AG53" s="18"/>
       <c r="AH53" s="19"/>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A54" s="17">
         <v>2022</v>
       </c>
@@ -22462,7 +22449,7 @@
       <c r="AG54" s="18"/>
       <c r="AH54" s="19"/>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A55" s="17">
         <v>2023</v>
       </c>
@@ -22560,7 +22547,7 @@
       <c r="AG55" s="18"/>
       <c r="AH55" s="19"/>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A56" s="17">
         <v>2024</v>
       </c>
@@ -22658,7 +22645,7 @@
       <c r="AG56" s="18"/>
       <c r="AH56" s="19"/>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="18"/>
@@ -22697,26 +22684,6 @@
   </sheetData>
   <sheetProtection password="DD0B" sheet="1"/>
   <mergeCells count="33">
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AA6:AB10"/>
-    <mergeCell ref="AE5:AF10"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="AC5:AD10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Q5:R10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="U5:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
     <mergeCell ref="C4:N4"/>
     <mergeCell ref="O4:Z4"/>
     <mergeCell ref="AA4:AF4"/>
@@ -22730,6 +22697,26 @@
     <mergeCell ref="S5:T10"/>
     <mergeCell ref="W5:X10"/>
     <mergeCell ref="Y5:Z10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Q5:R10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="U5:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AA6:AB10"/>
+    <mergeCell ref="AE5:AF10"/>
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="AC5:AD10"/>
+    <mergeCell ref="AA11:AB11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -22739,16 +22726,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E256F5-6106-45E8-A2D5-7B2125FC6023}">
   <dimension ref="A1:AI57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="32" width="9.77734375" customWidth="1"/>
+    <col min="3" max="32" width="9.75" customWidth="1"/>
     <col min="33" max="33" width="15.6640625" customWidth="1"/>
-    <col min="34" max="34" width="9.77734375" customWidth="1"/>
+    <col min="34" max="34" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
@@ -22783,7 +22770,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="10"/>
     </row>
-    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -22818,7 +22805,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="9"/>
@@ -22850,407 +22837,407 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="21" t="e">
+      <c r="D4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="E4" s="21" t="e">
+      <c r="E4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="F4" s="21" t="e">
+      <c r="F4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="G4" s="21" t="e">
+      <c r="G4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="H4" s="21" t="e">
+      <c r="H4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="I4" s="21" t="e">
+      <c r="I4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="J4" s="21" t="e">
+      <c r="J4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="K4" s="21" t="e">
+      <c r="K4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="L4" s="21" t="e">
+      <c r="L4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="M4" s="21" t="e">
+      <c r="M4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="N4" s="22" t="e">
+      <c r="N4" s="39" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="21" t="e">
+      <c r="P4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q4" s="21" t="e">
+      <c r="Q4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="R4" s="21" t="e">
+      <c r="R4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="S4" s="21" t="e">
+      <c r="S4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="T4" s="21" t="e">
+      <c r="T4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21" t="e">
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="X4" s="21" t="e">
+      <c r="X4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Y4" s="21" t="e">
+      <c r="Y4" s="44" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Z4" s="22" t="e">
+      <c r="Z4" s="39" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="AA4" s="20" t="s">
+      <c r="AA4" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="21"/>
-      <c r="AF4" s="22"/>
-    </row>
-    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="39"/>
+    </row>
+    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="20" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="20" t="s">
+      <c r="F5" s="39"/>
+      <c r="G5" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="20" t="s">
+      <c r="H5" s="39"/>
+      <c r="I5" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="20" t="s">
+      <c r="J5" s="39"/>
+      <c r="K5" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="20" t="s">
+      <c r="L5" s="39"/>
+      <c r="M5" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="31" t="s">
+      <c r="N5" s="39"/>
+      <c r="O5" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="P5" s="32" t="e">
+      <c r="P5" s="26" t="e">
         <v>#REF!</v>
       </c>
-      <c r="Q5" s="20" t="s">
+      <c r="Q5" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="R5" s="22"/>
-      <c r="S5" s="20" t="s">
+      <c r="R5" s="39"/>
+      <c r="S5" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="T5" s="22"/>
-      <c r="U5" s="20" t="s">
+      <c r="T5" s="39"/>
+      <c r="U5" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="V5" s="22"/>
-      <c r="W5" s="20" t="s">
+      <c r="V5" s="39"/>
+      <c r="W5" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="20" t="s">
+      <c r="X5" s="39"/>
+      <c r="Y5" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="Z5" s="22"/>
+      <c r="Z5" s="39"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="AC5" s="20" t="s">
+      <c r="AC5" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="20" t="s">
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="AF5" s="22"/>
+      <c r="AF5" s="39"/>
       <c r="AG5" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="33" t="e">
+      <c r="C6" s="32"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="27" t="e">
         <v>#REF!</v>
       </c>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="24"/>
-    </row>
-    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P6" s="28"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="41"/>
+    </row>
+    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="24"/>
-    </row>
-    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="32"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="41"/>
+    </row>
+    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="24"/>
-    </row>
-    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="32"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="41"/>
+    </row>
+    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="24"/>
-    </row>
-    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="32"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="41"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="41"/>
+    </row>
+    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="26"/>
-    </row>
-    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="33"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="42"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="42"/>
+      <c r="AF10" s="43"/>
+    </row>
+    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42" t="s">
+      <c r="D11" s="35"/>
+      <c r="E11" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="42" t="s">
+      <c r="F11" s="37"/>
+      <c r="G11" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42" t="s">
+      <c r="H11" s="37"/>
+      <c r="I11" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="42" t="s">
+      <c r="J11" s="37"/>
+      <c r="K11" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="42" t="s">
+      <c r="L11" s="37"/>
+      <c r="M11" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="43"/>
-      <c r="O11" s="27" t="s">
+      <c r="N11" s="37"/>
+      <c r="O11" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="27" t="s">
+      <c r="P11" s="22"/>
+      <c r="Q11" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="28"/>
-      <c r="S11" s="27" t="s">
+      <c r="R11" s="22"/>
+      <c r="S11" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27" t="s">
+      <c r="T11" s="22"/>
+      <c r="U11" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="V11" s="28"/>
-      <c r="W11" s="27" t="s">
+      <c r="V11" s="22"/>
+      <c r="W11" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="27" t="s">
+      <c r="X11" s="22"/>
+      <c r="Y11" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="27" t="s">
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="27" t="s">
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="27" t="s">
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="AF11" s="28"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AF11" s="22"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <v>1980</v>
       </c>
@@ -23290,7 +23277,7 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="19"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>1981</v>
       </c>
@@ -23332,7 +23319,7 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="19"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>1982</v>
       </c>
@@ -23374,7 +23361,7 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="19"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>1983</v>
       </c>
@@ -23416,7 +23403,7 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="19"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>1984</v>
       </c>
@@ -23458,7 +23445,7 @@
       <c r="AG16" s="18"/>
       <c r="AH16" s="19"/>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>1985</v>
       </c>
@@ -23500,7 +23487,7 @@
       <c r="AG17" s="18"/>
       <c r="AH17" s="19"/>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>1986</v>
       </c>
@@ -23542,7 +23529,7 @@
       <c r="AG18" s="18"/>
       <c r="AH18" s="19"/>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
         <v>1987</v>
       </c>
@@ -23584,7 +23571,7 @@
       <c r="AG19" s="18"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
         <v>1988</v>
       </c>
@@ -23626,7 +23613,7 @@
       <c r="AG20" s="18"/>
       <c r="AH20" s="19"/>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <v>1989</v>
       </c>
@@ -23672,7 +23659,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>1990</v>
       </c>
@@ -23739,11 +23726,11 @@
         <v>17312.918268793899</v>
       </c>
       <c r="AF22" s="19"/>
-      <c r="AG22" s="44">
+      <c r="AG22">
         <f>E22/C22</f>
         <v>0.54362766833129506</v>
       </c>
-      <c r="AH22" s="45">
+      <c r="AH22" s="20">
         <f>(G22+I22+K22+M22)/C22</f>
         <v>0.45637233166870522</v>
       </c>
@@ -23752,7 +23739,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <v>1991</v>
       </c>
@@ -23847,11 +23834,11 @@
       <c r="AF23" s="19">
         <v>7.4875073320421107E-2</v>
       </c>
-      <c r="AG23" s="44">
+      <c r="AG23">
         <f t="shared" ref="AG23:AG56" si="0">E23/C23</f>
         <v>0.55883921378893187</v>
       </c>
-      <c r="AH23" s="45">
+      <c r="AH23" s="20">
         <f t="shared" ref="AH23:AH56" si="1">(G23+I23+K23+M23)/C23</f>
         <v>0.44116078621106825</v>
       </c>
@@ -23860,7 +23847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <v>1992</v>
       </c>
@@ -23955,11 +23942,11 @@
       <c r="AF24" s="19">
         <v>0.24955454473709901</v>
       </c>
-      <c r="AG24" s="44">
+      <c r="AG24">
         <f t="shared" si="0"/>
         <v>0.56498665932484693</v>
       </c>
-      <c r="AH24" s="45">
+      <c r="AH24" s="20">
         <f t="shared" si="1"/>
         <v>0.43501334067515252</v>
       </c>
@@ -23968,7 +23955,7 @@
         <v>0.99999999999999944</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>1993</v>
       </c>
@@ -24063,11 +24050,11 @@
       <c r="AF25" s="19">
         <v>7.1149651773010402E-3</v>
       </c>
-      <c r="AG25" s="44">
+      <c r="AG25">
         <f t="shared" si="0"/>
         <v>0.55954709909811196</v>
       </c>
-      <c r="AH25" s="45">
+      <c r="AH25" s="20">
         <f t="shared" si="1"/>
         <v>0.44045290090188793</v>
       </c>
@@ -24076,7 +24063,7 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>1994</v>
       </c>
@@ -24171,11 +24158,11 @@
       <c r="AF26" s="19">
         <v>-6.69938231939393E-3</v>
       </c>
-      <c r="AG26" s="44">
+      <c r="AG26">
         <f t="shared" si="0"/>
         <v>0.54929658733945108</v>
       </c>
-      <c r="AH26" s="45">
+      <c r="AH26" s="20">
         <f t="shared" si="1"/>
         <v>0.4507034126605487</v>
       </c>
@@ -24184,7 +24171,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>1995</v>
       </c>
@@ -24279,11 +24266,11 @@
       <c r="AF27" s="19">
         <v>-1.6175566754619699E-2</v>
       </c>
-      <c r="AG27" s="44">
+      <c r="AG27">
         <f t="shared" si="0"/>
         <v>0.55550080359556098</v>
       </c>
-      <c r="AH27" s="45">
+      <c r="AH27" s="20">
         <f t="shared" si="1"/>
         <v>0.4444991964044388</v>
       </c>
@@ -24292,7 +24279,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <v>1996</v>
       </c>
@@ -24387,11 +24374,11 @@
       <c r="AF28" s="19">
         <v>6.9898300119236798E-2</v>
       </c>
-      <c r="AG28" s="44">
+      <c r="AG28">
         <f t="shared" si="0"/>
         <v>0.55245045019612005</v>
       </c>
-      <c r="AH28" s="45">
+      <c r="AH28" s="20">
         <f t="shared" si="1"/>
         <v>0.4475495498038804</v>
       </c>
@@ -24400,7 +24387,7 @@
         <v>1.0000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="17">
         <v>1997</v>
       </c>
@@ -24495,11 +24482,11 @@
       <c r="AF29" s="19">
         <v>-7.3386958534955599E-3</v>
       </c>
-      <c r="AG29" s="44">
+      <c r="AG29">
         <f t="shared" si="0"/>
         <v>0.55013061121946683</v>
       </c>
-      <c r="AH29" s="45">
+      <c r="AH29" s="20">
         <f t="shared" si="1"/>
         <v>0.44986938878053406</v>
       </c>
@@ -24508,7 +24495,7 @@
         <v>1.0000000000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="17">
         <v>1998</v>
       </c>
@@ -24603,11 +24590,11 @@
       <c r="AF30" s="19">
         <v>8.6635046379991906E-2</v>
       </c>
-      <c r="AG30" s="44">
+      <c r="AG30">
         <f t="shared" si="0"/>
         <v>0.5457994772779805</v>
       </c>
-      <c r="AH30" s="45">
+      <c r="AH30" s="20">
         <f t="shared" si="1"/>
         <v>0.45420052272201944</v>
       </c>
@@ -24616,7 +24603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="17">
         <v>1999</v>
       </c>
@@ -24711,11 +24698,11 @@
       <c r="AF31" s="19">
         <v>2.73056363132218E-3</v>
       </c>
-      <c r="AG31" s="44">
+      <c r="AG31">
         <f t="shared" si="0"/>
         <v>0.5461087673365399</v>
       </c>
-      <c r="AH31" s="45">
+      <c r="AH31" s="20">
         <f t="shared" si="1"/>
         <v>0.4538912326634601</v>
       </c>
@@ -24724,7 +24711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="17">
         <v>2000</v>
       </c>
@@ -24819,11 +24806,11 @@
       <c r="AF32" s="19">
         <v>0.15262642851250599</v>
       </c>
-      <c r="AG32" s="44">
+      <c r="AG32">
         <f t="shared" si="0"/>
         <v>0.54040470740615842</v>
       </c>
-      <c r="AH32" s="45">
+      <c r="AH32" s="20">
         <f t="shared" si="1"/>
         <v>0.4595952925938423</v>
       </c>
@@ -24832,7 +24819,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="17">
         <v>2001</v>
       </c>
@@ -24927,11 +24914,11 @@
       <c r="AF33" s="19">
         <v>0.12768575627588999</v>
       </c>
-      <c r="AG33" s="44">
+      <c r="AG33">
         <f t="shared" si="0"/>
         <v>0.55608182667152495</v>
       </c>
-      <c r="AH33" s="45">
+      <c r="AH33" s="20">
         <f t="shared" si="1"/>
         <v>0.44391817332847583</v>
       </c>
@@ -24940,7 +24927,7 @@
         <v>1.0000000000000009</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="17">
         <v>2002</v>
       </c>
@@ -25035,11 +25022,11 @@
       <c r="AF34" s="19">
         <v>0.25525031376465401</v>
       </c>
-      <c r="AG34" s="44">
+      <c r="AG34">
         <f t="shared" si="0"/>
         <v>0.5723146395705383</v>
       </c>
-      <c r="AH34" s="45">
+      <c r="AH34" s="20">
         <f t="shared" si="1"/>
         <v>0.42768536042946292</v>
       </c>
@@ -25048,7 +25035,7 @@
         <v>1.0000000000000013</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" s="17">
         <v>2003</v>
       </c>
@@ -25143,11 +25130,11 @@
       <c r="AF35" s="19">
         <v>-0.29557152641843598</v>
       </c>
-      <c r="AG35" s="44">
+      <c r="AG35">
         <f t="shared" si="0"/>
         <v>0.56927396844659717</v>
       </c>
-      <c r="AH35" s="45">
+      <c r="AH35" s="20">
         <f t="shared" si="1"/>
         <v>0.43072603155340333</v>
       </c>
@@ -25156,7 +25143,7 @@
         <v>1.0000000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" s="17">
         <v>2004</v>
       </c>
@@ -25251,11 +25238,11 @@
       <c r="AF36" s="19">
         <v>0.18734573803871399</v>
       </c>
-      <c r="AG36" s="44">
+      <c r="AG36">
         <f t="shared" si="0"/>
         <v>0.55765120478446617</v>
       </c>
-      <c r="AH36" s="45">
+      <c r="AH36" s="20">
         <f t="shared" si="1"/>
         <v>0.44234879521553438</v>
       </c>
@@ -25264,7 +25251,7 @@
         <v>1.0000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" s="17">
         <v>2005</v>
       </c>
@@ -25359,11 +25346,11 @@
       <c r="AF37" s="19">
         <v>2.01190793139037E-2</v>
       </c>
-      <c r="AG37" s="44">
+      <c r="AG37">
         <f t="shared" si="0"/>
         <v>0.55291058531557136</v>
       </c>
-      <c r="AH37" s="45">
+      <c r="AH37" s="20">
         <f t="shared" si="1"/>
         <v>0.44708941468442931</v>
       </c>
@@ -25372,7 +25359,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>2006</v>
       </c>
@@ -25467,11 +25454,11 @@
       <c r="AF38" s="19">
         <v>3.8732197131580798E-2</v>
       </c>
-      <c r="AG38" s="44">
+      <c r="AG38">
         <f t="shared" si="0"/>
         <v>0.54007336047454868</v>
       </c>
-      <c r="AH38" s="45">
+      <c r="AH38" s="20">
         <f t="shared" si="1"/>
         <v>0.45992663952545132</v>
       </c>
@@ -25480,7 +25467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <v>2007</v>
       </c>
@@ -25575,11 +25562,11 @@
       <c r="AF39" s="19">
         <v>3.0458278383337801E-2</v>
       </c>
-      <c r="AG39" s="44">
+      <c r="AG39">
         <f t="shared" si="0"/>
         <v>0.53448513024856936</v>
       </c>
-      <c r="AH39" s="45">
+      <c r="AH39" s="20">
         <f t="shared" si="1"/>
         <v>0.46551486975143053</v>
       </c>
@@ -25588,7 +25575,7 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" s="17">
         <v>2008</v>
       </c>
@@ -25683,11 +25670,11 @@
       <c r="AF40" s="19">
         <v>0.29705770026179801</v>
       </c>
-      <c r="AG40" s="44">
+      <c r="AG40">
         <f t="shared" si="0"/>
         <v>0.53958797034172734</v>
       </c>
-      <c r="AH40" s="45">
+      <c r="AH40" s="20">
         <f t="shared" si="1"/>
         <v>0.46041202965827271</v>
       </c>
@@ -25696,7 +25683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="17">
         <v>2009</v>
       </c>
@@ -25791,11 +25778,11 @@
       <c r="AF41" s="19">
         <v>-0.11852281162664401</v>
       </c>
-      <c r="AG41" s="44">
+      <c r="AG41">
         <f t="shared" si="0"/>
         <v>0.56028987163943378</v>
       </c>
-      <c r="AH41" s="45">
+      <c r="AH41" s="20">
         <f t="shared" si="1"/>
         <v>0.43971012836056622</v>
       </c>
@@ -25804,7 +25791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="17">
         <v>2010</v>
       </c>
@@ -25899,11 +25886,11 @@
       <c r="AF42" s="19">
         <v>-4.2376194981251697E-2</v>
       </c>
-      <c r="AG42" s="44">
+      <c r="AG42">
         <f t="shared" si="0"/>
         <v>0.5448442619083077</v>
       </c>
-      <c r="AH42" s="45">
+      <c r="AH42" s="20">
         <f t="shared" si="1"/>
         <v>0.45515573809169241</v>
       </c>
@@ -25912,7 +25899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="17">
         <v>2011</v>
       </c>
@@ -26007,11 +25994,11 @@
       <c r="AF43" s="19">
         <v>-2.5299128360893201E-2</v>
       </c>
-      <c r="AG43" s="44">
+      <c r="AG43">
         <f t="shared" si="0"/>
         <v>0.55706182039455077</v>
       </c>
-      <c r="AH43" s="45">
+      <c r="AH43" s="20">
         <f t="shared" si="1"/>
         <v>0.4429381796054494</v>
       </c>
@@ -26020,7 +26007,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" s="17">
         <v>2012</v>
       </c>
@@ -26115,11 +26102,11 @@
       <c r="AF44" s="19">
         <v>0.14303996056461801</v>
       </c>
-      <c r="AG44" s="44">
+      <c r="AG44">
         <f t="shared" si="0"/>
         <v>0.56385030427718452</v>
       </c>
-      <c r="AH44" s="45">
+      <c r="AH44" s="20">
         <f t="shared" si="1"/>
         <v>0.43614969572281703</v>
       </c>
@@ -26128,7 +26115,7 @@
         <v>1.0000000000000016</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" s="17">
         <v>2013</v>
       </c>
@@ -26223,11 +26210,11 @@
       <c r="AF45" s="19">
         <v>4.1260601852225201E-2</v>
       </c>
-      <c r="AG45" s="44">
+      <c r="AG45">
         <f t="shared" si="0"/>
         <v>0.56641130563568065</v>
       </c>
-      <c r="AH45" s="45">
+      <c r="AH45" s="20">
         <f t="shared" si="1"/>
         <v>0.43358869436431935</v>
       </c>
@@ -26236,7 +26223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="17">
         <v>2014</v>
       </c>
@@ -26331,11 +26318,11 @@
       <c r="AF46" s="19">
         <v>0.119148503483261</v>
       </c>
-      <c r="AG46" s="44">
+      <c r="AG46">
         <f t="shared" si="0"/>
         <v>0.5647958393070831</v>
       </c>
-      <c r="AH46" s="45">
+      <c r="AH46" s="20">
         <f t="shared" si="1"/>
         <v>0.4352041606929184</v>
       </c>
@@ -26344,7 +26331,7 @@
         <v>1.0000000000000016</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" s="17">
         <v>2015</v>
       </c>
@@ -26439,11 +26426,11 @@
       <c r="AF47" s="19">
         <v>-3.5813805762925602E-2</v>
       </c>
-      <c r="AG47" s="44">
+      <c r="AG47">
         <f t="shared" si="0"/>
         <v>0.57479325766048461</v>
       </c>
-      <c r="AH47" s="45">
+      <c r="AH47" s="20">
         <f t="shared" si="1"/>
         <v>0.42520674233951528</v>
       </c>
@@ -26452,7 +26439,7 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" s="17">
         <v>2016</v>
       </c>
@@ -26547,11 +26534,11 @@
       <c r="AF48" s="19">
         <v>8.7178245199122498E-2</v>
       </c>
-      <c r="AG48" s="44">
+      <c r="AG48">
         <f t="shared" si="0"/>
         <v>0.5741337233099183</v>
       </c>
-      <c r="AH48" s="45">
+      <c r="AH48" s="20">
         <f t="shared" si="1"/>
         <v>0.42586627669008176</v>
       </c>
@@ -26560,7 +26547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="17">
         <v>2017</v>
       </c>
@@ -26655,11 +26642,11 @@
       <c r="AF49" s="19">
         <v>0.11619037143677199</v>
       </c>
-      <c r="AG49" s="44">
+      <c r="AG49">
         <f t="shared" si="0"/>
         <v>0.5761350665822601</v>
       </c>
-      <c r="AH49" s="45">
+      <c r="AH49" s="20">
         <f t="shared" si="1"/>
         <v>0.42386493341773984</v>
       </c>
@@ -26668,7 +26655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" s="17">
         <v>2018</v>
       </c>
@@ -26763,11 +26750,11 @@
       <c r="AF50" s="19">
         <v>-0.10713623130042001</v>
       </c>
-      <c r="AG50" s="44">
+      <c r="AG50">
         <f t="shared" si="0"/>
         <v>0.56569594023113634</v>
       </c>
-      <c r="AH50" s="45">
+      <c r="AH50" s="20">
         <f t="shared" si="1"/>
         <v>0.43430405976886371</v>
       </c>
@@ -26776,7 +26763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="17">
         <v>2019</v>
       </c>
@@ -26871,11 +26858,11 @@
       <c r="AF51" s="19">
         <v>5.4050951534626399E-2</v>
       </c>
-      <c r="AG51" s="44">
+      <c r="AG51">
         <f t="shared" si="0"/>
         <v>0.57623256621002805</v>
       </c>
-      <c r="AH51" s="45">
+      <c r="AH51" s="20">
         <f t="shared" si="1"/>
         <v>0.42376743378997195</v>
       </c>
@@ -26884,7 +26871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" s="17">
         <v>2020</v>
       </c>
@@ -26979,11 +26966,11 @@
       <c r="AF52" s="19">
         <v>3.77702936276028E-2</v>
       </c>
-      <c r="AG52" s="44">
+      <c r="AG52">
         <f t="shared" si="0"/>
         <v>0.58468068902239723</v>
       </c>
-      <c r="AH52" s="45">
+      <c r="AH52" s="20">
         <f t="shared" si="1"/>
         <v>0.41531931097760288</v>
       </c>
@@ -26992,7 +26979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="17">
         <v>2021</v>
       </c>
@@ -27087,11 +27074,11 @@
       <c r="AF53" s="19">
         <v>1.30188363405288E-2</v>
       </c>
-      <c r="AG53" s="44">
+      <c r="AG53">
         <f t="shared" si="0"/>
         <v>0.5650197531115122</v>
       </c>
-      <c r="AH53" s="45">
+      <c r="AH53" s="20">
         <f t="shared" si="1"/>
         <v>0.4349802468884878</v>
       </c>
@@ -27100,7 +27087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="17">
         <v>2022</v>
       </c>
@@ -27195,11 +27182,11 @@
       <c r="AF54" s="19">
         <v>9.6440825675935704E-2</v>
       </c>
-      <c r="AG54" s="44">
+      <c r="AG54">
         <f t="shared" si="0"/>
         <v>0.56079930824898161</v>
       </c>
-      <c r="AH54" s="45">
+      <c r="AH54" s="20">
         <f t="shared" si="1"/>
         <v>0.43920069175101839</v>
       </c>
@@ -27208,7 +27195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="17">
         <v>2023</v>
       </c>
@@ -27303,11 +27290,11 @@
       <c r="AF55" s="19">
         <v>8.1613641782465995E-2</v>
       </c>
-      <c r="AG55" s="44">
+      <c r="AG55">
         <f t="shared" si="0"/>
         <v>0.57133007939099212</v>
       </c>
-      <c r="AH55" s="45">
+      <c r="AH55" s="20">
         <f t="shared" si="1"/>
         <v>0.4286699206090091</v>
       </c>
@@ -27316,7 +27303,7 @@
         <v>1.0000000000000013</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" s="17">
         <v>2024</v>
       </c>
@@ -27411,11 +27398,11 @@
       <c r="AF56" s="19">
         <v>8.7701749291093006E-2</v>
       </c>
-      <c r="AG56" s="44">
+      <c r="AG56">
         <f t="shared" si="0"/>
         <v>0.57686212254094515</v>
       </c>
-      <c r="AH56" s="45">
+      <c r="AH56" s="20">
         <f t="shared" si="1"/>
         <v>0.42313787745905473</v>
       </c>
@@ -27424,7 +27411,7 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="18"/>
@@ -27462,13 +27449,16 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="O4:Z4"/>
+    <mergeCell ref="AA4:AF4"/>
+    <mergeCell ref="C5:D10"/>
+    <mergeCell ref="E5:F10"/>
+    <mergeCell ref="G5:H10"/>
+    <mergeCell ref="I5:J10"/>
+    <mergeCell ref="K5:L10"/>
+    <mergeCell ref="M5:N10"/>
+    <mergeCell ref="O5:P10"/>
     <mergeCell ref="AE5:AF10"/>
     <mergeCell ref="AA6:AB10"/>
     <mergeCell ref="C11:D11"/>
@@ -27485,16 +27475,13 @@
     <mergeCell ref="W5:X10"/>
     <mergeCell ref="Y5:Z10"/>
     <mergeCell ref="AC5:AD10"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="O4:Z4"/>
-    <mergeCell ref="AA4:AF4"/>
-    <mergeCell ref="C5:D10"/>
-    <mergeCell ref="E5:F10"/>
-    <mergeCell ref="G5:H10"/>
-    <mergeCell ref="I5:J10"/>
-    <mergeCell ref="K5:L10"/>
-    <mergeCell ref="M5:N10"/>
-    <mergeCell ref="O5:P10"/>
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AD11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27504,9 +27491,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Table01"/>
   <dimension ref="A1:AR57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
@@ -27514,27 +27501,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>85</v>
       </c>
@@ -27542,7 +27529,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>77</v>
       </c>
@@ -27550,7 +27537,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="15" t="s">
         <v>2</v>
       </c>
@@ -27561,7 +27548,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AO17" s="15" t="s">
         <v>16</v>
       </c>
@@ -27572,7 +27559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="15" t="s">
         <v>27</v>
       </c>
@@ -27610,7 +27597,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M19" s="15" t="s">
         <v>16</v>
       </c>
@@ -27630,7 +27617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>7</v>
       </c>
@@ -27638,12 +27625,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>86</v>
       </c>
@@ -27651,7 +27638,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>78</v>
       </c>
@@ -27659,15 +27646,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
     </row>
-    <row r="27" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
     </row>
-    <row r="28" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="15" t="s">
@@ -27680,7 +27667,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AO29" s="15" t="s">
         <v>16</v>
       </c>
@@ -27691,7 +27678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E30" s="14" t="s">
         <v>39</v>
       </c>
@@ -27736,7 +27723,7 @@
       <c r="AO30" s="14"/>
       <c r="AQ30" s="14"/>
     </row>
-    <row r="31" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K31" s="16"/>
       <c r="M31" s="15" t="s">
         <v>16</v>
@@ -27748,7 +27735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>9</v>
       </c>
@@ -27756,12 +27743,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>81</v>
       </c>
@@ -27769,7 +27756,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>26</v>
       </c>
@@ -27777,15 +27764,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
     </row>
-    <row r="39" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
     </row>
-    <row r="40" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14"/>
       <c r="B40" s="14"/>
       <c r="C40" s="15" t="s">
@@ -27798,7 +27785,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AO41" s="15" t="s">
         <v>16</v>
       </c>
@@ -27809,7 +27796,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E42" s="14" t="s">
         <v>53</v>
       </c>
@@ -27854,7 +27841,7 @@
       <c r="AO42" s="14"/>
       <c r="AQ42" s="14"/>
     </row>
-    <row r="43" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M43" s="15" t="s">
         <v>16</v>
       </c>
@@ -27865,7 +27852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
         <v>12</v>
       </c>
@@ -27873,12 +27860,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15" t="s">
         <v>83</v>
       </c>
@@ -27886,7 +27873,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
         <v>13</v>
       </c>
@@ -27894,15 +27881,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
     </row>
-    <row r="51" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14"/>
       <c r="B51" s="14"/>
     </row>
-    <row r="52" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14"/>
       <c r="B52" s="14"/>
       <c r="C52" s="15" t="s">
@@ -27915,7 +27902,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AO53" s="15" t="s">
         <v>16</v>
       </c>
@@ -27926,7 +27913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E54" s="14" t="s">
         <v>64</v>
       </c>
@@ -27971,7 +27958,7 @@
       <c r="AO54" s="14"/>
       <c r="AQ54" s="14"/>
     </row>
-    <row r="55" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M55" s="15" t="s">
         <v>16</v>
       </c>
@@ -27982,7 +27969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
         <v>14</v>
       </c>

--- a/exercices/pib_suisse_seco_revenu.xlsx
+++ b/exercices/pib_suisse_seco_revenu.xlsx
@@ -1,30 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6278A2FB-3B41-4C61-9E9E-5EBE8DE39713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58CE184-8A3A-48AD-8A59-8721B4BA4F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="swiss_qna" sheetId="22080" r:id="rId1"/>
     <sheet name="nom_q" sheetId="22085" r:id="rId2"/>
     <sheet name="nom_y" sheetId="22089" r:id="rId3"/>
     <sheet name="Feuil1" sheetId="22090" r:id="rId4"/>
-    <sheet name="beschriftung" sheetId="22045" state="veryHidden" r:id="rId5"/>
+    <sheet name="correction exercice 2" sheetId="22091" r:id="rId5"/>
+    <sheet name="beschriftung" sheetId="22045" state="veryHidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="132">
   <si>
     <t>Produit intérieur brut</t>
   </si>
@@ -507,6 +521,39 @@
   <si>
     <t>part profits</t>
   </si>
+  <si>
+    <t>pib</t>
+  </si>
+  <si>
+    <t>compensation_employees</t>
+  </si>
+  <si>
+    <t>net_op_surplus_mixed_income</t>
+  </si>
+  <si>
+    <t>consumption_fixed_capital</t>
+  </si>
+  <si>
+    <t>taxes_on_production</t>
+  </si>
+  <si>
+    <t>subsidies</t>
+  </si>
+  <si>
+    <t>Part des salaires</t>
+  </si>
+  <si>
+    <t>Part des profits</t>
+  </si>
+  <si>
+    <t>Explications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afin de calculer la part des salaires dans la valeur ajoutée, on divise la colonne "compensation des employés", qui comporte les salaires et d'autres revenus versés aux employés, par le pib. Pour calculer la part des profits, il faut diviser la colonne "net operating surplus et mixed income" par le pib. En prenant la somme de la part des salaires et des profits, on remarque qu'elles ne s'additionne pas à 1. En effet, il faut procéder aux calculs suivants pour la colonne net operating surplus:
+- Il faut tout d'abord passer du net au brut en ajoutant la consommation de capital fixe, qui est le montant de profits utilisé pour compenser la dépréciation du capital (usure des machines par exemple). Puis il faut ajouter les taxes sur la production et les importations, qui sont de la valeur "retirée" aux profits, ainsi que soustraire les subventions qui sont de la valeur "addtionnelle" aux profits mais ne provenant pas de la production ayant permis le versement des profits. Attention: dans le tableau fournit par le Seco, les subventions ont déjà le signe négatif, il faut donc additionner pour correctement soustraire.
+En comparant cette la part des salaires que nous avons calculée avec celle de l'AMECO (adjusted wage share), nous remarquons que cette dernière a des valeurs plus grandes, ce qui implique que les salariés reçoivent une plus grande part du revenu national que notre mesure. La raison est que la mesure de la part des salaires de l'AMECO est corrigée pour la part des indépendants/auto-entrepreneurs dans l'emploi, ce qui gonfle la part des salaires
+</t>
+  </si>
 </sst>
 </file>
 
@@ -567,7 +614,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,6 +624,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -807,7 +878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
@@ -863,22 +934,17 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
@@ -886,7 +952,7 @@
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
@@ -894,7 +960,7 @@
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
@@ -902,15 +968,35 @@
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
@@ -930,28 +1016,28 @@
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1035,6 +1121,1069 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Part des salaires dans la valeur ajoutée</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'correction exercice 2'!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Part des salaires</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Feuil1!$A$22:$A$56</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'correction exercice 2'!$K$2:$K$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>0.54362766833129506</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.55883921378893187</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56498665932484693</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55954709909811196</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.54929658733945108</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.55550080359556098</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.55245045019612005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.55013061121946683</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5457994772779805</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.5461087673365399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.54040470740615842</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.55608182667152495</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.5723146395705383</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.56927396844659717</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.55765120478446617</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.55291058531557136</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.54007336047454868</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.53448513024856936</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.53958797034172734</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.56028987163943378</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.5448442619083077</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.55706182039455077</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.56385030427718452</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.56641130563568065</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.5647958393070831</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.57479325766048461</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.5741337233099183</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.5761350665822601</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.56569594023113634</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.57623256621002805</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.58468068902239723</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.5650197531115122</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.56079930824898161</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.57133007939099212</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.57686212254094515</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B63-4266-8970-CE4B2B0F3683}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1192967264"/>
+        <c:axId val="1192967744"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1192967264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1192967744"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1192967744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1192967264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1255,7 +2404,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>1081088</xdr:colOff>
+          <xdr:colOff>1079500</xdr:colOff>
           <xdr:row>25</xdr:row>
           <xdr:rowOff>57150</xdr:rowOff>
         </xdr:to>
@@ -1302,6 +2451,47 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>384175</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93A271B9-69F6-C4E7-D00B-DB40889E7959}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1657,121 +2847,121 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="150.75" customWidth="1"/>
+    <col min="1" max="1" width="150.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
     </row>
-    <row r="2" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="12.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
     </row>
   </sheetData>
@@ -1795,7 +2985,7 @@
                   </from>
                   <to>
                     <xdr:col>0</xdr:col>
-                    <xdr:colOff>1081088</xdr:colOff>
+                    <xdr:colOff>1079500</xdr:colOff>
                     <xdr:row>25</xdr:row>
                     <xdr:rowOff>57150</xdr:rowOff>
                   </to>
@@ -1814,14 +3004,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Table03"/>
   <dimension ref="A1:AH195"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
     <col min="2" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="34" width="9.75" customWidth="1"/>
+    <col min="3" max="34" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A1)-1,COLUMN(beschriftung!A$1)))</f>
         <v>ESA 2010, Quarterly aggregates of Gross Domestic Product, income approach, raw data</v>
@@ -1857,7 +3047,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="10"/>
     </row>
-    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A2)-1,COLUMN(beschriftung!A$1)))</f>
         <v>In Mio. Swiss Francs, at current prices, percentage change to previous year</v>
@@ -1893,7 +3083,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="9"/>
@@ -1925,354 +3115,354 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-      <c r="C4" s="38" t="str">
+      <c r="C4" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!C$1)))</f>
         <v xml:space="preserve">Gross domestic product </v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="38" t="str">
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!O$1)))</f>
         <v>Gross national income</v>
       </c>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="39"/>
-      <c r="AA4" s="38" t="str">
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!AA$1)))</f>
         <v>Disposable income, gross</v>
       </c>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="39"/>
-    </row>
-    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="23"/>
+    </row>
+    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="38" t="str">
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!E$1)))</f>
         <v>Compensation of employees</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="38" t="str">
+      <c r="F5" s="23"/>
+      <c r="G5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!G$1)))</f>
         <v>Net operating surplus and net mixed income</v>
       </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="38" t="str">
+      <c r="H5" s="23"/>
+      <c r="I5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!I$1)))</f>
         <v xml:space="preserve">Consumption of fixed capital </v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="38" t="str">
+      <c r="J5" s="23"/>
+      <c r="K5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!K$1)))</f>
         <v>Taxes on production and imports</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="38" t="str">
+      <c r="L5" s="23"/>
+      <c r="M5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!M$1)))</f>
         <v>Subsidies</v>
       </c>
-      <c r="N5" s="39"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="38" t="str">
+      <c r="N5" s="23"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Q$1)))</f>
         <v>Compensation of employees received from the rest of the world</v>
       </c>
-      <c r="R5" s="39"/>
-      <c r="S5" s="38" t="str">
+      <c r="R5" s="23"/>
+      <c r="S5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!S$1)))</f>
         <v>Compensation of employees paid to the rest of the world</v>
       </c>
-      <c r="T5" s="39"/>
-      <c r="U5" s="38" t="str">
+      <c r="T5" s="23"/>
+      <c r="U5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!U$1)))</f>
         <v>Taxes on production and imports received from the rest of the world</v>
       </c>
-      <c r="V5" s="39"/>
-      <c r="W5" s="38" t="str">
+      <c r="V5" s="23"/>
+      <c r="W5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!W$1)))</f>
         <v>Property income received from the rest of the world</v>
       </c>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="38" t="str">
+      <c r="X5" s="23"/>
+      <c r="Y5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Y$1)))</f>
         <v>Property income paid to the rest of the world</v>
       </c>
-      <c r="Z5" s="39"/>
+      <c r="Z5" s="23"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="11" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1))))</f>
         <v/>
       </c>
-      <c r="AC5" s="38" t="str">
+      <c r="AC5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AC$1)))</f>
         <v>Current transfers receivable from the rest of the world</v>
       </c>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="38" t="str">
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AE$1)))</f>
         <v>Current transfers payable to the rest of the world</v>
       </c>
-      <c r="AF5" s="39"/>
-    </row>
-    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF5" s="23"/>
+    </row>
+    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="41"/>
-    </row>
-    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+    </row>
+    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="41"/>
-    </row>
-    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="31"/>
+    </row>
+    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="41"/>
-      <c r="AE8" s="40"/>
-      <c r="AF8" s="41"/>
-    </row>
-    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="31"/>
+    </row>
+    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="41"/>
-    </row>
-    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+    </row>
+    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="42"/>
-      <c r="AF10" s="43"/>
-    </row>
-    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="33"/>
+    </row>
+    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="I11" s="36" t="s">
+      <c r="H11" s="42"/>
+      <c r="I11" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="37"/>
-      <c r="K11" s="36" t="s">
+      <c r="J11" s="42"/>
+      <c r="K11" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="37"/>
-      <c r="M11" s="36" t="s">
+      <c r="L11" s="42"/>
+      <c r="M11" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="37"/>
-      <c r="O11" s="21" t="s">
+      <c r="N11" s="42"/>
+      <c r="O11" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="21" t="s">
+      <c r="P11" s="44"/>
+      <c r="Q11" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="22"/>
-      <c r="S11" s="21" t="s">
+      <c r="R11" s="44"/>
+      <c r="S11" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="T11" s="22"/>
-      <c r="U11" s="21" t="s">
+      <c r="T11" s="44"/>
+      <c r="U11" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="V11" s="22"/>
-      <c r="W11" s="21" t="s">
+      <c r="V11" s="44"/>
+      <c r="W11" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="21" t="s">
+      <c r="X11" s="44"/>
+      <c r="Y11" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="21" t="s">
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="21" t="s">
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="21" t="s">
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="AF11" s="22"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AF11" s="44"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
         <v>1980</v>
       </c>
@@ -2314,7 +3504,7 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="19"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="17">
         <v>1980</v>
       </c>
@@ -2356,7 +3546,7 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="19"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="17">
         <v>1980</v>
       </c>
@@ -2398,7 +3588,7 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="19"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="17">
         <v>1980</v>
       </c>
@@ -2440,7 +3630,7 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="19"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="17">
         <v>1981</v>
       </c>
@@ -2484,7 +3674,7 @@
       <c r="AG16" s="18"/>
       <c r="AH16" s="19"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" s="17">
         <v>1981</v>
       </c>
@@ -2528,7 +3718,7 @@
       <c r="AG17" s="18"/>
       <c r="AH17" s="19"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" s="17">
         <v>1981</v>
       </c>
@@ -2572,7 +3762,7 @@
       <c r="AG18" s="18"/>
       <c r="AH18" s="19"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" s="17">
         <v>1981</v>
       </c>
@@ -2616,7 +3806,7 @@
       <c r="AG19" s="18"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" s="17">
         <v>1982</v>
       </c>
@@ -2660,7 +3850,7 @@
       <c r="AG20" s="18"/>
       <c r="AH20" s="19"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" s="17">
         <v>1982</v>
       </c>
@@ -2704,7 +3894,7 @@
       <c r="AG21" s="18"/>
       <c r="AH21" s="19"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
         <v>1982</v>
       </c>
@@ -2748,7 +3938,7 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="19"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
         <v>1982</v>
       </c>
@@ -2792,7 +3982,7 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="19"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
         <v>1983</v>
       </c>
@@ -2836,7 +4026,7 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="19"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
         <v>1983</v>
       </c>
@@ -2880,7 +4070,7 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="19"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
         <v>1983</v>
       </c>
@@ -2924,7 +4114,7 @@
       <c r="AG26" s="18"/>
       <c r="AH26" s="19"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" s="17">
         <v>1983</v>
       </c>
@@ -2968,7 +4158,7 @@
       <c r="AG27" s="18"/>
       <c r="AH27" s="19"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" s="17">
         <v>1984</v>
       </c>
@@ -3012,7 +4202,7 @@
       <c r="AG28" s="18"/>
       <c r="AH28" s="19"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" s="17">
         <v>1984</v>
       </c>
@@ -3056,7 +4246,7 @@
       <c r="AG29" s="18"/>
       <c r="AH29" s="19"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" s="17">
         <v>1984</v>
       </c>
@@ -3100,7 +4290,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="19"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" s="17">
         <v>1984</v>
       </c>
@@ -3144,7 +4334,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="19"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" s="17">
         <v>1985</v>
       </c>
@@ -3188,7 +4378,7 @@
       <c r="AG32" s="18"/>
       <c r="AH32" s="19"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" s="17">
         <v>1985</v>
       </c>
@@ -3232,7 +4422,7 @@
       <c r="AG33" s="18"/>
       <c r="AH33" s="19"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" s="17">
         <v>1985</v>
       </c>
@@ -3276,7 +4466,7 @@
       <c r="AG34" s="18"/>
       <c r="AH34" s="19"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" s="17">
         <v>1985</v>
       </c>
@@ -3320,7 +4510,7 @@
       <c r="AG35" s="18"/>
       <c r="AH35" s="19"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" s="17">
         <v>1986</v>
       </c>
@@ -3364,7 +4554,7 @@
       <c r="AG36" s="18"/>
       <c r="AH36" s="19"/>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37" s="17">
         <v>1986</v>
       </c>
@@ -3408,7 +4598,7 @@
       <c r="AG37" s="18"/>
       <c r="AH37" s="19"/>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38" s="17">
         <v>1986</v>
       </c>
@@ -3452,7 +4642,7 @@
       <c r="AG38" s="18"/>
       <c r="AH38" s="19"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39" s="17">
         <v>1986</v>
       </c>
@@ -3496,7 +4686,7 @@
       <c r="AG39" s="18"/>
       <c r="AH39" s="19"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40" s="17">
         <v>1987</v>
       </c>
@@ -3540,7 +4730,7 @@
       <c r="AG40" s="18"/>
       <c r="AH40" s="19"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41" s="17">
         <v>1987</v>
       </c>
@@ -3584,7 +4774,7 @@
       <c r="AG41" s="18"/>
       <c r="AH41" s="19"/>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42" s="17">
         <v>1987</v>
       </c>
@@ -3628,7 +4818,7 @@
       <c r="AG42" s="18"/>
       <c r="AH42" s="19"/>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43" s="17">
         <v>1987</v>
       </c>
@@ -3672,7 +4862,7 @@
       <c r="AG43" s="18"/>
       <c r="AH43" s="19"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44" s="17">
         <v>1988</v>
       </c>
@@ -3716,7 +4906,7 @@
       <c r="AG44" s="18"/>
       <c r="AH44" s="19"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A45" s="17">
         <v>1988</v>
       </c>
@@ -3760,7 +4950,7 @@
       <c r="AG45" s="18"/>
       <c r="AH45" s="19"/>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A46" s="17">
         <v>1988</v>
       </c>
@@ -3804,7 +4994,7 @@
       <c r="AG46" s="18"/>
       <c r="AH46" s="19"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A47" s="17">
         <v>1988</v>
       </c>
@@ -3848,7 +5038,7 @@
       <c r="AG47" s="18"/>
       <c r="AH47" s="19"/>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A48" s="17">
         <v>1989</v>
       </c>
@@ -3892,7 +5082,7 @@
       <c r="AG48" s="18"/>
       <c r="AH48" s="19"/>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A49" s="17">
         <v>1989</v>
       </c>
@@ -3936,7 +5126,7 @@
       <c r="AG49" s="18"/>
       <c r="AH49" s="19"/>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A50" s="17">
         <v>1989</v>
       </c>
@@ -3980,7 +5170,7 @@
       <c r="AG50" s="18"/>
       <c r="AH50" s="19"/>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A51" s="17">
         <v>1989</v>
       </c>
@@ -4024,7 +5214,7 @@
       <c r="AG51" s="18"/>
       <c r="AH51" s="19"/>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A52" s="17">
         <v>1990</v>
       </c>
@@ -4096,7 +5286,7 @@
       <c r="AG52" s="18"/>
       <c r="AH52" s="19"/>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A53" s="17">
         <v>1990</v>
       </c>
@@ -4168,7 +5358,7 @@
       <c r="AG53" s="18"/>
       <c r="AH53" s="19"/>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A54" s="17">
         <v>1990</v>
       </c>
@@ -4240,7 +5430,7 @@
       <c r="AG54" s="18"/>
       <c r="AH54" s="19"/>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A55" s="17">
         <v>1990</v>
       </c>
@@ -4312,7 +5502,7 @@
       <c r="AG55" s="18"/>
       <c r="AH55" s="19"/>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A56" s="17">
         <v>1991</v>
       </c>
@@ -4412,7 +5602,7 @@
       <c r="AG56" s="18"/>
       <c r="AH56" s="19"/>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A57" s="17">
         <v>1991</v>
       </c>
@@ -4512,7 +5702,7 @@
       <c r="AG57" s="18"/>
       <c r="AH57" s="19"/>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A58" s="17">
         <v>1991</v>
       </c>
@@ -4612,7 +5802,7 @@
       <c r="AG58" s="18"/>
       <c r="AH58" s="19"/>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A59" s="17">
         <v>1991</v>
       </c>
@@ -4712,7 +5902,7 @@
       <c r="AG59" s="18"/>
       <c r="AH59" s="19"/>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A60" s="17">
         <v>1992</v>
       </c>
@@ -4812,7 +6002,7 @@
       <c r="AG60" s="18"/>
       <c r="AH60" s="19"/>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A61" s="17">
         <v>1992</v>
       </c>
@@ -4912,7 +6102,7 @@
       <c r="AG61" s="18"/>
       <c r="AH61" s="19"/>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A62" s="17">
         <v>1992</v>
       </c>
@@ -5012,7 +6202,7 @@
       <c r="AG62" s="18"/>
       <c r="AH62" s="19"/>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A63" s="17">
         <v>1992</v>
       </c>
@@ -5112,7 +6302,7 @@
       <c r="AG63" s="18"/>
       <c r="AH63" s="19"/>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A64" s="17">
         <v>1993</v>
       </c>
@@ -5212,7 +6402,7 @@
       <c r="AG64" s="18"/>
       <c r="AH64" s="19"/>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A65" s="17">
         <v>1993</v>
       </c>
@@ -5312,7 +6502,7 @@
       <c r="AG65" s="18"/>
       <c r="AH65" s="19"/>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A66" s="17">
         <v>1993</v>
       </c>
@@ -5412,7 +6602,7 @@
       <c r="AG66" s="18"/>
       <c r="AH66" s="19"/>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A67" s="17">
         <v>1993</v>
       </c>
@@ -5512,7 +6702,7 @@
       <c r="AG67" s="18"/>
       <c r="AH67" s="19"/>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A68" s="17">
         <v>1994</v>
       </c>
@@ -5612,7 +6802,7 @@
       <c r="AG68" s="18"/>
       <c r="AH68" s="19"/>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A69" s="17">
         <v>1994</v>
       </c>
@@ -5712,7 +6902,7 @@
       <c r="AG69" s="18"/>
       <c r="AH69" s="19"/>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A70" s="17">
         <v>1994</v>
       </c>
@@ -5812,7 +7002,7 @@
       <c r="AG70" s="18"/>
       <c r="AH70" s="19"/>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A71" s="17">
         <v>1994</v>
       </c>
@@ -5912,7 +7102,7 @@
       <c r="AG71" s="18"/>
       <c r="AH71" s="19"/>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A72" s="17">
         <v>1995</v>
       </c>
@@ -6012,7 +7202,7 @@
       <c r="AG72" s="18"/>
       <c r="AH72" s="19"/>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A73" s="17">
         <v>1995</v>
       </c>
@@ -6112,7 +7302,7 @@
       <c r="AG73" s="18"/>
       <c r="AH73" s="19"/>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A74" s="17">
         <v>1995</v>
       </c>
@@ -6212,7 +7402,7 @@
       <c r="AG74" s="18"/>
       <c r="AH74" s="19"/>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A75" s="17">
         <v>1995</v>
       </c>
@@ -6312,7 +7502,7 @@
       <c r="AG75" s="18"/>
       <c r="AH75" s="19"/>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A76" s="17">
         <v>1996</v>
       </c>
@@ -6412,7 +7602,7 @@
       <c r="AG76" s="18"/>
       <c r="AH76" s="19"/>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A77" s="17">
         <v>1996</v>
       </c>
@@ -6512,7 +7702,7 @@
       <c r="AG77" s="18"/>
       <c r="AH77" s="19"/>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A78" s="17">
         <v>1996</v>
       </c>
@@ -6612,7 +7802,7 @@
       <c r="AG78" s="18"/>
       <c r="AH78" s="19"/>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A79" s="17">
         <v>1996</v>
       </c>
@@ -6712,7 +7902,7 @@
       <c r="AG79" s="18"/>
       <c r="AH79" s="19"/>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A80" s="17">
         <v>1997</v>
       </c>
@@ -6812,7 +8002,7 @@
       <c r="AG80" s="18"/>
       <c r="AH80" s="19"/>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A81" s="17">
         <v>1997</v>
       </c>
@@ -6912,7 +8102,7 @@
       <c r="AG81" s="18"/>
       <c r="AH81" s="19"/>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A82" s="17">
         <v>1997</v>
       </c>
@@ -7012,7 +8202,7 @@
       <c r="AG82" s="18"/>
       <c r="AH82" s="19"/>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A83" s="17">
         <v>1997</v>
       </c>
@@ -7112,7 +8302,7 @@
       <c r="AG83" s="18"/>
       <c r="AH83" s="19"/>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A84" s="17">
         <v>1998</v>
       </c>
@@ -7212,7 +8402,7 @@
       <c r="AG84" s="18"/>
       <c r="AH84" s="19"/>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A85" s="17">
         <v>1998</v>
       </c>
@@ -7312,7 +8502,7 @@
       <c r="AG85" s="18"/>
       <c r="AH85" s="19"/>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A86" s="17">
         <v>1998</v>
       </c>
@@ -7412,7 +8602,7 @@
       <c r="AG86" s="18"/>
       <c r="AH86" s="19"/>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A87" s="17">
         <v>1998</v>
       </c>
@@ -7512,7 +8702,7 @@
       <c r="AG87" s="18"/>
       <c r="AH87" s="19"/>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A88" s="17">
         <v>1999</v>
       </c>
@@ -7612,7 +8802,7 @@
       <c r="AG88" s="18"/>
       <c r="AH88" s="19"/>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A89" s="17">
         <v>1999</v>
       </c>
@@ -7712,7 +8902,7 @@
       <c r="AG89" s="18"/>
       <c r="AH89" s="19"/>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A90" s="17">
         <v>1999</v>
       </c>
@@ -7812,7 +9002,7 @@
       <c r="AG90" s="18"/>
       <c r="AH90" s="19"/>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A91" s="17">
         <v>1999</v>
       </c>
@@ -7912,7 +9102,7 @@
       <c r="AG91" s="18"/>
       <c r="AH91" s="19"/>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A92" s="17">
         <v>2000</v>
       </c>
@@ -8012,7 +9202,7 @@
       <c r="AG92" s="18"/>
       <c r="AH92" s="19"/>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A93" s="17">
         <v>2000</v>
       </c>
@@ -8112,7 +9302,7 @@
       <c r="AG93" s="18"/>
       <c r="AH93" s="19"/>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A94" s="17">
         <v>2000</v>
       </c>
@@ -8212,7 +9402,7 @@
       <c r="AG94" s="18"/>
       <c r="AH94" s="19"/>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A95" s="17">
         <v>2000</v>
       </c>
@@ -8312,7 +9502,7 @@
       <c r="AG95" s="18"/>
       <c r="AH95" s="19"/>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A96" s="17">
         <v>2001</v>
       </c>
@@ -8412,7 +9602,7 @@
       <c r="AG96" s="18"/>
       <c r="AH96" s="19"/>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A97" s="17">
         <v>2001</v>
       </c>
@@ -8512,7 +9702,7 @@
       <c r="AG97" s="18"/>
       <c r="AH97" s="19"/>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A98" s="17">
         <v>2001</v>
       </c>
@@ -8612,7 +9802,7 @@
       <c r="AG98" s="18"/>
       <c r="AH98" s="19"/>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A99" s="17">
         <v>2001</v>
       </c>
@@ -8712,7 +9902,7 @@
       <c r="AG99" s="18"/>
       <c r="AH99" s="19"/>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A100" s="17">
         <v>2002</v>
       </c>
@@ -8812,7 +10002,7 @@
       <c r="AG100" s="18"/>
       <c r="AH100" s="19"/>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A101" s="17">
         <v>2002</v>
       </c>
@@ -8912,7 +10102,7 @@
       <c r="AG101" s="18"/>
       <c r="AH101" s="19"/>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A102" s="17">
         <v>2002</v>
       </c>
@@ -9012,7 +10202,7 @@
       <c r="AG102" s="18"/>
       <c r="AH102" s="19"/>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A103" s="17">
         <v>2002</v>
       </c>
@@ -9112,7 +10302,7 @@
       <c r="AG103" s="18"/>
       <c r="AH103" s="19"/>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A104" s="17">
         <v>2003</v>
       </c>
@@ -9212,7 +10402,7 @@
       <c r="AG104" s="18"/>
       <c r="AH104" s="19"/>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A105" s="17">
         <v>2003</v>
       </c>
@@ -9312,7 +10502,7 @@
       <c r="AG105" s="18"/>
       <c r="AH105" s="19"/>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A106" s="17">
         <v>2003</v>
       </c>
@@ -9412,7 +10602,7 @@
       <c r="AG106" s="18"/>
       <c r="AH106" s="19"/>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A107" s="17">
         <v>2003</v>
       </c>
@@ -9512,7 +10702,7 @@
       <c r="AG107" s="18"/>
       <c r="AH107" s="19"/>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A108" s="17">
         <v>2004</v>
       </c>
@@ -9612,7 +10802,7 @@
       <c r="AG108" s="18"/>
       <c r="AH108" s="19"/>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A109" s="17">
         <v>2004</v>
       </c>
@@ -9712,7 +10902,7 @@
       <c r="AG109" s="18"/>
       <c r="AH109" s="19"/>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A110" s="17">
         <v>2004</v>
       </c>
@@ -9812,7 +11002,7 @@
       <c r="AG110" s="18"/>
       <c r="AH110" s="19"/>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A111" s="17">
         <v>2004</v>
       </c>
@@ -9912,7 +11102,7 @@
       <c r="AG111" s="18"/>
       <c r="AH111" s="19"/>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A112" s="17">
         <v>2005</v>
       </c>
@@ -10012,7 +11202,7 @@
       <c r="AG112" s="18"/>
       <c r="AH112" s="19"/>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A113" s="17">
         <v>2005</v>
       </c>
@@ -10112,7 +11302,7 @@
       <c r="AG113" s="18"/>
       <c r="AH113" s="19"/>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A114" s="17">
         <v>2005</v>
       </c>
@@ -10212,7 +11402,7 @@
       <c r="AG114" s="18"/>
       <c r="AH114" s="19"/>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A115" s="17">
         <v>2005</v>
       </c>
@@ -10312,7 +11502,7 @@
       <c r="AG115" s="18"/>
       <c r="AH115" s="19"/>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A116" s="17">
         <v>2006</v>
       </c>
@@ -10412,7 +11602,7 @@
       <c r="AG116" s="18"/>
       <c r="AH116" s="19"/>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A117" s="17">
         <v>2006</v>
       </c>
@@ -10512,7 +11702,7 @@
       <c r="AG117" s="18"/>
       <c r="AH117" s="19"/>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A118" s="17">
         <v>2006</v>
       </c>
@@ -10612,7 +11802,7 @@
       <c r="AG118" s="18"/>
       <c r="AH118" s="19"/>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A119" s="17">
         <v>2006</v>
       </c>
@@ -10712,7 +11902,7 @@
       <c r="AG119" s="18"/>
       <c r="AH119" s="19"/>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A120" s="17">
         <v>2007</v>
       </c>
@@ -10812,7 +12002,7 @@
       <c r="AG120" s="18"/>
       <c r="AH120" s="19"/>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A121" s="17">
         <v>2007</v>
       </c>
@@ -10912,7 +12102,7 @@
       <c r="AG121" s="18"/>
       <c r="AH121" s="19"/>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A122" s="17">
         <v>2007</v>
       </c>
@@ -11012,7 +12202,7 @@
       <c r="AG122" s="18"/>
       <c r="AH122" s="19"/>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A123" s="17">
         <v>2007</v>
       </c>
@@ -11112,7 +12302,7 @@
       <c r="AG123" s="18"/>
       <c r="AH123" s="19"/>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A124" s="17">
         <v>2008</v>
       </c>
@@ -11212,7 +12402,7 @@
       <c r="AG124" s="18"/>
       <c r="AH124" s="19"/>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A125" s="17">
         <v>2008</v>
       </c>
@@ -11312,7 +12502,7 @@
       <c r="AG125" s="18"/>
       <c r="AH125" s="19"/>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A126" s="17">
         <v>2008</v>
       </c>
@@ -11412,7 +12602,7 @@
       <c r="AG126" s="18"/>
       <c r="AH126" s="19"/>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A127" s="17">
         <v>2008</v>
       </c>
@@ -11512,7 +12702,7 @@
       <c r="AG127" s="18"/>
       <c r="AH127" s="19"/>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A128" s="17">
         <v>2009</v>
       </c>
@@ -11612,7 +12802,7 @@
       <c r="AG128" s="18"/>
       <c r="AH128" s="19"/>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A129" s="17">
         <v>2009</v>
       </c>
@@ -11712,7 +12902,7 @@
       <c r="AG129" s="18"/>
       <c r="AH129" s="19"/>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A130" s="17">
         <v>2009</v>
       </c>
@@ -11812,7 +13002,7 @@
       <c r="AG130" s="18"/>
       <c r="AH130" s="19"/>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A131" s="17">
         <v>2009</v>
       </c>
@@ -11912,7 +13102,7 @@
       <c r="AG131" s="18"/>
       <c r="AH131" s="19"/>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A132" s="17">
         <v>2010</v>
       </c>
@@ -12012,7 +13202,7 @@
       <c r="AG132" s="18"/>
       <c r="AH132" s="19"/>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A133" s="17">
         <v>2010</v>
       </c>
@@ -12112,7 +13302,7 @@
       <c r="AG133" s="18"/>
       <c r="AH133" s="19"/>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A134" s="17">
         <v>2010</v>
       </c>
@@ -12212,7 +13402,7 @@
       <c r="AG134" s="18"/>
       <c r="AH134" s="19"/>
     </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A135" s="17">
         <v>2010</v>
       </c>
@@ -12312,7 +13502,7 @@
       <c r="AG135" s="18"/>
       <c r="AH135" s="19"/>
     </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A136" s="17">
         <v>2011</v>
       </c>
@@ -12412,7 +13602,7 @@
       <c r="AG136" s="18"/>
       <c r="AH136" s="19"/>
     </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A137" s="17">
         <v>2011</v>
       </c>
@@ -12512,7 +13702,7 @@
       <c r="AG137" s="18"/>
       <c r="AH137" s="19"/>
     </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A138" s="17">
         <v>2011</v>
       </c>
@@ -12612,7 +13802,7 @@
       <c r="AG138" s="18"/>
       <c r="AH138" s="19"/>
     </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A139" s="17">
         <v>2011</v>
       </c>
@@ -12712,7 +13902,7 @@
       <c r="AG139" s="18"/>
       <c r="AH139" s="19"/>
     </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A140" s="17">
         <v>2012</v>
       </c>
@@ -12812,7 +14002,7 @@
       <c r="AG140" s="18"/>
       <c r="AH140" s="19"/>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A141" s="17">
         <v>2012</v>
       </c>
@@ -12912,7 +14102,7 @@
       <c r="AG141" s="18"/>
       <c r="AH141" s="19"/>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A142" s="17">
         <v>2012</v>
       </c>
@@ -13012,7 +14202,7 @@
       <c r="AG142" s="18"/>
       <c r="AH142" s="19"/>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A143" s="17">
         <v>2012</v>
       </c>
@@ -13112,7 +14302,7 @@
       <c r="AG143" s="18"/>
       <c r="AH143" s="19"/>
     </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A144" s="17">
         <v>2013</v>
       </c>
@@ -13212,7 +14402,7 @@
       <c r="AG144" s="18"/>
       <c r="AH144" s="19"/>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A145" s="17">
         <v>2013</v>
       </c>
@@ -13312,7 +14502,7 @@
       <c r="AG145" s="18"/>
       <c r="AH145" s="19"/>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A146" s="17">
         <v>2013</v>
       </c>
@@ -13412,7 +14602,7 @@
       <c r="AG146" s="18"/>
       <c r="AH146" s="19"/>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A147" s="17">
         <v>2013</v>
       </c>
@@ -13512,7 +14702,7 @@
       <c r="AG147" s="18"/>
       <c r="AH147" s="19"/>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A148" s="17">
         <v>2014</v>
       </c>
@@ -13612,7 +14802,7 @@
       <c r="AG148" s="18"/>
       <c r="AH148" s="19"/>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A149" s="17">
         <v>2014</v>
       </c>
@@ -13712,7 +14902,7 @@
       <c r="AG149" s="18"/>
       <c r="AH149" s="19"/>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A150" s="17">
         <v>2014</v>
       </c>
@@ -13812,7 +15002,7 @@
       <c r="AG150" s="18"/>
       <c r="AH150" s="19"/>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A151" s="17">
         <v>2014</v>
       </c>
@@ -13912,7 +15102,7 @@
       <c r="AG151" s="18"/>
       <c r="AH151" s="19"/>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A152" s="17">
         <v>2015</v>
       </c>
@@ -14012,7 +15202,7 @@
       <c r="AG152" s="18"/>
       <c r="AH152" s="19"/>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A153" s="17">
         <v>2015</v>
       </c>
@@ -14112,7 +15302,7 @@
       <c r="AG153" s="18"/>
       <c r="AH153" s="19"/>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A154" s="17">
         <v>2015</v>
       </c>
@@ -14212,7 +15402,7 @@
       <c r="AG154" s="18"/>
       <c r="AH154" s="19"/>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A155" s="17">
         <v>2015</v>
       </c>
@@ -14312,7 +15502,7 @@
       <c r="AG155" s="18"/>
       <c r="AH155" s="19"/>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A156" s="17">
         <v>2016</v>
       </c>
@@ -14412,7 +15602,7 @@
       <c r="AG156" s="18"/>
       <c r="AH156" s="19"/>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A157" s="17">
         <v>2016</v>
       </c>
@@ -14512,7 +15702,7 @@
       <c r="AG157" s="18"/>
       <c r="AH157" s="19"/>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A158" s="17">
         <v>2016</v>
       </c>
@@ -14612,7 +15802,7 @@
       <c r="AG158" s="18"/>
       <c r="AH158" s="19"/>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A159" s="17">
         <v>2016</v>
       </c>
@@ -14712,7 +15902,7 @@
       <c r="AG159" s="18"/>
       <c r="AH159" s="19"/>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A160" s="17">
         <v>2017</v>
       </c>
@@ -14812,7 +16002,7 @@
       <c r="AG160" s="18"/>
       <c r="AH160" s="19"/>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A161" s="17">
         <v>2017</v>
       </c>
@@ -14912,7 +16102,7 @@
       <c r="AG161" s="18"/>
       <c r="AH161" s="19"/>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A162" s="17">
         <v>2017</v>
       </c>
@@ -15012,7 +16202,7 @@
       <c r="AG162" s="18"/>
       <c r="AH162" s="19"/>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A163" s="17">
         <v>2017</v>
       </c>
@@ -15112,7 +16302,7 @@
       <c r="AG163" s="18"/>
       <c r="AH163" s="19"/>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A164" s="17">
         <v>2018</v>
       </c>
@@ -15212,7 +16402,7 @@
       <c r="AG164" s="18"/>
       <c r="AH164" s="19"/>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A165" s="17">
         <v>2018</v>
       </c>
@@ -15312,7 +16502,7 @@
       <c r="AG165" s="18"/>
       <c r="AH165" s="19"/>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A166" s="17">
         <v>2018</v>
       </c>
@@ -15412,7 +16602,7 @@
       <c r="AG166" s="18"/>
       <c r="AH166" s="19"/>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A167" s="17">
         <v>2018</v>
       </c>
@@ -15512,7 +16702,7 @@
       <c r="AG167" s="18"/>
       <c r="AH167" s="19"/>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A168" s="17">
         <v>2019</v>
       </c>
@@ -15612,7 +16802,7 @@
       <c r="AG168" s="18"/>
       <c r="AH168" s="19"/>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A169" s="17">
         <v>2019</v>
       </c>
@@ -15712,7 +16902,7 @@
       <c r="AG169" s="18"/>
       <c r="AH169" s="19"/>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A170" s="17">
         <v>2019</v>
       </c>
@@ -15812,7 +17002,7 @@
       <c r="AG170" s="18"/>
       <c r="AH170" s="19"/>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A171" s="17">
         <v>2019</v>
       </c>
@@ -15912,7 +17102,7 @@
       <c r="AG171" s="18"/>
       <c r="AH171" s="19"/>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A172" s="17">
         <v>2020</v>
       </c>
@@ -16012,7 +17202,7 @@
       <c r="AG172" s="18"/>
       <c r="AH172" s="19"/>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A173" s="17">
         <v>2020</v>
       </c>
@@ -16112,7 +17302,7 @@
       <c r="AG173" s="18"/>
       <c r="AH173" s="19"/>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A174" s="17">
         <v>2020</v>
       </c>
@@ -16212,7 +17402,7 @@
       <c r="AG174" s="18"/>
       <c r="AH174" s="19"/>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A175" s="17">
         <v>2020</v>
       </c>
@@ -16312,7 +17502,7 @@
       <c r="AG175" s="18"/>
       <c r="AH175" s="19"/>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A176" s="17">
         <v>2021</v>
       </c>
@@ -16412,7 +17602,7 @@
       <c r="AG176" s="18"/>
       <c r="AH176" s="19"/>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A177" s="17">
         <v>2021</v>
       </c>
@@ -16512,7 +17702,7 @@
       <c r="AG177" s="18"/>
       <c r="AH177" s="19"/>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A178" s="17">
         <v>2021</v>
       </c>
@@ -16612,7 +17802,7 @@
       <c r="AG178" s="18"/>
       <c r="AH178" s="19"/>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A179" s="17">
         <v>2021</v>
       </c>
@@ -16712,7 +17902,7 @@
       <c r="AG179" s="18"/>
       <c r="AH179" s="19"/>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A180" s="17">
         <v>2022</v>
       </c>
@@ -16812,7 +18002,7 @@
       <c r="AG180" s="18"/>
       <c r="AH180" s="19"/>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A181" s="17">
         <v>2022</v>
       </c>
@@ -16912,7 +18102,7 @@
       <c r="AG181" s="18"/>
       <c r="AH181" s="19"/>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A182" s="17">
         <v>2022</v>
       </c>
@@ -17012,7 +18202,7 @@
       <c r="AG182" s="18"/>
       <c r="AH182" s="19"/>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A183" s="17">
         <v>2022</v>
       </c>
@@ -17112,7 +18302,7 @@
       <c r="AG183" s="18"/>
       <c r="AH183" s="19"/>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A184" s="17">
         <v>2023</v>
       </c>
@@ -17212,7 +18402,7 @@
       <c r="AG184" s="18"/>
       <c r="AH184" s="19"/>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A185" s="17">
         <v>2023</v>
       </c>
@@ -17312,7 +18502,7 @@
       <c r="AG185" s="18"/>
       <c r="AH185" s="19"/>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A186" s="17">
         <v>2023</v>
       </c>
@@ -17412,7 +18602,7 @@
       <c r="AG186" s="18"/>
       <c r="AH186" s="19"/>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A187" s="17">
         <v>2023</v>
       </c>
@@ -17512,7 +18702,7 @@
       <c r="AG187" s="18"/>
       <c r="AH187" s="19"/>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A188" s="17">
         <v>2024</v>
       </c>
@@ -17612,7 +18802,7 @@
       <c r="AG188" s="18"/>
       <c r="AH188" s="19"/>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A189" s="17">
         <v>2024</v>
       </c>
@@ -17712,7 +18902,7 @@
       <c r="AG189" s="18"/>
       <c r="AH189" s="19"/>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A190" s="17">
         <v>2024</v>
       </c>
@@ -17812,7 +19002,7 @@
       <c r="AG190" s="18"/>
       <c r="AH190" s="19"/>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A191" s="17">
         <v>2024</v>
       </c>
@@ -17912,7 +19102,7 @@
       <c r="AG191" s="18"/>
       <c r="AH191" s="19"/>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A192" s="17">
         <v>2025</v>
       </c>
@@ -18012,7 +19202,7 @@
       <c r="AG192" s="18"/>
       <c r="AH192" s="19"/>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A193" s="17">
         <v>2025</v>
       </c>
@@ -18112,7 +19302,7 @@
       <c r="AG193" s="18"/>
       <c r="AH193" s="19"/>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A194" s="17">
         <v>2025</v>
       </c>
@@ -18212,7 +19402,7 @@
       <c r="AG194" s="18"/>
       <c r="AH194" s="19"/>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A195" s="17"/>
       <c r="B195" s="17"/>
       <c r="C195" s="18"/>
@@ -18251,6 +19441,25 @@
   </sheetData>
   <sheetProtection password="DD0B" sheet="1"/>
   <mergeCells count="33">
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="AA6:AB10"/>
+    <mergeCell ref="O5:P10"/>
+    <mergeCell ref="C5:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="U5:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
     <mergeCell ref="AA4:AF4"/>
     <mergeCell ref="AC5:AD10"/>
     <mergeCell ref="AE5:AF10"/>
@@ -18265,25 +19474,6 @@
     <mergeCell ref="W5:X10"/>
     <mergeCell ref="Y5:Z10"/>
     <mergeCell ref="O4:Z4"/>
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="AA6:AB10"/>
-    <mergeCell ref="O5:P10"/>
-    <mergeCell ref="C5:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="U5:V10"/>
-    <mergeCell ref="U11:V11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18294,14 +19484,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Table04"/>
   <dimension ref="A1:AH57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
     <col min="2" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="34" width="9.75" customWidth="1"/>
+    <col min="3" max="34" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A1)-1,COLUMN(beschriftung!A$1)))</f>
         <v>ESA 2010, Quarterly aggregates of Gross Domestic Product, income approach, raw data</v>
@@ -18337,7 +19527,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="10"/>
     </row>
-    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A2)-1,COLUMN(beschriftung!B$1)))</f>
         <v>In Mio. Swiss Francs, at current prices, percentage change to previous year</v>
@@ -18373,7 +19563,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="9"/>
@@ -18405,427 +19595,427 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-      <c r="C4" s="38" t="str">
+      <c r="C4" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!C$1)))</f>
         <v xml:space="preserve">Gross domestic product </v>
       </c>
-      <c r="D4" s="44" t="e">
+      <c r="D4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="E4" s="44" t="e">
+      <c r="E4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="F4" s="44" t="e">
+      <c r="F4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="G4" s="44" t="e">
+      <c r="G4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="H4" s="44" t="e">
+      <c r="H4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="I4" s="44" t="e">
+      <c r="I4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="J4" s="44" t="e">
+      <c r="J4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="K4" s="44" t="e">
+      <c r="K4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="L4" s="44" t="e">
+      <c r="L4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="M4" s="44" t="e">
+      <c r="M4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="N4" s="39" t="e">
+      <c r="N4" s="23" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="O4" s="38" t="str">
+      <c r="O4" s="21" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A5)-1,COLUMN(O$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A5)-1,COLUMN(O$1))))</f>
         <v>Gross national income</v>
       </c>
-      <c r="P4" s="44" t="e">
+      <c r="P4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q4" s="44" t="e">
+      <c r="Q4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="R4" s="44" t="e">
+      <c r="R4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="S4" s="44" t="e">
+      <c r="S4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="T4" s="44" t="e">
+      <c r="T4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44" t="e">
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="X4" s="44" t="e">
+      <c r="X4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Y4" s="44" t="e">
+      <c r="Y4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Z4" s="39" t="e">
+      <c r="Z4" s="23" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="AA4" s="38" t="str">
+      <c r="AA4" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A5)-1,COLUMN(beschriftung!AA$1)))</f>
         <v>Disposable income, gross</v>
       </c>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="39"/>
-    </row>
-    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="23"/>
+    </row>
+    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="38" t="str">
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!E$1)))</f>
         <v>Compensation of employees</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="38" t="str">
+      <c r="F5" s="23"/>
+      <c r="G5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!G$1)))</f>
         <v>Net operating surplus and net mixed income</v>
       </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="38" t="str">
+      <c r="H5" s="23"/>
+      <c r="I5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!I$1)))</f>
         <v xml:space="preserve">Consumption of fixed capital </v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="38" t="str">
+      <c r="J5" s="23"/>
+      <c r="K5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!K$1)))</f>
         <v>Taxes on production and imports</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="38" t="str">
+      <c r="L5" s="23"/>
+      <c r="M5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!M$1)))</f>
         <v>Subsidies</v>
       </c>
-      <c r="N5" s="39"/>
-      <c r="O5" s="25" t="str">
+      <c r="N5" s="23"/>
+      <c r="O5" s="34" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(O$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(O$1))))</f>
         <v/>
       </c>
-      <c r="P5" s="26" t="e">
+      <c r="P5" s="25" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A6)-1,COLUMN(P$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A6)-1,COLUMN(P$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q5" s="38" t="str">
+      <c r="Q5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Q$1)))</f>
         <v>Compensation of employees received from the rest of the world</v>
       </c>
-      <c r="R5" s="39"/>
-      <c r="S5" s="38" t="str">
+      <c r="R5" s="23"/>
+      <c r="S5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!S$1)))</f>
         <v>Compensation of employees paid to the rest of the world</v>
       </c>
-      <c r="T5" s="39"/>
-      <c r="U5" s="38" t="str">
+      <c r="T5" s="23"/>
+      <c r="U5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!U$1)))</f>
         <v>Taxes on production and imports received from the rest of the world</v>
       </c>
-      <c r="V5" s="39"/>
-      <c r="W5" s="38" t="str">
+      <c r="V5" s="23"/>
+      <c r="W5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!W$1)))</f>
         <v>Property income received from the rest of the world</v>
       </c>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="38" t="str">
+      <c r="X5" s="23"/>
+      <c r="Y5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!Y$1)))</f>
         <v>Property income paid to the rest of the world</v>
       </c>
-      <c r="Z5" s="39"/>
+      <c r="Z5" s="23"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="11" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AB$1))))</f>
         <v/>
       </c>
-      <c r="AC5" s="38" t="str">
+      <c r="AC5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AC$1)))</f>
         <v>Current transfers receivable from the rest of the world</v>
       </c>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="38" t="str">
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="21" t="str">
         <f ca="1">INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW(beschriftung!$A7)-1,COLUMN(beschriftung!AE$1)))</f>
         <v>Current transfers payable to the rest of the world</v>
       </c>
-      <c r="AF5" s="39"/>
+      <c r="AF5" s="23"/>
       <c r="AG5" s="4" t="str">
         <f ca="1">IF(INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AG$1)))="","",INDIRECT("beschriftung!"&amp;ADDRESS(beschriftung!$C$1*12+ROW($A6)-1,COLUMN(AG$1))))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="27" t="e">
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="35" t="e">
         <f ca="1">INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW(#REF!)-1,COLUMN(#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="41"/>
-    </row>
-    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="27"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+    </row>
+    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="41"/>
-    </row>
-    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="31"/>
+    </row>
+    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="41"/>
-      <c r="AE8" s="40"/>
-      <c r="AF8" s="41"/>
-    </row>
-    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="31"/>
+    </row>
+    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="41"/>
-    </row>
-    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+    </row>
+    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="42"/>
-      <c r="AF10" s="43"/>
-    </row>
-    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="33"/>
+    </row>
+    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="I11" s="36" t="s">
+      <c r="H11" s="42"/>
+      <c r="I11" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="37"/>
-      <c r="K11" s="36" t="s">
+      <c r="J11" s="42"/>
+      <c r="K11" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="37"/>
-      <c r="M11" s="36" t="s">
+      <c r="L11" s="42"/>
+      <c r="M11" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="37"/>
-      <c r="O11" s="21" t="s">
+      <c r="N11" s="42"/>
+      <c r="O11" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="21" t="s">
+      <c r="P11" s="44"/>
+      <c r="Q11" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="22"/>
-      <c r="S11" s="21" t="s">
+      <c r="R11" s="44"/>
+      <c r="S11" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="T11" s="22"/>
-      <c r="U11" s="21" t="s">
+      <c r="T11" s="44"/>
+      <c r="U11" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="V11" s="22"/>
-      <c r="W11" s="21" t="s">
+      <c r="V11" s="44"/>
+      <c r="W11" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="21" t="s">
+      <c r="X11" s="44"/>
+      <c r="Y11" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="21" t="s">
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="21" t="s">
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="21" t="s">
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="AF11" s="22"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AF11" s="44"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
         <v>1980</v>
       </c>
@@ -18865,7 +20055,7 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="19"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="17">
         <v>1981</v>
       </c>
@@ -18907,7 +20097,7 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="19"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="17">
         <v>1982</v>
       </c>
@@ -18949,7 +20139,7 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="19"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="17">
         <v>1983</v>
       </c>
@@ -18991,7 +20181,7 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="19"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="17">
         <v>1984</v>
       </c>
@@ -19033,7 +20223,7 @@
       <c r="AG16" s="18"/>
       <c r="AH16" s="19"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" s="17">
         <v>1985</v>
       </c>
@@ -19075,7 +20265,7 @@
       <c r="AG17" s="18"/>
       <c r="AH17" s="19"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" s="17">
         <v>1986</v>
       </c>
@@ -19117,7 +20307,7 @@
       <c r="AG18" s="18"/>
       <c r="AH18" s="19"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" s="17">
         <v>1987</v>
       </c>
@@ -19159,7 +20349,7 @@
       <c r="AG19" s="18"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" s="17">
         <v>1988</v>
       </c>
@@ -19201,7 +20391,7 @@
       <c r="AG20" s="18"/>
       <c r="AH20" s="19"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" s="17">
         <v>1989</v>
       </c>
@@ -19243,7 +20433,7 @@
       <c r="AG21" s="18"/>
       <c r="AH21" s="19"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
         <v>1990</v>
       </c>
@@ -19313,7 +20503,7 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="19"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
         <v>1991</v>
       </c>
@@ -19411,7 +20601,7 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="19"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
         <v>1992</v>
       </c>
@@ -19509,7 +20699,7 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="19"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
         <v>1993</v>
       </c>
@@ -19607,7 +20797,7 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="19"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
         <v>1994</v>
       </c>
@@ -19705,7 +20895,7 @@
       <c r="AG26" s="18"/>
       <c r="AH26" s="19"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" s="17">
         <v>1995</v>
       </c>
@@ -19803,7 +20993,7 @@
       <c r="AG27" s="18"/>
       <c r="AH27" s="19"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" s="17">
         <v>1996</v>
       </c>
@@ -19901,7 +21091,7 @@
       <c r="AG28" s="18"/>
       <c r="AH28" s="19"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" s="17">
         <v>1997</v>
       </c>
@@ -19999,7 +21189,7 @@
       <c r="AG29" s="18"/>
       <c r="AH29" s="19"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" s="17">
         <v>1998</v>
       </c>
@@ -20097,7 +21287,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="19"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" s="17">
         <v>1999</v>
       </c>
@@ -20195,7 +21385,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="19"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" s="17">
         <v>2000</v>
       </c>
@@ -20293,7 +21483,7 @@
       <c r="AG32" s="18"/>
       <c r="AH32" s="19"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" s="17">
         <v>2001</v>
       </c>
@@ -20391,7 +21581,7 @@
       <c r="AG33" s="18"/>
       <c r="AH33" s="19"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" s="17">
         <v>2002</v>
       </c>
@@ -20489,7 +21679,7 @@
       <c r="AG34" s="18"/>
       <c r="AH34" s="19"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" s="17">
         <v>2003</v>
       </c>
@@ -20587,7 +21777,7 @@
       <c r="AG35" s="18"/>
       <c r="AH35" s="19"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" s="17">
         <v>2004</v>
       </c>
@@ -20685,7 +21875,7 @@
       <c r="AG36" s="18"/>
       <c r="AH36" s="19"/>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37" s="17">
         <v>2005</v>
       </c>
@@ -20783,7 +21973,7 @@
       <c r="AG37" s="18"/>
       <c r="AH37" s="19"/>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38" s="17">
         <v>2006</v>
       </c>
@@ -20881,7 +22071,7 @@
       <c r="AG38" s="18"/>
       <c r="AH38" s="19"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39" s="17">
         <v>2007</v>
       </c>
@@ -20979,7 +22169,7 @@
       <c r="AG39" s="18"/>
       <c r="AH39" s="19"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40" s="17">
         <v>2008</v>
       </c>
@@ -21077,7 +22267,7 @@
       <c r="AG40" s="18"/>
       <c r="AH40" s="19"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41" s="17">
         <v>2009</v>
       </c>
@@ -21175,7 +22365,7 @@
       <c r="AG41" s="18"/>
       <c r="AH41" s="19"/>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42" s="17">
         <v>2010</v>
       </c>
@@ -21273,7 +22463,7 @@
       <c r="AG42" s="18"/>
       <c r="AH42" s="19"/>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43" s="17">
         <v>2011</v>
       </c>
@@ -21371,7 +22561,7 @@
       <c r="AG43" s="18"/>
       <c r="AH43" s="19"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44" s="17">
         <v>2012</v>
       </c>
@@ -21469,7 +22659,7 @@
       <c r="AG44" s="18"/>
       <c r="AH44" s="19"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A45" s="17">
         <v>2013</v>
       </c>
@@ -21567,7 +22757,7 @@
       <c r="AG45" s="18"/>
       <c r="AH45" s="19"/>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A46" s="17">
         <v>2014</v>
       </c>
@@ -21665,7 +22855,7 @@
       <c r="AG46" s="18"/>
       <c r="AH46" s="19"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A47" s="17">
         <v>2015</v>
       </c>
@@ -21763,7 +22953,7 @@
       <c r="AG47" s="18"/>
       <c r="AH47" s="19"/>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A48" s="17">
         <v>2016</v>
       </c>
@@ -21861,7 +23051,7 @@
       <c r="AG48" s="18"/>
       <c r="AH48" s="19"/>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A49" s="17">
         <v>2017</v>
       </c>
@@ -21959,7 +23149,7 @@
       <c r="AG49" s="18"/>
       <c r="AH49" s="19"/>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A50" s="17">
         <v>2018</v>
       </c>
@@ -22057,7 +23247,7 @@
       <c r="AG50" s="18"/>
       <c r="AH50" s="19"/>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A51" s="17">
         <v>2019</v>
       </c>
@@ -22155,7 +23345,7 @@
       <c r="AG51" s="18"/>
       <c r="AH51" s="19"/>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A52" s="17">
         <v>2020</v>
       </c>
@@ -22253,7 +23443,7 @@
       <c r="AG52" s="18"/>
       <c r="AH52" s="19"/>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A53" s="17">
         <v>2021</v>
       </c>
@@ -22351,7 +23541,7 @@
       <c r="AG53" s="18"/>
       <c r="AH53" s="19"/>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A54" s="17">
         <v>2022</v>
       </c>
@@ -22449,7 +23639,7 @@
       <c r="AG54" s="18"/>
       <c r="AH54" s="19"/>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A55" s="17">
         <v>2023</v>
       </c>
@@ -22547,7 +23737,7 @@
       <c r="AG55" s="18"/>
       <c r="AH55" s="19"/>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A56" s="17">
         <v>2024</v>
       </c>
@@ -22645,7 +23835,7 @@
       <c r="AG56" s="18"/>
       <c r="AH56" s="19"/>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="18"/>
@@ -22684,6 +23874,26 @@
   </sheetData>
   <sheetProtection password="DD0B" sheet="1"/>
   <mergeCells count="33">
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AA6:AB10"/>
+    <mergeCell ref="AE5:AF10"/>
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="AC5:AD10"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Q5:R10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="U5:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="C4:N4"/>
     <mergeCell ref="O4:Z4"/>
     <mergeCell ref="AA4:AF4"/>
@@ -22697,26 +23907,6 @@
     <mergeCell ref="S5:T10"/>
     <mergeCell ref="W5:X10"/>
     <mergeCell ref="Y5:Z10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Q5:R10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="U5:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AA6:AB10"/>
-    <mergeCell ref="AE5:AF10"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="AC5:AD10"/>
-    <mergeCell ref="AA11:AB11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -22726,16 +23916,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E256F5-6106-45E8-A2D5-7B2125FC6023}">
   <dimension ref="A1:AI57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
     <col min="2" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="32" width="9.75" customWidth="1"/>
+    <col min="3" max="32" width="9.77734375" customWidth="1"/>
     <col min="33" max="33" width="15.6640625" customWidth="1"/>
-    <col min="34" max="34" width="9.75" customWidth="1"/>
+    <col min="34" max="34" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
@@ -22770,7 +23960,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="10"/>
     </row>
-    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -22805,7 +23995,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="9"/>
@@ -22837,407 +24027,407 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="44" t="e">
+      <c r="D4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(D$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="E4" s="44" t="e">
+      <c r="E4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(E$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="F4" s="44" t="e">
+      <c r="F4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(F$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="G4" s="44" t="e">
+      <c r="G4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(G$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="H4" s="44" t="e">
+      <c r="H4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(H$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="I4" s="44" t="e">
+      <c r="I4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(I$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="J4" s="44" t="e">
+      <c r="J4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(J$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="K4" s="44" t="e">
+      <c r="K4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(K$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="L4" s="44" t="e">
+      <c r="L4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(L$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="M4" s="44" t="e">
+      <c r="M4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(M$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="N4" s="39" t="e">
+      <c r="N4" s="23" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(N$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="O4" s="38" t="s">
+      <c r="O4" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="44" t="e">
+      <c r="P4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(P$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q4" s="44" t="e">
+      <c r="Q4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Q$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="R4" s="44" t="e">
+      <c r="R4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(R$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="S4" s="44" t="e">
+      <c r="S4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(S$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="T4" s="44" t="e">
+      <c r="T4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(T$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44" t="e">
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(W$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="X4" s="44" t="e">
+      <c r="X4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(X$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Y4" s="44" t="e">
+      <c r="Y4" s="22" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Y$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="Z4" s="39" t="e">
+      <c r="Z4" s="23" t="e">
         <f ca="1">IF(INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1)))="","",INDIRECT("beschriftung.!"&amp;ADDRESS(#REF!*12+ROW($A5)-1,COLUMN(Z$1))))</f>
         <v>#REF!</v>
       </c>
-      <c r="AA4" s="38" t="s">
+      <c r="AA4" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="39"/>
-    </row>
-    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="23"/>
+    </row>
+    <row r="5" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="38" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="38" t="s">
+      <c r="F5" s="23"/>
+      <c r="G5" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="38" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="38" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="38" t="s">
+      <c r="L5" s="23"/>
+      <c r="M5" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="39"/>
-      <c r="O5" s="25" t="s">
+      <c r="N5" s="23"/>
+      <c r="O5" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="P5" s="26" t="e">
+      <c r="P5" s="25" t="e">
         <v>#REF!</v>
       </c>
-      <c r="Q5" s="38" t="s">
+      <c r="Q5" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="R5" s="39"/>
-      <c r="S5" s="38" t="s">
+      <c r="R5" s="23"/>
+      <c r="S5" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="T5" s="39"/>
-      <c r="U5" s="38" t="s">
+      <c r="T5" s="23"/>
+      <c r="U5" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="V5" s="39"/>
-      <c r="W5" s="38" t="s">
+      <c r="V5" s="23"/>
+      <c r="W5" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="38" t="s">
+      <c r="X5" s="23"/>
+      <c r="Y5" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="Z5" s="39"/>
+      <c r="Z5" s="23"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="AC5" s="38" t="s">
+      <c r="AC5" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="38" t="s">
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="AF5" s="39"/>
+      <c r="AF5" s="23"/>
       <c r="AG5" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="27" t="e">
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="35" t="e">
         <v>#REF!</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="41"/>
-    </row>
-    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="27"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+    </row>
+    <row r="7" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="41"/>
-    </row>
-    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="31"/>
+    </row>
+    <row r="8" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="41"/>
-      <c r="AE8" s="40"/>
-      <c r="AF8" s="41"/>
-    </row>
-    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="31"/>
+    </row>
+    <row r="9" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="41"/>
-    </row>
-    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+    </row>
+    <row r="10" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="42"/>
-      <c r="AF10" s="43"/>
-    </row>
-    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="33"/>
+    </row>
+    <row r="11" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="I11" s="36" t="s">
+      <c r="H11" s="42"/>
+      <c r="I11" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="37"/>
-      <c r="K11" s="36" t="s">
+      <c r="J11" s="42"/>
+      <c r="K11" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="37"/>
-      <c r="M11" s="36" t="s">
+      <c r="L11" s="42"/>
+      <c r="M11" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="37"/>
-      <c r="O11" s="21" t="s">
+      <c r="N11" s="42"/>
+      <c r="O11" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="21" t="s">
+      <c r="P11" s="44"/>
+      <c r="Q11" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="22"/>
-      <c r="S11" s="21" t="s">
+      <c r="R11" s="44"/>
+      <c r="S11" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="T11" s="22"/>
-      <c r="U11" s="21" t="s">
+      <c r="T11" s="44"/>
+      <c r="U11" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="V11" s="22"/>
-      <c r="W11" s="21" t="s">
+      <c r="V11" s="44"/>
+      <c r="W11" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="21" t="s">
+      <c r="X11" s="44"/>
+      <c r="Y11" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="21" t="s">
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="21" t="s">
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="21" t="s">
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="AF11" s="22"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AF11" s="44"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
         <v>1980</v>
       </c>
@@ -23277,7 +24467,7 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="19"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="17">
         <v>1981</v>
       </c>
@@ -23319,7 +24509,7 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="19"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="17">
         <v>1982</v>
       </c>
@@ -23361,7 +24551,7 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="19"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="17">
         <v>1983</v>
       </c>
@@ -23403,7 +24593,7 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="19"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="17">
         <v>1984</v>
       </c>
@@ -23445,7 +24635,7 @@
       <c r="AG16" s="18"/>
       <c r="AH16" s="19"/>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17" s="17">
         <v>1985</v>
       </c>
@@ -23487,7 +24677,7 @@
       <c r="AG17" s="18"/>
       <c r="AH17" s="19"/>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18" s="17">
         <v>1986</v>
       </c>
@@ -23529,7 +24719,7 @@
       <c r="AG18" s="18"/>
       <c r="AH18" s="19"/>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19" s="17">
         <v>1987</v>
       </c>
@@ -23571,7 +24761,7 @@
       <c r="AG19" s="18"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20" s="17">
         <v>1988</v>
       </c>
@@ -23613,7 +24803,7 @@
       <c r="AG20" s="18"/>
       <c r="AH20" s="19"/>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21" s="17">
         <v>1989</v>
       </c>
@@ -23659,34 +24849,34 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
         <v>1990</v>
       </c>
       <c r="B22" s="17"/>
-      <c r="C22" s="18">
+      <c r="C22" s="45">
         <v>374762.03661856701</v>
       </c>
       <c r="D22" s="19">
         <v>8.4474127528293697E-2</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="45">
         <v>203731.01214603899</v>
       </c>
       <c r="F22" s="19"/>
-      <c r="G22" s="18">
+      <c r="G22" s="45">
         <v>79044.620603616393</v>
       </c>
       <c r="H22" s="19"/>
-      <c r="I22" s="18">
+      <c r="I22" s="45">
         <v>83944.672117875496</v>
       </c>
       <c r="J22" s="19"/>
-      <c r="K22" s="18">
+      <c r="K22" s="45">
         <v>18568.786066836201</v>
       </c>
       <c r="L22" s="19"/>
-      <c r="M22" s="18">
+      <c r="M22" s="45">
         <v>-10527.0543158</v>
       </c>
       <c r="N22" s="19"/>
@@ -23739,42 +24929,42 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
         <v>1991</v>
       </c>
       <c r="B23" s="17"/>
-      <c r="C23" s="18">
+      <c r="C23" s="45">
         <v>391415.52755128301</v>
       </c>
       <c r="D23" s="19">
         <v>4.44375078195711E-2</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="45">
         <v>218738.34568153901</v>
       </c>
       <c r="F23" s="19">
         <v>7.3662489463029807E-2</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="45">
         <v>76828.038137784999</v>
       </c>
       <c r="H23" s="19">
         <v>-2.8042167182341898E-2</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="45">
         <v>89063.359040906595</v>
       </c>
       <c r="J23" s="19">
         <v>6.0976912457808098E-2</v>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="45">
         <v>18826.302565772501</v>
       </c>
       <c r="L23" s="19">
         <v>1.38682463145083E-2</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="45">
         <v>-12040.517874720001</v>
       </c>
       <c r="N23" s="19">
@@ -23847,42 +25037,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
         <v>1992</v>
       </c>
       <c r="B24" s="17"/>
-      <c r="C24" s="18">
+      <c r="C24" s="45">
         <v>399556.86425075599</v>
       </c>
       <c r="D24" s="19">
         <v>2.079972848907E-2</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="45">
         <v>225744.297943346</v>
       </c>
       <c r="F24" s="19">
         <v>3.20289167405838E-2</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="45">
         <v>75906.012277514994</v>
       </c>
       <c r="H24" s="19">
         <v>-1.20011636717365E-2</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="45">
         <v>91710.313051464298</v>
       </c>
       <c r="J24" s="19">
         <v>2.9719898722234201E-2</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="45">
         <v>18734.5747605305</v>
       </c>
       <c r="L24" s="19">
         <v>-4.8723218444798296E-3</v>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="45">
         <v>-12538.3337821</v>
       </c>
       <c r="N24" s="19">
@@ -23955,42 +25145,42 @@
         <v>0.99999999999999944</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
         <v>1993</v>
       </c>
       <c r="B25" s="17"/>
-      <c r="C25" s="18">
+      <c r="C25" s="45">
         <v>408319.60620642401</v>
       </c>
       <c r="D25" s="19">
         <v>2.1931151081836499E-2</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="45">
         <v>228474.05115768799</v>
       </c>
       <c r="F25" s="19">
         <v>1.20922355036714E-2</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="45">
         <v>81352.737932190401</v>
       </c>
       <c r="H25" s="19">
         <v>7.1756182300316801E-2</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="45">
         <v>91929.025693728894</v>
       </c>
       <c r="J25" s="19">
         <v>2.3848205832843702E-3</v>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="45">
         <v>19500.539721726698</v>
       </c>
       <c r="L25" s="19">
         <v>4.08850999281773E-2</v>
       </c>
-      <c r="M25" s="18">
+      <c r="M25" s="45">
         <v>-12936.748298910001</v>
       </c>
       <c r="N25" s="19">
@@ -24063,42 +25253,42 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
         <v>1994</v>
       </c>
       <c r="B26" s="17"/>
-      <c r="C26" s="18">
+      <c r="C26" s="45">
         <v>418401.76711088698</v>
       </c>
       <c r="D26" s="19">
         <v>2.4691836373309101E-2</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="45">
         <v>229826.66281080601</v>
       </c>
       <c r="F26" s="19">
         <v>5.9201981418210998E-3</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="45">
         <v>89929.649890297194</v>
       </c>
       <c r="H26" s="19">
         <v>0.105428682255978</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="45">
         <v>91906.195261186804</v>
       </c>
       <c r="J26" s="19">
         <v>-2.4834846632793001E-4</v>
       </c>
-      <c r="K26" s="18">
+      <c r="K26" s="45">
         <v>19748.383557896901</v>
       </c>
       <c r="L26" s="19">
         <v>1.27095885399553E-2</v>
       </c>
-      <c r="M26" s="18">
+      <c r="M26" s="45">
         <v>-13009.1244093</v>
       </c>
       <c r="N26" s="19">
@@ -24171,42 +25361,42 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27" s="17">
         <v>1995</v>
       </c>
       <c r="B27" s="17"/>
-      <c r="C27" s="18">
+      <c r="C27" s="45">
         <v>423515.35549793398</v>
       </c>
       <c r="D27" s="19">
         <v>1.22217179491302E-2</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="45">
         <v>235263.12031416199</v>
       </c>
       <c r="F27" s="19">
         <v>2.3654598804453E-2</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="45">
         <v>88845.8131586331</v>
       </c>
       <c r="H27" s="19">
         <v>-1.2052051053086901E-2</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="45">
         <v>90073.676767328798</v>
       </c>
       <c r="J27" s="19">
         <v>-1.9939009428582798E-2</v>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="45">
         <v>22653.29144673</v>
       </c>
       <c r="L27" s="19">
         <v>0.14709598283407299</v>
       </c>
-      <c r="M27" s="18">
+      <c r="M27" s="45">
         <v>-13320.54618892</v>
       </c>
       <c r="N27" s="19">
@@ -24279,42 +25469,42 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28" s="17">
         <v>1996</v>
       </c>
       <c r="B28" s="17"/>
-      <c r="C28" s="18">
+      <c r="C28" s="45">
         <v>426881.82800179801</v>
       </c>
       <c r="D28" s="19">
         <v>7.9488794447752902E-3</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="45">
         <v>235831.05806013601</v>
       </c>
       <c r="F28" s="19">
         <v>2.4140534445673502E-3</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="45">
         <v>92158.899006478998</v>
       </c>
       <c r="H28" s="19">
         <v>3.72902867345071E-2</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="45">
         <v>90384.262289993203</v>
       </c>
       <c r="J28" s="19">
         <v>3.4481275086240002E-3</v>
       </c>
-      <c r="K28" s="18">
+      <c r="K28" s="45">
         <v>22723.879517009998</v>
       </c>
       <c r="L28" s="19">
         <v>3.11601828131614E-3</v>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="45">
         <v>-14216.270871819999</v>
       </c>
       <c r="N28" s="19">
@@ -24387,42 +25577,42 @@
         <v>1.0000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29" s="17">
         <v>1997</v>
       </c>
       <c r="B29" s="17"/>
-      <c r="C29" s="18">
+      <c r="C29" s="45">
         <v>433747.49206923298</v>
       </c>
       <c r="D29" s="19">
         <v>1.6083289606336301E-2</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="45">
         <v>238617.77292695799</v>
       </c>
       <c r="F29" s="19">
         <v>1.18165728031945E-2</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="45">
         <v>95351.807568306598</v>
       </c>
       <c r="H29" s="19">
         <v>3.46456890897009E-2</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="45">
         <v>90688.4288774788</v>
       </c>
       <c r="J29" s="19">
         <v>3.3652604975598099E-3</v>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="45">
         <v>23522.550729670002</v>
       </c>
       <c r="L29" s="19">
         <v>3.5146780815403997E-2</v>
       </c>
-      <c r="M29" s="18">
+      <c r="M29" s="45">
         <v>-14433.068033179999</v>
       </c>
       <c r="N29" s="19">
@@ -24495,42 +25685,42 @@
         <v>1.0000000000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30" s="17">
         <v>1998</v>
       </c>
       <c r="B30" s="17"/>
-      <c r="C30" s="18">
+      <c r="C30" s="45">
         <v>444954.84281793702</v>
       </c>
       <c r="D30" s="19">
         <v>2.5838422016546601E-2</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="45">
         <v>242856.12062233599</v>
       </c>
       <c r="F30" s="19">
         <v>1.7762078840100899E-2</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="45">
         <v>98586.619056308002</v>
       </c>
       <c r="H30" s="19">
         <v>3.3925014852855602E-2</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="45">
         <v>93257.573677733002</v>
       </c>
       <c r="J30" s="19">
         <v>2.83293561488995E-2</v>
       </c>
-      <c r="K30" s="18">
+      <c r="K30" s="45">
         <v>25752.902030839999</v>
       </c>
       <c r="L30" s="19">
         <v>9.4817578535679695E-2</v>
       </c>
-      <c r="M30" s="18">
+      <c r="M30" s="45">
         <v>-15498.37256928</v>
       </c>
       <c r="N30" s="19">
@@ -24603,42 +25793,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A31" s="17">
         <v>1999</v>
       </c>
       <c r="B31" s="17"/>
-      <c r="C31" s="18">
+      <c r="C31" s="45">
         <v>453531.10713721003</v>
       </c>
       <c r="D31" s="19">
         <v>1.92744599990393E-2</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="45">
         <v>247677.31386747799</v>
       </c>
       <c r="F31" s="19">
         <v>1.9852055747194602E-2</v>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="45">
         <v>93727.482219836704</v>
       </c>
       <c r="H31" s="19">
         <v>-4.9287995500646498E-2</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="45">
         <v>98103.476519475298</v>
       </c>
       <c r="J31" s="19">
         <v>5.1962566155625098E-2</v>
       </c>
-      <c r="K31" s="18">
+      <c r="K31" s="45">
         <v>27883.297295230001</v>
       </c>
       <c r="L31" s="19">
         <v>8.2724473608402793E-2</v>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="45">
         <v>-13860.462764809999</v>
       </c>
       <c r="N31" s="19">
@@ -24711,42 +25901,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A32" s="17">
         <v>2000</v>
       </c>
       <c r="B32" s="17"/>
-      <c r="C32" s="18">
+      <c r="C32" s="45">
         <v>476794.43183223403</v>
       </c>
       <c r="D32" s="19">
         <v>5.1293779696540497E-2</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="45">
         <v>257661.955427184</v>
       </c>
       <c r="F32" s="19">
         <v>4.0313104998581401E-2</v>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="45">
         <v>97948.326774442394</v>
       </c>
       <c r="H32" s="19">
         <v>4.50331584145802E-2</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="45">
         <v>104324.530136858</v>
       </c>
       <c r="J32" s="19">
         <v>6.34131820613653E-2</v>
       </c>
-      <c r="K32" s="18">
+      <c r="K32" s="45">
         <v>30694.881650830001</v>
       </c>
       <c r="L32" s="19">
         <v>0.100833998426756</v>
       </c>
-      <c r="M32" s="18">
+      <c r="M32" s="45">
         <v>-13835.26215708</v>
       </c>
       <c r="N32" s="19">
@@ -24819,42 +26009,42 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A33" s="17">
         <v>2001</v>
       </c>
       <c r="B33" s="17"/>
-      <c r="C33" s="18">
+      <c r="C33" s="45">
         <v>489674.25564941502</v>
       </c>
       <c r="D33" s="19">
         <v>2.7013368775483399E-2</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="45">
         <v>272298.95455554599</v>
       </c>
       <c r="F33" s="19">
         <v>5.68069861307028E-2</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="45">
         <v>90871.448591660403</v>
       </c>
       <c r="H33" s="19">
         <v>-7.2251139103976805E-2</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="45">
         <v>110615.68810560901</v>
       </c>
       <c r="J33" s="19">
         <v>6.0303726846393103E-2</v>
       </c>
-      <c r="K33" s="18">
+      <c r="K33" s="45">
         <v>30761.562310550002</v>
       </c>
       <c r="L33" s="19">
         <v>2.1723706407643698E-3</v>
       </c>
-      <c r="M33" s="18">
+      <c r="M33" s="45">
         <v>-14873.397913950001</v>
       </c>
       <c r="N33" s="19">
@@ -24927,42 +26117,42 @@
         <v>1.0000000000000009</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A34" s="17">
         <v>2002</v>
       </c>
       <c r="B34" s="17"/>
-      <c r="C34" s="18">
+      <c r="C34" s="45">
         <v>489292.79718540399</v>
       </c>
       <c r="D34" s="19">
         <v>-7.7900453129831103E-4</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="45">
         <v>280029.43086562498</v>
       </c>
       <c r="F34" s="19">
         <v>2.8389665772668101E-2</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="45">
         <v>81309.619586122601</v>
       </c>
       <c r="H34" s="19">
         <v>-0.10522368855926099</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="45">
         <v>113730.163228127</v>
       </c>
       <c r="J34" s="19">
         <v>2.8155817460037098E-2</v>
       </c>
-      <c r="K34" s="18">
+      <c r="K34" s="45">
         <v>29854.062466719999</v>
       </c>
       <c r="L34" s="19">
         <v>-2.9501097332717899E-2</v>
       </c>
-      <c r="M34" s="18">
+      <c r="M34" s="45">
         <v>-15630.47896119</v>
       </c>
       <c r="N34" s="19">
@@ -25035,42 +26225,42 @@
         <v>1.0000000000000013</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A35" s="17">
         <v>2003</v>
       </c>
       <c r="B35" s="17"/>
-      <c r="C35" s="18">
+      <c r="C35" s="45">
         <v>493651.67529704701</v>
       </c>
       <c r="D35" s="19">
         <v>8.90852703476663E-3</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="45">
         <v>281023.04822666099</v>
       </c>
       <c r="F35" s="19">
         <v>3.54826047378176E-3</v>
       </c>
-      <c r="G35" s="18">
+      <c r="G35" s="45">
         <v>81639.355459541301</v>
       </c>
       <c r="H35" s="19">
         <v>4.05531196797049E-3</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="45">
         <v>116796.481103875</v>
       </c>
       <c r="J35" s="19">
         <v>2.6961342432942199E-2</v>
       </c>
-      <c r="K35" s="18">
+      <c r="K35" s="45">
         <v>30222.412235719999</v>
       </c>
       <c r="L35" s="19">
         <v>1.23383465620677E-2</v>
       </c>
-      <c r="M35" s="18">
+      <c r="M35" s="45">
         <v>-16029.62172875</v>
       </c>
       <c r="N35" s="19">
@@ -25143,42 +26333,42 @@
         <v>1.0000000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A36" s="17">
         <v>2004</v>
       </c>
       <c r="B36" s="17"/>
-      <c r="C36" s="18">
+      <c r="C36" s="45">
         <v>508607.55280216801</v>
       </c>
       <c r="D36" s="19">
         <v>3.02964180079437E-2</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="45">
         <v>283625.61458260799</v>
       </c>
       <c r="F36" s="19">
         <v>9.2610423677701396E-3</v>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="45">
         <v>90477.270484397304</v>
       </c>
       <c r="H36" s="19">
         <v>0.10825557079803</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="45">
         <v>119274.35993984299</v>
       </c>
       <c r="J36" s="19">
         <v>2.1215355227733899E-2</v>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="45">
         <v>31404.528685450001</v>
       </c>
       <c r="L36" s="19">
         <v>3.9113901316350001E-2</v>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="45">
         <v>-16174.22089013</v>
       </c>
       <c r="N36" s="19">
@@ -25251,42 +26441,42 @@
         <v>1.0000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A37" s="17">
         <v>2005</v>
       </c>
       <c r="B37" s="17"/>
-      <c r="C37" s="18">
+      <c r="C37" s="45">
         <v>528601.15710151696</v>
       </c>
       <c r="D37" s="19">
         <v>3.93104746266442E-2</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="45">
         <v>292269.17517148802</v>
       </c>
       <c r="F37" s="19">
         <v>3.0475246749488E-2</v>
       </c>
-      <c r="G37" s="18">
+      <c r="G37" s="45">
         <v>97764.108483215299</v>
       </c>
       <c r="H37" s="19">
         <v>8.0537774402408294E-2</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="45">
         <v>122564.10077375401</v>
       </c>
       <c r="J37" s="19">
         <v>2.7581291029943798E-2</v>
       </c>
-      <c r="K37" s="18">
+      <c r="K37" s="45">
         <v>32480.002539429999</v>
       </c>
       <c r="L37" s="19">
         <v>3.42458205551186E-2</v>
       </c>
-      <c r="M37" s="18">
+      <c r="M37" s="45">
         <v>-16476.229866369998</v>
       </c>
       <c r="N37" s="19">
@@ -25359,42 +26549,42 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A38" s="17">
         <v>2006</v>
       </c>
       <c r="B38" s="17"/>
-      <c r="C38" s="18">
+      <c r="C38" s="45">
         <v>562159.63845092803</v>
       </c>
       <c r="D38" s="19">
         <v>6.3485448146617399E-2</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="45">
         <v>303607.44506135001</v>
       </c>
       <c r="F38" s="19">
         <v>3.87939298874376E-2</v>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="45">
         <v>114030.914763591</v>
       </c>
       <c r="H38" s="19">
         <v>0.16638832525300501</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="45">
         <v>126945.381284847</v>
       </c>
       <c r="J38" s="19">
         <v>3.5746849880461798E-2</v>
       </c>
-      <c r="K38" s="18">
+      <c r="K38" s="45">
         <v>34115.870315009997</v>
       </c>
       <c r="L38" s="19">
         <v>5.0365383241398602E-2</v>
       </c>
-      <c r="M38" s="18">
+      <c r="M38" s="45">
         <v>-16539.972973870001</v>
       </c>
       <c r="N38" s="19">
@@ -25467,42 +26657,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A39" s="17">
         <v>2007</v>
       </c>
       <c r="B39" s="17"/>
-      <c r="C39" s="18">
+      <c r="C39" s="45">
         <v>598992.21216647106</v>
       </c>
       <c r="D39" s="19">
         <v>6.5519776227689105E-2</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="45">
         <v>320152.43053767498</v>
       </c>
       <c r="F39" s="19">
         <v>5.4494663241811299E-2</v>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="45">
         <v>125166.010020635</v>
       </c>
       <c r="H39" s="19">
         <v>9.7649793305000204E-2</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="45">
         <v>133504.30201078099</v>
       </c>
       <c r="J39" s="19">
         <v>5.1667265555856101E-2</v>
       </c>
-      <c r="K39" s="18">
+      <c r="K39" s="45">
         <v>35635.03881667</v>
       </c>
       <c r="L39" s="19">
         <v>4.4529671605405802E-2</v>
       </c>
-      <c r="M39" s="18">
+      <c r="M39" s="45">
         <v>-15465.569219290001</v>
       </c>
       <c r="N39" s="19">
@@ -25575,42 +26765,42 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40" s="17">
         <v>2008</v>
       </c>
       <c r="B40" s="17"/>
-      <c r="C40" s="18">
+      <c r="C40" s="45">
         <v>622461.84339465504</v>
       </c>
       <c r="D40" s="19">
         <v>3.9181863722898398E-2</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="45">
         <v>335872.92269249202</v>
       </c>
       <c r="F40" s="19">
         <v>4.9103147923679397E-2</v>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="45">
         <v>123079.55951443</v>
       </c>
       <c r="H40" s="19">
         <v>-1.6669465662930601E-2</v>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="45">
         <v>142439.977584323</v>
       </c>
       <c r="J40" s="19">
         <v>6.6931742565273303E-2</v>
       </c>
-      <c r="K40" s="18">
+      <c r="K40" s="45">
         <v>36732.247075090003</v>
       </c>
       <c r="L40" s="19">
         <v>3.0790151908203701E-2</v>
       </c>
-      <c r="M40" s="18">
+      <c r="M40" s="45">
         <v>-15662.863471680001</v>
       </c>
       <c r="N40" s="19">
@@ -25683,42 +26873,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41" s="17">
         <v>2009</v>
       </c>
       <c r="B41" s="17"/>
-      <c r="C41" s="18">
+      <c r="C41" s="45">
         <v>613317.965337715</v>
       </c>
       <c r="D41" s="19">
         <v>-1.46898611601205E-2</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="45">
         <v>343635.84407322702</v>
       </c>
       <c r="F41" s="19">
         <v>2.3112674039051501E-2</v>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="45">
         <v>100573.727279977</v>
       </c>
       <c r="H41" s="19">
         <v>-0.182855969937188</v>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="45">
         <v>149678.859024301</v>
       </c>
       <c r="J41" s="19">
         <v>5.0820574130549197E-2</v>
       </c>
-      <c r="K41" s="18">
+      <c r="K41" s="45">
         <v>36070.434106000001</v>
       </c>
       <c r="L41" s="19">
         <v>-1.80172197942884E-2</v>
       </c>
-      <c r="M41" s="18">
+      <c r="M41" s="45">
         <v>-16640.899145790001</v>
       </c>
       <c r="N41" s="19">
@@ -25791,42 +26981,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42" s="17">
         <v>2010</v>
       </c>
       <c r="B42" s="17"/>
-      <c r="C42" s="18">
+      <c r="C42" s="45">
         <v>636172.01998340595</v>
       </c>
       <c r="D42" s="19">
         <v>3.7262979298359401E-2</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="45">
         <v>346614.67467457597</v>
       </c>
       <c r="F42" s="19">
         <v>8.6685677665045997E-3</v>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="45">
         <v>117608.305026513</v>
       </c>
       <c r="H42" s="19">
         <v>0.16937403243607699</v>
       </c>
-      <c r="I42" s="18">
+      <c r="I42" s="45">
         <v>150923.54894169699</v>
       </c>
       <c r="J42" s="19">
         <v>8.3157362737125203E-3</v>
       </c>
-      <c r="K42" s="18">
+      <c r="K42" s="45">
         <v>37801.799804449998</v>
       </c>
       <c r="L42" s="19">
         <v>4.7999580303415203E-2</v>
       </c>
-      <c r="M42" s="18">
+      <c r="M42" s="45">
         <v>-16776.308463829999</v>
       </c>
       <c r="N42" s="19">
@@ -25899,42 +27089,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A43" s="17">
         <v>2011</v>
       </c>
       <c r="B43" s="17"/>
-      <c r="C43" s="18">
+      <c r="C43" s="45">
         <v>645812.25803482695</v>
       </c>
       <c r="D43" s="19">
         <v>1.5153508404333899E-2</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="45">
         <v>359757.35209399601</v>
       </c>
       <c r="F43" s="19">
         <v>3.7917256191646299E-2</v>
       </c>
-      <c r="G43" s="18">
+      <c r="G43" s="45">
         <v>111699.387910672</v>
       </c>
       <c r="H43" s="19">
         <v>-5.0242345678812202E-2</v>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="45">
         <v>153645.28138966899</v>
       </c>
       <c r="J43" s="19">
         <v>1.8033848707224E-2</v>
       </c>
-      <c r="K43" s="18">
+      <c r="K43" s="45">
         <v>38476.286591540003</v>
       </c>
       <c r="L43" s="19">
         <v>1.7842716235183301E-2</v>
       </c>
-      <c r="M43" s="18">
+      <c r="M43" s="45">
         <v>-17766.049951050001</v>
       </c>
       <c r="N43" s="19">
@@ -26007,42 +27197,42 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A44" s="17">
         <v>2012</v>
       </c>
       <c r="B44" s="17"/>
-      <c r="C44" s="18">
+      <c r="C44" s="45">
         <v>654393.62395549798</v>
       </c>
       <c r="D44" s="19">
         <v>1.3287709878385E-2</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="45">
         <v>368980.04398435698</v>
       </c>
       <c r="F44" s="19">
         <v>2.5635867722173501E-2</v>
       </c>
-      <c r="G44" s="18">
+      <c r="G44" s="45">
         <v>114547.534262296</v>
       </c>
       <c r="H44" s="19">
         <v>2.5498316552113199E-2</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="45">
         <v>151487.303366426</v>
       </c>
       <c r="J44" s="19">
         <v>-1.4045195555144699E-2</v>
       </c>
-      <c r="K44" s="18">
+      <c r="K44" s="45">
         <v>38446.698270239998</v>
       </c>
       <c r="L44" s="19">
         <v>-7.6900147912173399E-4</v>
       </c>
-      <c r="M44" s="18">
+      <c r="M44" s="45">
         <v>-19067.955927819999</v>
       </c>
       <c r="N44" s="19">
@@ -26115,42 +27305,42 @@
         <v>1.0000000000000016</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A45" s="17">
         <v>2013</v>
       </c>
       <c r="B45" s="17"/>
-      <c r="C45" s="18">
+      <c r="C45" s="45">
         <v>666210.44413731096</v>
       </c>
       <c r="D45" s="19">
         <v>1.8057663994928801E-2</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="45">
         <v>377349.12749194098</v>
       </c>
       <c r="F45" s="19">
         <v>2.2681669765150798E-2</v>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="45">
         <v>113231.424990955</v>
       </c>
       <c r="H45" s="19">
         <v>-1.14896342362734E-2</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="45">
         <v>155902.35550023499</v>
       </c>
       <c r="J45" s="19">
         <v>2.91447008144936E-2</v>
       </c>
-      <c r="K45" s="18">
+      <c r="K45" s="45">
         <v>38860.206014670002</v>
       </c>
       <c r="L45" s="19">
         <v>1.07553512534022E-2</v>
       </c>
-      <c r="M45" s="18">
+      <c r="M45" s="45">
         <v>-19132.669860490001</v>
       </c>
       <c r="N45" s="19">
@@ -26223,42 +27413,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A46" s="17">
         <v>2014</v>
       </c>
       <c r="B46" s="17"/>
-      <c r="C46" s="18">
+      <c r="C46" s="45">
         <v>679021.94921179803</v>
       </c>
       <c r="D46" s="19">
         <v>1.9230417636393798E-2</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="45">
         <v>383508.77171300899</v>
       </c>
       <c r="F46" s="19">
         <v>1.6323462205963101E-2</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="45">
         <v>116253.44527723501</v>
       </c>
       <c r="H46" s="19">
         <v>2.66888832894321E-2</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="45">
         <v>159448.784731675</v>
       </c>
       <c r="J46" s="19">
         <v>2.2747759134626799E-2</v>
       </c>
-      <c r="K46" s="18">
+      <c r="K46" s="45">
         <v>38957.470197210001</v>
       </c>
       <c r="L46" s="19">
         <v>2.50292503604532E-3</v>
       </c>
-      <c r="M46" s="18">
+      <c r="M46" s="45">
         <v>-19146.522707330001</v>
       </c>
       <c r="N46" s="19">
@@ -26331,42 +27521,42 @@
         <v>1.0000000000000016</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A47" s="17">
         <v>2015</v>
       </c>
       <c r="B47" s="17"/>
-      <c r="C47" s="18">
+      <c r="C47" s="45">
         <v>679632.73968588503</v>
       </c>
       <c r="D47" s="19">
         <v>8.9951506692154105E-4</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="45">
         <v>390648.31645677</v>
       </c>
       <c r="F47" s="19">
         <v>1.8616379260038899E-2</v>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="45">
         <v>111045.384841379</v>
       </c>
       <c r="H47" s="19">
         <v>-4.47991921739197E-2</v>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="45">
         <v>158394.95331530599</v>
       </c>
       <c r="J47" s="19">
         <v>-6.6092157312003198E-3</v>
       </c>
-      <c r="K47" s="18">
+      <c r="K47" s="45">
         <v>39206.889030470003</v>
       </c>
       <c r="L47" s="19">
         <v>6.4023364966307996E-3</v>
       </c>
-      <c r="M47" s="18">
+      <c r="M47" s="45">
         <v>-19662.80395804</v>
       </c>
       <c r="N47" s="19">
@@ -26439,42 +27629,42 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A48" s="17">
         <v>2016</v>
       </c>
       <c r="B48" s="17"/>
-      <c r="C48" s="18">
+      <c r="C48" s="45">
         <v>688404.189284969</v>
       </c>
       <c r="D48" s="19">
         <v>1.2906161058601E-2</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="45">
         <v>395236.06033632503</v>
       </c>
       <c r="F48" s="19">
         <v>1.1743923335358701E-2</v>
       </c>
-      <c r="G48" s="18">
+      <c r="G48" s="45">
         <v>113379.10453306101</v>
       </c>
       <c r="H48" s="19">
         <v>2.1015908900809999E-2</v>
       </c>
-      <c r="I48" s="18">
+      <c r="I48" s="45">
         <v>160602.16878013301</v>
       </c>
       <c r="J48" s="19">
         <v>1.3934885036604601E-2</v>
       </c>
-      <c r="K48" s="18">
+      <c r="K48" s="45">
         <v>39169.058955859997</v>
       </c>
       <c r="L48" s="19">
         <v>-9.64883354570789E-4</v>
       </c>
-      <c r="M48" s="18">
+      <c r="M48" s="45">
         <v>-19982.203320410001</v>
       </c>
       <c r="N48" s="19">
@@ -26547,42 +27737,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A49" s="17">
         <v>2017</v>
       </c>
       <c r="B49" s="17"/>
-      <c r="C49" s="18">
+      <c r="C49" s="45">
         <v>695842.64982842503</v>
       </c>
       <c r="D49" s="19">
         <v>1.0805367920817301E-2</v>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="45">
         <v>400899.35138967598</v>
       </c>
       <c r="F49" s="19">
         <v>1.43288824621204E-2</v>
       </c>
-      <c r="G49" s="18">
+      <c r="G49" s="45">
         <v>111767.963696461</v>
       </c>
       <c r="H49" s="19">
         <v>-1.4210209572876199E-2</v>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="45">
         <v>163146.157173238</v>
       </c>
       <c r="J49" s="19">
         <v>1.58403115750443E-2</v>
       </c>
-      <c r="K49" s="18">
+      <c r="K49" s="45">
         <v>40461.376477509999</v>
       </c>
       <c r="L49" s="19">
         <v>3.2993325755064098E-2</v>
       </c>
-      <c r="M49" s="18">
+      <c r="M49" s="45">
         <v>-20432.198908459999</v>
       </c>
       <c r="N49" s="19">
@@ -26655,42 +27845,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A50" s="17">
         <v>2018</v>
       </c>
       <c r="B50" s="17"/>
-      <c r="C50" s="18">
+      <c r="C50" s="45">
         <v>724383.24489115598</v>
       </c>
       <c r="D50" s="19">
         <v>4.1015874881724201E-2</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="45">
         <v>409780.660806384</v>
       </c>
       <c r="F50" s="19">
         <v>2.2153464169801799E-2</v>
       </c>
-      <c r="G50" s="18">
+      <c r="G50" s="45">
         <v>126709.71565866</v>
       </c>
       <c r="H50" s="19">
         <v>0.133685462882522</v>
       </c>
-      <c r="I50" s="18">
+      <c r="I50" s="45">
         <v>168540.269294542</v>
       </c>
       <c r="J50" s="19">
         <v>3.3063065748929699E-2</v>
       </c>
-      <c r="K50" s="18">
+      <c r="K50" s="45">
         <v>40257.700707570002</v>
       </c>
       <c r="L50" s="19">
         <v>-5.0338319570815103E-3</v>
       </c>
-      <c r="M50" s="18">
+      <c r="M50" s="45">
         <v>-20905.101576000001</v>
       </c>
       <c r="N50" s="19">
@@ -26763,42 +27953,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A51" s="17">
         <v>2019</v>
       </c>
       <c r="B51" s="17"/>
-      <c r="C51" s="18">
+      <c r="C51" s="45">
         <v>731800.76850289002</v>
       </c>
       <c r="D51" s="19">
         <v>1.0239777996037499E-2</v>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="45">
         <v>421687.434788891</v>
       </c>
       <c r="F51" s="19">
         <v>2.90564565908904E-2</v>
       </c>
-      <c r="G51" s="18">
+      <c r="G51" s="45">
         <v>118045.60644939799</v>
       </c>
       <c r="H51" s="19">
         <v>-6.8377623327651404E-2</v>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="45">
         <v>172835.97490358099</v>
       </c>
       <c r="J51" s="19">
         <v>2.5487710604829E-2</v>
       </c>
-      <c r="K51" s="18">
+      <c r="K51" s="45">
         <v>40468.752715499999</v>
       </c>
       <c r="L51" s="19">
         <v>5.2425251373164903E-3</v>
       </c>
-      <c r="M51" s="18">
+      <c r="M51" s="45">
         <v>-21237.000354479998</v>
       </c>
       <c r="N51" s="19">
@@ -26871,42 +28061,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A52" s="17">
         <v>2020</v>
       </c>
       <c r="B52" s="17"/>
-      <c r="C52" s="18">
+      <c r="C52" s="45">
         <v>709854.59789991495</v>
       </c>
       <c r="D52" s="19">
         <v>-2.99892696858911E-2</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="45">
         <v>415038.27540583903</v>
       </c>
       <c r="F52" s="19">
         <v>-1.5767980818258899E-2</v>
       </c>
-      <c r="G52" s="18">
+      <c r="G52" s="45">
         <v>100815.094472981</v>
       </c>
       <c r="H52" s="19">
         <v>-0.145964873193342</v>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="45">
         <v>176488.93440639501</v>
       </c>
       <c r="J52" s="19">
         <v>2.1135411796368499E-2</v>
       </c>
-      <c r="K52" s="18">
+      <c r="K52" s="45">
         <v>39864.963945000003</v>
       </c>
       <c r="L52" s="19">
         <v>-1.49198759532991E-2</v>
       </c>
-      <c r="M52" s="18">
+      <c r="M52" s="45">
         <v>-22352.670330299999</v>
       </c>
       <c r="N52" s="19">
@@ -26979,42 +28169,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A53" s="17">
         <v>2021</v>
       </c>
       <c r="B53" s="17"/>
-      <c r="C53" s="18">
+      <c r="C53" s="45">
         <v>768279.35247361602</v>
       </c>
       <c r="D53" s="19">
         <v>8.2305242153180899E-2</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="45">
         <v>434093.01005531498</v>
       </c>
       <c r="F53" s="19">
         <v>4.5910788904574E-2</v>
       </c>
-      <c r="G53" s="18">
+      <c r="G53" s="45">
         <v>137062.86080584201</v>
       </c>
       <c r="H53" s="19">
         <v>0.35954701547769102</v>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="45">
         <v>181960.46584894901</v>
       </c>
       <c r="J53" s="19">
         <v>3.1002121809828202E-2</v>
       </c>
-      <c r="K53" s="18">
+      <c r="K53" s="45">
         <v>42248.054040149997</v>
       </c>
       <c r="L53" s="19">
         <v>5.97790605915971E-2</v>
       </c>
-      <c r="M53" s="18">
+      <c r="M53" s="45">
         <v>-27085.03827664</v>
       </c>
       <c r="N53" s="19">
@@ -27087,42 +28277,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A54" s="17">
         <v>2022</v>
       </c>
       <c r="B54" s="17"/>
-      <c r="C54" s="18">
+      <c r="C54" s="45">
         <v>819703.68671952398</v>
       </c>
       <c r="D54" s="19">
         <v>6.6934421809381306E-2</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="45">
         <v>459689.26048144902</v>
       </c>
       <c r="F54" s="19">
         <v>5.8964898842468E-2</v>
       </c>
-      <c r="G54" s="18">
+      <c r="G54" s="45">
         <v>146043.514491398</v>
       </c>
       <c r="H54" s="19">
         <v>6.5522152629494207E-2</v>
       </c>
-      <c r="I54" s="18">
+      <c r="I54" s="45">
         <v>194727.503698007</v>
       </c>
       <c r="J54" s="19">
         <v>7.0163800633793502E-2</v>
       </c>
-      <c r="K54" s="18">
+      <c r="K54" s="45">
         <v>43487.990104190001</v>
       </c>
       <c r="L54" s="19">
         <v>2.9348950909352099E-2</v>
       </c>
-      <c r="M54" s="18">
+      <c r="M54" s="45">
         <v>-24244.582055520001</v>
       </c>
       <c r="N54" s="19">
@@ -27195,42 +28385,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A55" s="17">
         <v>2023</v>
       </c>
       <c r="B55" s="17"/>
-      <c r="C55" s="18">
+      <c r="C55" s="45">
         <v>834189.81128891394</v>
       </c>
       <c r="D55" s="19">
         <v>1.76723916264971E-2</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="45">
         <v>476597.73111085198</v>
       </c>
       <c r="F55" s="19">
         <v>3.67823921135206E-2</v>
       </c>
-      <c r="G55" s="18">
+      <c r="G55" s="45">
         <v>133461.90386745901</v>
       </c>
       <c r="H55" s="19">
         <v>-8.6149738779945806E-2</v>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="45">
         <v>205112.029398724</v>
       </c>
       <c r="J55" s="19">
         <v>5.3328500101464303E-2</v>
       </c>
-      <c r="K55" s="18">
+      <c r="K55" s="45">
         <v>42881.119232279998</v>
       </c>
       <c r="L55" s="19">
         <v>-1.39549073308753E-2</v>
       </c>
-      <c r="M55" s="18">
+      <c r="M55" s="45">
         <v>-23862.9723204</v>
       </c>
       <c r="N55" s="19">
@@ -27303,42 +28493,42 @@
         <v>1.0000000000000013</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A56" s="17">
         <v>2024</v>
       </c>
       <c r="B56" s="17"/>
-      <c r="C56" s="18">
+      <c r="C56" s="45">
         <v>853956.984778921</v>
       </c>
       <c r="D56" s="19">
         <v>2.3696253805191199E-2</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="45">
         <v>492615.43879823398</v>
       </c>
       <c r="F56" s="19">
         <v>3.3608443015555198E-2</v>
       </c>
-      <c r="G56" s="18">
+      <c r="G56" s="45">
         <v>129289.81721319001</v>
       </c>
       <c r="H56" s="19">
         <v>-3.1260506057305897E-2</v>
       </c>
-      <c r="I56" s="18">
+      <c r="I56" s="45">
         <v>211775.65393723699</v>
       </c>
       <c r="J56" s="19">
         <v>3.2487731499937202E-2</v>
       </c>
-      <c r="K56" s="18">
+      <c r="K56" s="45">
         <v>45008.232084759999</v>
       </c>
       <c r="L56" s="19">
         <v>4.9604881835237903E-2</v>
       </c>
-      <c r="M56" s="18">
+      <c r="M56" s="45">
         <v>-24732.157254500002</v>
       </c>
       <c r="N56" s="19">
@@ -27411,7 +28601,7 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="18"/>
@@ -27449,6 +28639,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q5:R10"/>
+    <mergeCell ref="S5:T10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="C4:N4"/>
     <mergeCell ref="O4:Z4"/>
     <mergeCell ref="AA4:AF4"/>
@@ -27461,39 +28668,1316 @@
     <mergeCell ref="O5:P10"/>
     <mergeCell ref="AE5:AF10"/>
     <mergeCell ref="AA6:AB10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q5:R10"/>
-    <mergeCell ref="S5:T10"/>
     <mergeCell ref="U5:V10"/>
     <mergeCell ref="W5:X10"/>
     <mergeCell ref="Y5:Z10"/>
     <mergeCell ref="AC5:AD10"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AD11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF91B6AF-CD17-4790-A209-8BC748F04641}">
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" style="51" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" s="51" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>374762.03661856701</v>
+      </c>
+      <c r="B2">
+        <v>203731.01214603899</v>
+      </c>
+      <c r="C2">
+        <v>79044.620603616393</v>
+      </c>
+      <c r="D2">
+        <v>83944.672117875496</v>
+      </c>
+      <c r="E2">
+        <v>18568.786066836201</v>
+      </c>
+      <c r="F2">
+        <v>-10527.0543158</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="50">
+        <f>B2/A2</f>
+        <v>0.54362766833129506</v>
+      </c>
+      <c r="L2" s="51">
+        <f>(C2+D2+E2+F2)/A2</f>
+        <v>0.45637233166870522</v>
+      </c>
+      <c r="M2">
+        <f>K2+L2</f>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>391415.52755128301</v>
+      </c>
+      <c r="B3">
+        <v>218738.34568153901</v>
+      </c>
+      <c r="C3">
+        <v>76828.038137784999</v>
+      </c>
+      <c r="D3">
+        <v>89063.359040906595</v>
+      </c>
+      <c r="E3">
+        <v>18826.302565772501</v>
+      </c>
+      <c r="F3">
+        <v>-12040.517874720001</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="50">
+        <f t="shared" ref="K3:K36" si="0">B3/A3</f>
+        <v>0.55883921378893187</v>
+      </c>
+      <c r="L3" s="51">
+        <f t="shared" ref="L3:L36" si="1">(C3+D3+E3+F3)/A3</f>
+        <v>0.44116078621106825</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M36" si="2">K3+L3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>399556.86425075599</v>
+      </c>
+      <c r="B4">
+        <v>225744.297943346</v>
+      </c>
+      <c r="C4">
+        <v>75906.012277514994</v>
+      </c>
+      <c r="D4">
+        <v>91710.313051464298</v>
+      </c>
+      <c r="E4">
+        <v>18734.5747605305</v>
+      </c>
+      <c r="F4">
+        <v>-12538.3337821</v>
+      </c>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56498665932484693</v>
+      </c>
+      <c r="L4" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43501334067515252</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999944</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>408319.60620642401</v>
+      </c>
+      <c r="B5">
+        <v>228474.05115768799</v>
+      </c>
+      <c r="C5">
+        <v>81352.737932190401</v>
+      </c>
+      <c r="D5">
+        <v>91929.025693728894</v>
+      </c>
+      <c r="E5">
+        <v>19500.539721726698</v>
+      </c>
+      <c r="F5">
+        <v>-12936.748298910001</v>
+      </c>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55954709909811196</v>
+      </c>
+      <c r="L5" s="51">
+        <f t="shared" si="1"/>
+        <v>0.44045290090188793</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>418401.76711088698</v>
+      </c>
+      <c r="B6">
+        <v>229826.66281080601</v>
+      </c>
+      <c r="C6">
+        <v>89929.649890297194</v>
+      </c>
+      <c r="D6">
+        <v>91906.195261186804</v>
+      </c>
+      <c r="E6">
+        <v>19748.383557896901</v>
+      </c>
+      <c r="F6">
+        <v>-13009.1244093</v>
+      </c>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="50">
+        <f t="shared" si="0"/>
+        <v>0.54929658733945108</v>
+      </c>
+      <c r="L6" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4507034126605487</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>423515.35549793398</v>
+      </c>
+      <c r="B7">
+        <v>235263.12031416199</v>
+      </c>
+      <c r="C7">
+        <v>88845.8131586331</v>
+      </c>
+      <c r="D7">
+        <v>90073.676767328798</v>
+      </c>
+      <c r="E7">
+        <v>22653.29144673</v>
+      </c>
+      <c r="F7">
+        <v>-13320.54618892</v>
+      </c>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55550080359556098</v>
+      </c>
+      <c r="L7" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4444991964044388</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>426881.82800179801</v>
+      </c>
+      <c r="B8">
+        <v>235831.05806013601</v>
+      </c>
+      <c r="C8">
+        <v>92158.899006478998</v>
+      </c>
+      <c r="D8">
+        <v>90384.262289993203</v>
+      </c>
+      <c r="E8">
+        <v>22723.879517009998</v>
+      </c>
+      <c r="F8">
+        <v>-14216.270871819999</v>
+      </c>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55245045019612005</v>
+      </c>
+      <c r="L8" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4475495498038804</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>433747.49206923298</v>
+      </c>
+      <c r="B9">
+        <v>238617.77292695799</v>
+      </c>
+      <c r="C9">
+        <v>95351.807568306598</v>
+      </c>
+      <c r="D9">
+        <v>90688.4288774788</v>
+      </c>
+      <c r="E9">
+        <v>23522.550729670002</v>
+      </c>
+      <c r="F9">
+        <v>-14433.068033179999</v>
+      </c>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55013061121946683</v>
+      </c>
+      <c r="L9" s="51">
+        <f t="shared" si="1"/>
+        <v>0.44986938878053406</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>444954.84281793702</v>
+      </c>
+      <c r="B10">
+        <v>242856.12062233599</v>
+      </c>
+      <c r="C10">
+        <v>98586.619056308002</v>
+      </c>
+      <c r="D10">
+        <v>93257.573677733002</v>
+      </c>
+      <c r="E10">
+        <v>25752.902030839999</v>
+      </c>
+      <c r="F10">
+        <v>-15498.37256928</v>
+      </c>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5457994772779805</v>
+      </c>
+      <c r="L10" s="51">
+        <f t="shared" si="1"/>
+        <v>0.45420052272201944</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>453531.10713721003</v>
+      </c>
+      <c r="B11">
+        <v>247677.31386747799</v>
+      </c>
+      <c r="C11">
+        <v>93727.482219836704</v>
+      </c>
+      <c r="D11">
+        <v>98103.476519475298</v>
+      </c>
+      <c r="E11">
+        <v>27883.297295230001</v>
+      </c>
+      <c r="F11">
+        <v>-13860.462764809999</v>
+      </c>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5461087673365399</v>
+      </c>
+      <c r="L11" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4538912326634601</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>476794.43183223403</v>
+      </c>
+      <c r="B12">
+        <v>257661.955427184</v>
+      </c>
+      <c r="C12">
+        <v>97948.326774442394</v>
+      </c>
+      <c r="D12">
+        <v>104324.530136858</v>
+      </c>
+      <c r="E12">
+        <v>30694.881650830001</v>
+      </c>
+      <c r="F12">
+        <v>-13835.26215708</v>
+      </c>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="50">
+        <f t="shared" si="0"/>
+        <v>0.54040470740615842</v>
+      </c>
+      <c r="L12" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4595952925938423</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>489674.25564941502</v>
+      </c>
+      <c r="B13">
+        <v>272298.95455554599</v>
+      </c>
+      <c r="C13">
+        <v>90871.448591660403</v>
+      </c>
+      <c r="D13">
+        <v>110615.68810560901</v>
+      </c>
+      <c r="E13">
+        <v>30761.562310550002</v>
+      </c>
+      <c r="F13">
+        <v>-14873.397913950001</v>
+      </c>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55608182667152495</v>
+      </c>
+      <c r="L13" s="51">
+        <f t="shared" si="1"/>
+        <v>0.44391817332847583</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>489292.79718540399</v>
+      </c>
+      <c r="B14">
+        <v>280029.43086562498</v>
+      </c>
+      <c r="C14">
+        <v>81309.619586122601</v>
+      </c>
+      <c r="D14">
+        <v>113730.163228127</v>
+      </c>
+      <c r="E14">
+        <v>29854.062466719999</v>
+      </c>
+      <c r="F14">
+        <v>-15630.47896119</v>
+      </c>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5723146395705383</v>
+      </c>
+      <c r="L14" s="51">
+        <f t="shared" si="1"/>
+        <v>0.42768536042946292</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>493651.67529704701</v>
+      </c>
+      <c r="B15">
+        <v>281023.04822666099</v>
+      </c>
+      <c r="C15">
+        <v>81639.355459541301</v>
+      </c>
+      <c r="D15">
+        <v>116796.481103875</v>
+      </c>
+      <c r="E15">
+        <v>30222.412235719999</v>
+      </c>
+      <c r="F15">
+        <v>-16029.62172875</v>
+      </c>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56927396844659717</v>
+      </c>
+      <c r="L15" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43072603155340333</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>508607.55280216801</v>
+      </c>
+      <c r="B16">
+        <v>283625.61458260799</v>
+      </c>
+      <c r="C16">
+        <v>90477.270484397304</v>
+      </c>
+      <c r="D16">
+        <v>119274.35993984299</v>
+      </c>
+      <c r="E16">
+        <v>31404.528685450001</v>
+      </c>
+      <c r="F16">
+        <v>-16174.22089013</v>
+      </c>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55765120478446617</v>
+      </c>
+      <c r="L16" s="51">
+        <f t="shared" si="1"/>
+        <v>0.44234879521553438</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>528601.15710151696</v>
+      </c>
+      <c r="B17">
+        <v>292269.17517148802</v>
+      </c>
+      <c r="C17">
+        <v>97764.108483215299</v>
+      </c>
+      <c r="D17">
+        <v>122564.10077375401</v>
+      </c>
+      <c r="E17">
+        <v>32480.002539429999</v>
+      </c>
+      <c r="F17">
+        <v>-16476.229866369998</v>
+      </c>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55291058531557136</v>
+      </c>
+      <c r="L17" s="51">
+        <f t="shared" si="1"/>
+        <v>0.44708941468442931</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>562159.63845092803</v>
+      </c>
+      <c r="B18">
+        <v>303607.44506135001</v>
+      </c>
+      <c r="C18">
+        <v>114030.914763591</v>
+      </c>
+      <c r="D18">
+        <v>126945.381284847</v>
+      </c>
+      <c r="E18">
+        <v>34115.870315009997</v>
+      </c>
+      <c r="F18">
+        <v>-16539.972973870001</v>
+      </c>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="50">
+        <f t="shared" si="0"/>
+        <v>0.54007336047454868</v>
+      </c>
+      <c r="L18" s="51">
+        <f t="shared" si="1"/>
+        <v>0.45992663952545132</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>598992.21216647106</v>
+      </c>
+      <c r="B19">
+        <v>320152.43053767498</v>
+      </c>
+      <c r="C19">
+        <v>125166.010020635</v>
+      </c>
+      <c r="D19">
+        <v>133504.30201078099</v>
+      </c>
+      <c r="E19">
+        <v>35635.03881667</v>
+      </c>
+      <c r="F19">
+        <v>-15465.569219290001</v>
+      </c>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="50">
+        <f t="shared" si="0"/>
+        <v>0.53448513024856936</v>
+      </c>
+      <c r="L19" s="51">
+        <f t="shared" si="1"/>
+        <v>0.46551486975143053</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>622461.84339465504</v>
+      </c>
+      <c r="B20">
+        <v>335872.92269249202</v>
+      </c>
+      <c r="C20">
+        <v>123079.55951443</v>
+      </c>
+      <c r="D20">
+        <v>142439.977584323</v>
+      </c>
+      <c r="E20">
+        <v>36732.247075090003</v>
+      </c>
+      <c r="F20">
+        <v>-15662.863471680001</v>
+      </c>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="50">
+        <f t="shared" si="0"/>
+        <v>0.53958797034172734</v>
+      </c>
+      <c r="L20" s="51">
+        <f t="shared" si="1"/>
+        <v>0.46041202965827271</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>613317.965337715</v>
+      </c>
+      <c r="B21">
+        <v>343635.84407322702</v>
+      </c>
+      <c r="C21">
+        <v>100573.727279977</v>
+      </c>
+      <c r="D21">
+        <v>149678.859024301</v>
+      </c>
+      <c r="E21">
+        <v>36070.434106000001</v>
+      </c>
+      <c r="F21">
+        <v>-16640.899145790001</v>
+      </c>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56028987163943378</v>
+      </c>
+      <c r="L21" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43971012836056622</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>636172.01998340595</v>
+      </c>
+      <c r="B22">
+        <v>346614.67467457597</v>
+      </c>
+      <c r="C22">
+        <v>117608.305026513</v>
+      </c>
+      <c r="D22">
+        <v>150923.54894169699</v>
+      </c>
+      <c r="E22">
+        <v>37801.799804449998</v>
+      </c>
+      <c r="F22">
+        <v>-16776.308463829999</v>
+      </c>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5448442619083077</v>
+      </c>
+      <c r="L22" s="51">
+        <f t="shared" si="1"/>
+        <v>0.45515573809169241</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>645812.25803482695</v>
+      </c>
+      <c r="B23">
+        <v>359757.35209399601</v>
+      </c>
+      <c r="C23">
+        <v>111699.387910672</v>
+      </c>
+      <c r="D23">
+        <v>153645.28138966899</v>
+      </c>
+      <c r="E23">
+        <v>38476.286591540003</v>
+      </c>
+      <c r="F23">
+        <v>-17766.049951050001</v>
+      </c>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="50">
+        <f t="shared" si="0"/>
+        <v>0.55706182039455077</v>
+      </c>
+      <c r="L23" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4429381796054494</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>654393.62395549798</v>
+      </c>
+      <c r="B24">
+        <v>368980.04398435698</v>
+      </c>
+      <c r="C24">
+        <v>114547.534262296</v>
+      </c>
+      <c r="D24">
+        <v>151487.303366426</v>
+      </c>
+      <c r="E24">
+        <v>38446.698270239998</v>
+      </c>
+      <c r="F24">
+        <v>-19067.955927819999</v>
+      </c>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56385030427718452</v>
+      </c>
+      <c r="L24" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43614969572281703</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000016</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>666210.44413731096</v>
+      </c>
+      <c r="B25">
+        <v>377349.12749194098</v>
+      </c>
+      <c r="C25">
+        <v>113231.424990955</v>
+      </c>
+      <c r="D25">
+        <v>155902.35550023499</v>
+      </c>
+      <c r="E25">
+        <v>38860.206014670002</v>
+      </c>
+      <c r="F25">
+        <v>-19132.669860490001</v>
+      </c>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56641130563568065</v>
+      </c>
+      <c r="L25" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43358869436431935</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>679021.94921179803</v>
+      </c>
+      <c r="B26">
+        <v>383508.77171300899</v>
+      </c>
+      <c r="C26">
+        <v>116253.44527723501</v>
+      </c>
+      <c r="D26">
+        <v>159448.784731675</v>
+      </c>
+      <c r="E26">
+        <v>38957.470197210001</v>
+      </c>
+      <c r="F26">
+        <v>-19146.522707330001</v>
+      </c>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5647958393070831</v>
+      </c>
+      <c r="L26" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4352041606929184</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000016</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>679632.73968588503</v>
+      </c>
+      <c r="B27">
+        <v>390648.31645677</v>
+      </c>
+      <c r="C27">
+        <v>111045.384841379</v>
+      </c>
+      <c r="D27">
+        <v>158394.95331530599</v>
+      </c>
+      <c r="E27">
+        <v>39206.889030470003</v>
+      </c>
+      <c r="F27">
+        <v>-19662.80395804</v>
+      </c>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="50">
+        <f t="shared" si="0"/>
+        <v>0.57479325766048461</v>
+      </c>
+      <c r="L27" s="51">
+        <f t="shared" si="1"/>
+        <v>0.42520674233951528</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>688404.189284969</v>
+      </c>
+      <c r="B28">
+        <v>395236.06033632503</v>
+      </c>
+      <c r="C28">
+        <v>113379.10453306101</v>
+      </c>
+      <c r="D28">
+        <v>160602.16878013301</v>
+      </c>
+      <c r="E28">
+        <v>39169.058955859997</v>
+      </c>
+      <c r="F28">
+        <v>-19982.203320410001</v>
+      </c>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5741337233099183</v>
+      </c>
+      <c r="L28" s="51">
+        <f t="shared" si="1"/>
+        <v>0.42586627669008176</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>695842.64982842503</v>
+      </c>
+      <c r="B29">
+        <v>400899.35138967598</v>
+      </c>
+      <c r="C29">
+        <v>111767.963696461</v>
+      </c>
+      <c r="D29">
+        <v>163146.157173238</v>
+      </c>
+      <c r="E29">
+        <v>40461.376477509999</v>
+      </c>
+      <c r="F29">
+        <v>-20432.198908459999</v>
+      </c>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5761350665822601</v>
+      </c>
+      <c r="L29" s="51">
+        <f t="shared" si="1"/>
+        <v>0.42386493341773984</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>724383.24489115598</v>
+      </c>
+      <c r="B30">
+        <v>409780.660806384</v>
+      </c>
+      <c r="C30">
+        <v>126709.71565866</v>
+      </c>
+      <c r="D30">
+        <v>168540.269294542</v>
+      </c>
+      <c r="E30">
+        <v>40257.700707570002</v>
+      </c>
+      <c r="F30">
+        <v>-20905.101576000001</v>
+      </c>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56569594023113634</v>
+      </c>
+      <c r="L30" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43430405976886371</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>731800.76850289002</v>
+      </c>
+      <c r="B31">
+        <v>421687.434788891</v>
+      </c>
+      <c r="C31">
+        <v>118045.60644939799</v>
+      </c>
+      <c r="D31">
+        <v>172835.97490358099</v>
+      </c>
+      <c r="E31">
+        <v>40468.752715499999</v>
+      </c>
+      <c r="F31">
+        <v>-21237.000354479998</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="50">
+        <f t="shared" si="0"/>
+        <v>0.57623256621002805</v>
+      </c>
+      <c r="L31" s="51">
+        <f t="shared" si="1"/>
+        <v>0.42376743378997195</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>709854.59789991495</v>
+      </c>
+      <c r="B32">
+        <v>415038.27540583903</v>
+      </c>
+      <c r="C32">
+        <v>100815.094472981</v>
+      </c>
+      <c r="D32">
+        <v>176488.93440639501</v>
+      </c>
+      <c r="E32">
+        <v>39864.963945000003</v>
+      </c>
+      <c r="F32">
+        <v>-22352.670330299999</v>
+      </c>
+      <c r="K32" s="50">
+        <f t="shared" si="0"/>
+        <v>0.58468068902239723</v>
+      </c>
+      <c r="L32" s="51">
+        <f t="shared" si="1"/>
+        <v>0.41531931097760288</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>768279.35247361602</v>
+      </c>
+      <c r="B33">
+        <v>434093.01005531498</v>
+      </c>
+      <c r="C33">
+        <v>137062.86080584201</v>
+      </c>
+      <c r="D33">
+        <v>181960.46584894901</v>
+      </c>
+      <c r="E33">
+        <v>42248.054040149997</v>
+      </c>
+      <c r="F33">
+        <v>-27085.03827664</v>
+      </c>
+      <c r="K33" s="50">
+        <f t="shared" si="0"/>
+        <v>0.5650197531115122</v>
+      </c>
+      <c r="L33" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4349802468884878</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>819703.68671952398</v>
+      </c>
+      <c r="B34">
+        <v>459689.26048144902</v>
+      </c>
+      <c r="C34">
+        <v>146043.514491398</v>
+      </c>
+      <c r="D34">
+        <v>194727.503698007</v>
+      </c>
+      <c r="E34">
+        <v>43487.990104190001</v>
+      </c>
+      <c r="F34">
+        <v>-24244.582055520001</v>
+      </c>
+      <c r="K34" s="50">
+        <f t="shared" si="0"/>
+        <v>0.56079930824898161</v>
+      </c>
+      <c r="L34" s="51">
+        <f t="shared" si="1"/>
+        <v>0.43920069175101839</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>834189.81128891394</v>
+      </c>
+      <c r="B35">
+        <v>476597.73111085198</v>
+      </c>
+      <c r="C35">
+        <v>133461.90386745901</v>
+      </c>
+      <c r="D35">
+        <v>205112.029398724</v>
+      </c>
+      <c r="E35">
+        <v>42881.119232279998</v>
+      </c>
+      <c r="F35">
+        <v>-23862.9723204</v>
+      </c>
+      <c r="K35" s="50">
+        <f t="shared" si="0"/>
+        <v>0.57133007939099212</v>
+      </c>
+      <c r="L35" s="51">
+        <f t="shared" si="1"/>
+        <v>0.4286699206090091</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000013</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>853956.984778921</v>
+      </c>
+      <c r="B36">
+        <v>492615.43879823398</v>
+      </c>
+      <c r="C36">
+        <v>129289.81721319001</v>
+      </c>
+      <c r="D36">
+        <v>211775.65393723699</v>
+      </c>
+      <c r="E36">
+        <v>45008.232084759999</v>
+      </c>
+      <c r="F36">
+        <v>-24732.157254500002</v>
+      </c>
+      <c r="K36" s="50">
+        <f t="shared" si="0"/>
+        <v>0.57686212254094515</v>
+      </c>
+      <c r="L36" s="51">
+        <f t="shared" si="1"/>
+        <v>0.42313787745905473</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G3:J31"/>
+    <mergeCell ref="G2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Table01"/>
   <dimension ref="A1:AR57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
@@ -27501,27 +29985,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>85</v>
       </c>
@@ -27529,7 +30013,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>77</v>
       </c>
@@ -27537,7 +30021,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="15" t="s">
         <v>2</v>
       </c>
@@ -27548,7 +30032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AO17" s="15" t="s">
         <v>16</v>
       </c>
@@ -27559,7 +30043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E18" s="15" t="s">
         <v>27</v>
       </c>
@@ -27597,7 +30081,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="M19" s="15" t="s">
         <v>16</v>
       </c>
@@ -27617,7 +30101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>7</v>
       </c>
@@ -27625,12 +30109,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
         <v>86</v>
       </c>
@@ -27638,7 +30122,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
         <v>78</v>
       </c>
@@ -27646,15 +30130,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
     </row>
-    <row r="27" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
     </row>
-    <row r="28" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="15" t="s">
@@ -27667,7 +30151,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AO29" s="15" t="s">
         <v>16</v>
       </c>
@@ -27678,7 +30162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="14" t="s">
         <v>39</v>
       </c>
@@ -27723,7 +30207,7 @@
       <c r="AO30" s="14"/>
       <c r="AQ30" s="14"/>
     </row>
-    <row r="31" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K31" s="16"/>
       <c r="M31" s="15" t="s">
         <v>16</v>
@@ -27735,7 +30219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>9</v>
       </c>
@@ -27743,12 +30227,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>81</v>
       </c>
@@ -27756,7 +30240,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>26</v>
       </c>
@@ -27764,15 +30248,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
     </row>
-    <row r="39" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
     </row>
-    <row r="40" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14"/>
       <c r="B40" s="14"/>
       <c r="C40" s="15" t="s">
@@ -27785,7 +30269,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AO41" s="15" t="s">
         <v>16</v>
       </c>
@@ -27796,7 +30280,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E42" s="14" t="s">
         <v>53</v>
       </c>
@@ -27841,7 +30325,7 @@
       <c r="AO42" s="14"/>
       <c r="AQ42" s="14"/>
     </row>
-    <row r="43" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="M43" s="15" t="s">
         <v>16</v>
       </c>
@@ -27852,7 +30336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
         <v>12</v>
       </c>
@@ -27860,12 +30344,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
         <v>83</v>
       </c>
@@ -27873,7 +30357,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
         <v>13</v>
       </c>
@@ -27881,15 +30365,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
     </row>
-    <row r="51" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="14"/>
       <c r="B51" s="14"/>
     </row>
-    <row r="52" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="14"/>
       <c r="B52" s="14"/>
       <c r="C52" s="15" t="s">
@@ -27902,7 +30386,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AO53" s="15" t="s">
         <v>16</v>
       </c>
@@ -27913,7 +30397,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E54" s="14" t="s">
         <v>64</v>
       </c>
@@ -27958,7 +30442,7 @@
       <c r="AO54" s="14"/>
       <c r="AQ54" s="14"/>
     </row>
-    <row r="55" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="M55" s="15" t="s">
         <v>16</v>
       </c>
@@ -27969,7 +30453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:44" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
         <v>14</v>
       </c>
